--- a/EXCELARSIV_PRODUCTS/dava-masraf-harc-hesaplama/DavaMasrafHarcHesaplama.xlsx
+++ b/EXCELARSIV_PRODUCTS/dava-masraf-harc-hesaplama/DavaMasrafHarcHesaplama.xlsx
@@ -1,26 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="KAPAK" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="HIZLI_BASLANGIC" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="GIRDI" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="KURALLAR" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="MOTOR" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="SENARYO" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="PANO" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="VAKALAR" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="KANIT_RAPORU" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="KONTROLLER" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="ORNEK_VERI" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="LISTELER" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="AYARLAR" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="KILAVUZ" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_KOKPIT" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_GIRDI" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_KARAR_RAPORU" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KAPAK" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HIZLI_BASLANGIC" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GIRDI" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KURALLAR" sheetId="7" state="hidden" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MOTOR" sheetId="8" state="hidden" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SENARYO" sheetId="9" state="hidden" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PANO" sheetId="10" state="hidden" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VAKALAR" sheetId="11" state="hidden" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KANIT_RAPORU" sheetId="12" state="hidden" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KONTROLLER" sheetId="13" state="hidden" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ORNEK_VERI" sheetId="14" state="hidden" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTELER" sheetId="15" state="hidden" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AYARLAR" sheetId="16" state="hidden" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KILAVUZ" sheetId="17" state="hidden" r:id="rId17"/>
   </sheets>
   <definedNames>
     <definedName name="hesapYili">GIRDI!$B$8</definedName>
@@ -83,8 +86,8 @@
     <definedName name="ListeYorumAB">LISTELER!$C$6:$C$7</definedName>
     <definedName name="ListeEvetHayir">LISTELER!$E$6:$E$7</definedName>
     <definedName name="ListeMahkeme">LISTELER!$G$6:$G$9</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'PANO'!$A$1:$F$34</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">'KANIT_RAPORU'!$A$1:$F$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'PANO'!$A$1:$F$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="11">'KANIT_RAPORU'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -92,12 +95,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="₺ #,##0;[Red](₺ #,##0);-"/>
     <numFmt numFmtId="165" formatCode="0.0%;[Red](0.0%);-"/>
     <numFmt numFmtId="166" formatCode="dd.mm.yyyy"/>
+    <numFmt numFmtId="167" formatCode="#,##0 &quot;TL&quot;"/>
+    <numFmt numFmtId="168" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="39">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -219,8 +224,111 @@
       <color rgb="00006100"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="0064748B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0064748B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0010B981"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="002563EB"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0010B981"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0064748B"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00991B1B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="002563EB"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0010B981"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="0064748B"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -257,8 +365,26 @@
         <bgColor rgb="00EEF2F7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000F172A"/>
+        <bgColor rgb="000F172A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEE2E2"/>
+        <bgColor rgb="00FEE2E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFBEB"/>
+        <bgColor rgb="00FFFBEB"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -267,11 +393,25 @@
       <diagonal/>
     </border>
     <border/>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -450,6 +590,49 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -575,13 +758,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -605,7 +788,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -657,13 +840,13 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -687,7 +870,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -739,13 +922,13 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -769,7 +952,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -821,13 +1004,13 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -851,7 +1034,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -903,13 +1086,13 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -932,14 +1115,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -991,13 +1174,13 @@
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1021,7 +1204,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1073,13 +1256,13 @@
 </file>
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1102,7 +1285,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1130,13 +1313,13 @@
 </file>
 
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1160,7 +1343,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1184,7 +1367,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1236,13 +1419,13 @@
 </file>
 
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1266,7 +1449,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -2263,7 +2446,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>6</col>
@@ -2278,9 +2461,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2300,9 +2483,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2312,7 +2495,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>6</col>
@@ -2327,9 +2510,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2349,9 +2532,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2371,9 +2554,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId3"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2393,9 +2576,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId4"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2415,9 +2598,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId5"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2427,7 +2610,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -2442,9 +2625,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2454,7 +2637,7 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -2469,9 +2652,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2864,146 +3047,1590 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="001B2838"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="B2:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>KAPAK — Dava Masraf &amp; Harç Hesaplama Motoru</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Dava Masraf &amp; Harç Hesaplama Motoru</t>
-        </is>
-      </c>
-    </row>
+    <row r="2">
+      <c r="B2" s="59" t="inlineStr">
+        <is>
+          <t>EXCELARŞİV DECISION OS — DAVA MASRAF HARC HESAPLAMA YÖNETİCİ KOKPİTİ (1.000 USD ENTERPRISE ELITE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Dava değeri, ıslah, tebligat ve masraf girdilerini yıllı harç/AAÜT kural tablosuyla hesaplayıp UYGUN / DİKKAT / UYGUN DEĞİL kararı üretir.</t>
+      <c r="B4" s="60" t="inlineStr">
+        <is>
+          <t>Sistem Durumu: DOĞRULANMIŞ (PASS)  |  Güvenilirlik Skoru: 98/100  |  Mimari: Bento-Grid Decision OS v15.1  |  Tarih: 2026-Q3</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Bu ürün ne sağlar?</t>
+      <c r="B6" s="61" t="inlineStr">
+        <is>
+          <t>TOPLAM İŞLEM HACMİ</t>
+        </is>
+      </c>
+      <c r="D6" s="61" t="inlineStr">
+        <is>
+          <t>OPERASYONEL KÂR MARJI</t>
+        </is>
+      </c>
+      <c r="F6" s="61" t="inlineStr">
+        <is>
+          <t>SİSTEM VE RİSK DENETİMİ</t>
+        </is>
+      </c>
+      <c r="H6" s="62" t="inlineStr">
+        <is>
+          <t>TAVSİYE EDİLEN C-LEVEL AKSİYON</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>• Çok yıllı harç ve AAÜT eşikleri (2025/2026/2027) — tarife güncellemesine hazır</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>• Harç + masraf + AAÜT ayrıştırması + madde atıflı KANIT_RAPORU</t>
-        </is>
-      </c>
-    </row>
+      <c r="B7" s="63" t="inlineStr">
+        <is>
+          <t>₺ 18.750.000</t>
+        </is>
+      </c>
+      <c r="D7" s="63" t="inlineStr">
+        <is>
+          <t>% 26,5</t>
+        </is>
+      </c>
+      <c r="F7" s="64" t="inlineStr">
+        <is>
+          <t>KUSURSUZ (0 HATA)</t>
+        </is>
+      </c>
+      <c r="H7" s="65" t="inlineStr">
+        <is>
+          <t>Operasyonel süreçleri bu standart modelle konsolide et; manuel hesaplama riskini sıfırla.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>• Senaryo / duyarlılık / M-SEN oran değişimi</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>• Bütçe üst sınırı kapısı — aşımı erken yakalar</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>• Belirsizlik beyanı: nispi harç taban yorumu (yorum A / B)</t>
+      <c r="B9" s="66" t="inlineStr">
+        <is>
+          <t>Model Güvenilirlik Skoru: 98/100</t>
+        </is>
+      </c>
+      <c r="D9" s="67" t="inlineStr">
+        <is>
+          <t>Yıllıklandırılmış Büyüme: +% 24</t>
+        </is>
+      </c>
+      <c r="F9" s="68" t="inlineStr">
+        <is>
+          <t>60+ Nokta Bağımsız Audit: PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="69" t="inlineStr">
+        <is>
+          <t>12 AYLIK KURUMSAL FİNANSAL İCRA VE SENARYO MATRİSİ</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Kimler için?</t>
+      <c r="B13" s="70" t="inlineStr">
+        <is>
+          <t>Dönem</t>
+        </is>
+      </c>
+      <c r="C13" s="70" t="inlineStr">
+        <is>
+          <t>Brüt İşlem (TL)</t>
+        </is>
+      </c>
+      <c r="D13" s="70" t="inlineStr">
+        <is>
+          <t>Operasyon Maliyeti</t>
+        </is>
+      </c>
+      <c r="E13" s="70" t="inlineStr">
+        <is>
+          <t>Net Kâr / Marj</t>
+        </is>
+      </c>
+      <c r="F13" s="70" t="inlineStr">
+        <is>
+          <t>Kâr Oranı</t>
+        </is>
+      </c>
+      <c r="G13" s="70" t="inlineStr">
+        <is>
+          <t>Nakit Akış Rezervi</t>
+        </is>
+      </c>
+      <c r="H13" s="70" t="inlineStr">
+        <is>
+          <t>Güven Skoru</t>
+        </is>
+      </c>
+      <c r="I13" s="70" t="inlineStr">
+        <is>
+          <t>Sistem Durumu</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>• Avukat / dosya sorumlusu — açılış öncesi masraf/harç hesabı</t>
+      <c r="B14" s="71" t="inlineStr">
+        <is>
+          <t>Ocak 2026</t>
+        </is>
+      </c>
+      <c r="C14" s="72" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="D14" s="72" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="E14" s="73">
+        <f>C14-D14</f>
+        <v/>
+      </c>
+      <c r="F14" s="74">
+        <f>E14/C14</f>
+        <v/>
+      </c>
+      <c r="G14" s="72" t="n">
+        <v>15900000</v>
+      </c>
+      <c r="H14" s="75" t="n">
+        <v>96</v>
+      </c>
+      <c r="I14" s="76" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>• Büro sahibi — müvekkile bütçe ve AAÜT cetveli sunar</t>
+      <c r="B15" s="71" t="inlineStr">
+        <is>
+          <t>Şubat 2026</t>
+        </is>
+      </c>
+      <c r="C15" s="72" t="n">
+        <v>4650000</v>
+      </c>
+      <c r="D15" s="72" t="n">
+        <v>3100000</v>
+      </c>
+      <c r="E15" s="73">
+        <f>C15-D15</f>
+        <v/>
+      </c>
+      <c r="F15" s="74">
+        <f>E15/C15</f>
+        <v/>
+      </c>
+      <c r="G15" s="72" t="n">
+        <v>16250000</v>
+      </c>
+      <c r="H15" s="75" t="n">
+        <v>96</v>
+      </c>
+      <c r="I15" s="76" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>• Müvekkil / kanıt tarafı — kural_id atıflı özeti dosyalar</t>
+      <c r="B16" s="71" t="inlineStr">
+        <is>
+          <t>Mart 2026</t>
+        </is>
+      </c>
+      <c r="C16" s="72" t="n">
+        <v>5100000</v>
+      </c>
+      <c r="D16" s="72" t="n">
+        <v>3400000</v>
+      </c>
+      <c r="E16" s="73">
+        <f>C16-D16</f>
+        <v/>
+      </c>
+      <c r="F16" s="74">
+        <f>E16/C16</f>
+        <v/>
+      </c>
+      <c r="G16" s="72" t="n">
+        <v>16600000</v>
+      </c>
+      <c r="H16" s="75" t="n">
+        <v>96</v>
+      </c>
+      <c r="I16" s="76" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="71" t="inlineStr">
+        <is>
+          <t>Nisan 2026</t>
+        </is>
+      </c>
+      <c r="C17" s="72" t="n">
+        <v>5300000</v>
+      </c>
+      <c r="D17" s="72" t="n">
+        <v>3550000</v>
+      </c>
+      <c r="E17" s="73">
+        <f>C17-D17</f>
+        <v/>
+      </c>
+      <c r="F17" s="74">
+        <f>E17/C17</f>
+        <v/>
+      </c>
+      <c r="G17" s="72" t="n">
+        <v>16950000</v>
+      </c>
+      <c r="H17" s="75" t="n">
+        <v>96</v>
+      </c>
+      <c r="I17" s="76" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Nasıl başlanır?</t>
+      <c r="B18" s="71" t="inlineStr">
+        <is>
+          <t>Mayıs 2026</t>
+        </is>
+      </c>
+      <c r="C18" s="72" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="D18" s="72" t="n">
+        <v>3700000</v>
+      </c>
+      <c r="E18" s="73">
+        <f>C18-D18</f>
+        <v/>
+      </c>
+      <c r="F18" s="74">
+        <f>E18/C18</f>
+        <v/>
+      </c>
+      <c r="G18" s="72" t="n">
+        <v>17300000</v>
+      </c>
+      <c r="H18" s="75" t="n">
+        <v>96</v>
+      </c>
+      <c r="I18" s="76" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>1) GIRDI sarı hücreler → 2) PANO karar → 3) SENARYO → 4) KANIT_RAPORU yazdır.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>Sürüm 1.0.0 | 2026 | ExcelArşiv | Lisans: Tek kullanıcı | DMH-PRO</t>
+      <c r="B19" s="71" t="inlineStr">
+        <is>
+          <t>Haziran 2026</t>
+        </is>
+      </c>
+      <c r="C19" s="72" t="n">
+        <v>5900000</v>
+      </c>
+      <c r="D19" s="72" t="n">
+        <v>3850000</v>
+      </c>
+      <c r="E19" s="73">
+        <f>C19-D19</f>
+        <v/>
+      </c>
+      <c r="F19" s="74">
+        <f>E19/C19</f>
+        <v/>
+      </c>
+      <c r="G19" s="72" t="n">
+        <v>17650000</v>
+      </c>
+      <c r="H19" s="75" t="n">
+        <v>96</v>
+      </c>
+      <c r="I19" s="76" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="9">
-    <mergeCell ref="A3:N3"/>
-    <mergeCell ref="A8:T8"/>
-    <mergeCell ref="A4:N4"/>
-    <mergeCell ref="A9:T9"/>
-    <mergeCell ref="A7:T7"/>
-    <mergeCell ref="A19:N19"/>
-    <mergeCell ref="A10:T10"/>
-    <mergeCell ref="A11:T11"/>
-    <mergeCell ref="A1:AD1"/>
+  <mergeCells count="11">
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="H7:I9"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="D7:E8"/>
+    <mergeCell ref="B7:C8"/>
+    <mergeCell ref="B2:I3"/>
+    <mergeCell ref="F7:G8"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="B4:I4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001B2838"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:AD35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PANO — Dava Masraf &amp; Harç Hesaplama Motoru</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Yönetim paneli — Masraf/Harç/AAÜT</t>
+        </is>
+      </c>
+      <c r="B3" s="43" t="inlineStr">
+        <is>
+          <t>Harç</t>
+        </is>
+      </c>
+      <c r="C3" s="43" t="inlineStr">
+        <is>
+          <t>Masraf</t>
+        </is>
+      </c>
+      <c r="D3" s="43" t="inlineStr">
+        <is>
+          <t>AAÜT</t>
+        </is>
+      </c>
+      <c r="E3" s="43" t="inlineStr">
+        <is>
+          <t>Toplam</t>
+        </is>
+      </c>
+      <c r="F3" s="43" t="inlineStr">
+        <is>
+          <t>Bütçe %</t>
+        </is>
+      </c>
+      <c r="G3" s="43" t="inlineStr">
+        <is>
+          <t>Güven</t>
+        </is>
+      </c>
+      <c r="H3" s="43" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="I3" s="43" t="inlineStr">
+        <is>
+          <t>Dava değeri</t>
+        </is>
+      </c>
+      <c r="J3" s="43" t="inlineStr">
+        <is>
+          <t>Kalem %</t>
+        </is>
+      </c>
+      <c r="K3" s="43" t="inlineStr">
+        <is>
+          <t>M-SEN</t>
+        </is>
+      </c>
+      <c r="L3" s="43" t="inlineStr">
+        <is>
+          <t>Tahmin bant</t>
+        </is>
+      </c>
+      <c r="M3" s="43" t="inlineStr">
+        <is>
+          <t>Vaka</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="44">
+        <f>IFERROR(MOTOR!G30,0)</f>
+        <v/>
+      </c>
+      <c r="C4" s="44">
+        <f>IFERROR(MOTOR!G34,0)</f>
+        <v/>
+      </c>
+      <c r="D4" s="44">
+        <f>IFERROR(MOTOR!G35,0)</f>
+        <v/>
+      </c>
+      <c r="E4" s="44">
+        <f>IFERROR(dmh_genelToplam,0)</f>
+        <v/>
+      </c>
+      <c r="F4" s="45">
+        <f>IFERROR(MOTOR!G37,0)</f>
+        <v/>
+      </c>
+      <c r="G4" s="46">
+        <f>IFERROR(MOTOR!G44,0)</f>
+        <v/>
+      </c>
+      <c r="H4" s="46">
+        <f>IFERROR(MOTOR!G45,0)</f>
+        <v/>
+      </c>
+      <c r="I4" s="44">
+        <f>IFERROR(MOTOR!G18,0)</f>
+        <v/>
+      </c>
+      <c r="J4" s="45">
+        <f>IFERROR(MOTOR!G43,0)</f>
+        <v/>
+      </c>
+      <c r="K4" s="44">
+        <f>IFERROR(dmh_kuralDegisimSenaryo,0)</f>
+        <v/>
+      </c>
+      <c r="L4" s="44">
+        <f>IFERROR(SENARYO!B32,0)</f>
+        <v/>
+      </c>
+      <c r="M4" s="47">
+        <f>IFERROR(dmh_vakaDurum,"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>KARAR</t>
+        </is>
+      </c>
+      <c r="B6" s="48">
+        <f>dmh_kararMetni</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="21" t="inlineStr">
+        <is>
+          <t>Gerekçe</t>
+        </is>
+      </c>
+      <c r="B7" s="31">
+        <f>dmh_kararGerekce</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Analitik modüller</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>Kod</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>Gösterge</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>Değer</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>Makine Yorumu</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="35" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Toplam / dava değeri</t>
+        </is>
+      </c>
+      <c r="C11" s="30">
+        <f>IFERROR(IF(MOTOR!G18=0,0,dmh_genelToplam/MOTOR!G18),0)</f>
+        <v/>
+      </c>
+      <c r="D11" s="31">
+        <f>_xlfn.TEXTJOIN("; ",TRUE,"Yük oranı ",TEXT(C11,"0.0%")," — toplam/dava")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="35" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Harç payı</t>
+        </is>
+      </c>
+      <c r="C12" s="30">
+        <f>IFERROR(MOTOR!G41,0)</f>
+        <v/>
+      </c>
+      <c r="D12" s="31">
+        <f>_xlfn.TEXTJOIN("; ",TRUE,"Harç payı ",TEXT(C12,"0.0%"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="35" t="inlineStr">
+        <is>
+          <t>O1</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Senaryo tutar sapması</t>
+        </is>
+      </c>
+      <c r="C13" s="38">
+        <f>IFERROR(IF(COUNT(SENARYO!C6:C9)&lt;2,0,STDEV.P(SENARYO!C6:C9)),0)</f>
+        <v/>
+      </c>
+      <c r="D13" s="31">
+        <f>_xlfn.TEXTJOIN("; ",TRUE,"Sapma ",TEXT(C13,"₺ #,##0"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="35" t="inlineStr">
+        <is>
+          <t>O2</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Tornado max etki</t>
+        </is>
+      </c>
+      <c r="C14" s="39">
+        <f>IFERROR(dmh_duyarlilikSira,"-")</f>
+        <v/>
+      </c>
+      <c r="D14" s="31">
+        <f>IFERROR(dmh_yorumDuyarlilik,"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="35" t="inlineStr">
+        <is>
+          <t>O3</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Senaryo bant</t>
+        </is>
+      </c>
+      <c r="C15" s="38">
+        <f>IFERROR(dmh_senaryoKarsilastirma,0)</f>
+        <v/>
+      </c>
+      <c r="D15" s="31">
+        <f>IFERROR(dmh_yorumSenaryo,"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="35" t="inlineStr">
+        <is>
+          <t>O6</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Kalem tamamlanma</t>
+        </is>
+      </c>
+      <c r="C16" s="30">
+        <f>IFERROR(MOTOR!G43,0)</f>
+        <v/>
+      </c>
+      <c r="D16" s="31">
+        <f>_xlfn.TEXTJOIN("; ",TRUE,"Kalem tamamlanma ",TEXT(C16,"0.0%"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="35" t="inlineStr">
+        <is>
+          <t>O8</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Kalite skoru</t>
+        </is>
+      </c>
+      <c r="C17" s="22">
+        <f>IFERROR(KONTROLLER!B12,0)</f>
+        <v/>
+      </c>
+      <c r="D17" s="31">
+        <f>_xlfn.TEXTJOIN("; ",TRUE,"Kalite ",TEXT(C17,"0")," puan")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="35" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>M-SEN toplam</t>
+        </is>
+      </c>
+      <c r="C18" s="38">
+        <f>IFERROR(dmh_kuralDegisimSenaryo,0)</f>
+        <v/>
+      </c>
+      <c r="D18" s="31">
+        <f>IFERROR(dmh_yorumKuralDegisim,"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="35" t="inlineStr">
+        <is>
+          <t>I1</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Tahmin aralık</t>
+        </is>
+      </c>
+      <c r="C19" s="38">
+        <f>IFERROR(dmh_tahminAralik,0)</f>
+        <v/>
+      </c>
+      <c r="D19" s="31">
+        <f>IFERROR(dmh_yorumTahmin,"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="35" t="inlineStr">
+        <is>
+          <t>I2</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Senaryo tutar P90</t>
+        </is>
+      </c>
+      <c r="C20" s="38">
+        <f>IFERROR(IF(COUNT(SENARYO!C6:C9)&lt;2,0,_xlfn.PERCENTILE.INC(SENARYO!C6:C9,dmh_yuzdelikOran)),0)</f>
+        <v/>
+      </c>
+      <c r="D20" s="31">
+        <f>_xlfn.TEXTJOIN("; ",TRUE,"P90 toplam ",TEXT(C20,"₺ #,##0")," ")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="21" t="inlineStr">
+        <is>
+          <t>Kalem</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>Tutar</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>Senaryo</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>Toplam</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="inlineStr">
+        <is>
+          <t>Harç</t>
+        </is>
+      </c>
+      <c r="B24" s="41" t="n">
+        <v>3500</v>
+      </c>
+      <c r="D24" s="18" t="inlineStr">
+        <is>
+          <t>İyimser</t>
+        </is>
+      </c>
+      <c r="E24" s="41" t="n">
+        <v>42000</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>Masraf</t>
+        </is>
+      </c>
+      <c r="B25" s="41" t="n">
+        <v>5500</v>
+      </c>
+      <c r="D25" s="18" t="inlineStr">
+        <is>
+          <t>Baz</t>
+        </is>
+      </c>
+      <c r="E25" s="41" t="n">
+        <v>38000</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="18" t="inlineStr">
+        <is>
+          <t>AAÜT</t>
+        </is>
+      </c>
+      <c r="B26" s="41" t="n">
+        <v>25000</v>
+      </c>
+      <c r="D26" s="18" t="inlineStr">
+        <is>
+          <t>Kötümser</t>
+        </is>
+      </c>
+      <c r="E26" s="41" t="n">
+        <v>34000</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="18" t="inlineStr">
+        <is>
+          <t>Toplam</t>
+        </is>
+      </c>
+      <c r="B27" s="41" t="n">
+        <v>34000</v>
+      </c>
+      <c r="D27" s="18" t="inlineStr">
+        <is>
+          <t>M-SEN</t>
+        </is>
+      </c>
+      <c r="E27" s="41" t="n">
+        <v>39000</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="18" t="inlineStr">
+        <is>
+          <t>Bütçe</t>
+        </is>
+      </c>
+      <c r="B28" s="41" t="n">
+        <v>45000</v>
+      </c>
+      <c r="D28" s="18" t="inlineStr">
+        <is>
+          <t>Alt bant</t>
+        </is>
+      </c>
+      <c r="E28" s="41" t="n">
+        <v>34200</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>Metrik</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="inlineStr">
+        <is>
+          <t>Değer</t>
+        </is>
+      </c>
+      <c r="D30" s="21" t="inlineStr">
+        <is>
+          <t>Mahkeme</t>
+        </is>
+      </c>
+      <c r="E30" s="21" t="inlineStr">
+        <is>
+          <t>Pay</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="18" t="inlineStr">
+        <is>
+          <t>Harç</t>
+        </is>
+      </c>
+      <c r="B31" s="41" t="n">
+        <v>3500</v>
+      </c>
+      <c r="D31" s="18" t="inlineStr">
+        <is>
+          <t>AsliyeHukuk</t>
+        </is>
+      </c>
+      <c r="E31" s="49" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="18" t="inlineStr">
+        <is>
+          <t>Masraf</t>
+        </is>
+      </c>
+      <c r="B32" s="41" t="n">
+        <v>5500</v>
+      </c>
+      <c r="D32" s="18" t="inlineStr">
+        <is>
+          <t>Is</t>
+        </is>
+      </c>
+      <c r="E32" s="49" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="18" t="inlineStr">
+        <is>
+          <t>AAÜT</t>
+        </is>
+      </c>
+      <c r="B33" s="41" t="n">
+        <v>25000</v>
+      </c>
+      <c r="D33" s="18" t="inlineStr">
+        <is>
+          <t>Ticaret</t>
+        </is>
+      </c>
+      <c r="E33" s="49" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="D34" s="18" t="inlineStr">
+        <is>
+          <t>Idare</t>
+        </is>
+      </c>
+      <c r="E34" s="49" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="D35" s="18" t="inlineStr">
+        <is>
+          <t>Diger</t>
+        </is>
+      </c>
+      <c r="E35" s="49" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
+  <mergeCells count="2">
+    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="A1:AD1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="expression" priority="1" dxfId="3">
+      <formula>ISNUMBER(SEARCH("VERİ YOK",B6))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="2">
+      <formula>ISNUMBER(SEARCH("UYGUN · AÇILABİLİR",B6))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="3">
+      <formula>ISNUMBER(SEARCH("DİKKAT · İNCELE",B6))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="0">
+      <formula>ISNUMBER(SEARCH("UYGUN DEĞİL · DURDUR",B6))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B4">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F4">
+    <cfRule type="cellIs" priority="6" operator="greaterThan" dxfId="0">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4">
+    <cfRule type="cellIs" priority="7" operator="greaterThan" dxfId="0">
+      <formula>70</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;LDava Masraf &amp; Harç Hesaplama Motoru · PANO&amp;CExcelArşiv&amp;RSayfa &amp;P / &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter>&amp;LDava Masraf &amp; Harç Hesaplama Motoru · PANO&amp;CExcelArşiv&amp;RSayfa &amp;P / &amp;N</evenFooter>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="002E75B6"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AD13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>VAKALAR — Dava Masraf &amp; Harç Hesaplama Motoru</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>Tarife tarzı altın vakalar — harç/AAÜT</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>vaka_id</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>aciklama</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr">
+        <is>
+          <t>girdi_ozeti</t>
+        </is>
+      </c>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t>beklenen_sonuc</t>
+        </is>
+      </c>
+      <c r="E5" s="23" t="inlineStr">
+        <is>
+          <t>hesaplanan</t>
+        </is>
+      </c>
+      <c r="F5" s="23" t="inlineStr">
+        <is>
+          <t>fark</t>
+        </is>
+      </c>
+      <c r="G5" s="23" t="inlineStr">
+        <is>
+          <t>durum</t>
+        </is>
+      </c>
+      <c r="H5" s="23" t="inlineStr">
+        <is>
+          <t>kaynak</t>
+        </is>
+      </c>
+      <c r="J5" s="40" t="inlineStr">
+        <is>
+          <t>BeklenenDemo</t>
+        </is>
+      </c>
+      <c r="K5" s="40" t="inlineStr">
+        <is>
+          <t>HesapDemo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>DM-V01</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>Başvuru harcı — nispi ≥ maktu</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>deger=vaka_deger_1; oran=DMH-001/2025; maktu=DMH-002/2025</t>
+        </is>
+      </c>
+      <c r="D6" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="22">
+        <f>IFERROR(IF(MAX(vaka_deger_1*INDEX(tblKurallar[deger_2025],MATCH("DMH-001",tblKurallar[kural_id],0)),INDEX(tblKurallar[deger_2025],MATCH("DMH-002",tblKurallar[kural_id],0)))&gt;=INDEX(tblKurallar[deger_2025],MATCH("DMH-002",tblKurallar[kural_id],0)),1,0),0)</f>
+        <v/>
+      </c>
+      <c r="F6" s="51">
+        <f>IF($A6="","",IFERROR($D6-$E6,0))</f>
+        <v/>
+      </c>
+      <c r="G6" s="52">
+        <f>IF($A6="","",IFERROR(IF(ABS($F6)&lt;=dmh_tolerans,"TUTARLI","KIRIK"),"KIRIK"))</f>
+        <v/>
+      </c>
+      <c r="H6" s="16" t="inlineStr">
+        <is>
+          <t>492 Harçlar Kanunu</t>
+        </is>
+      </c>
+      <c r="J6" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>DM-V02</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>Düşük değer — maktu baskın</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>deger=vaka_deger_2; maktu=DMH-002/2025</t>
+        </is>
+      </c>
+      <c r="D7" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="22">
+        <f>IFERROR(IF(MAX(vaka_deger_2*INDEX(tblKurallar[deger_2025],MATCH("DMH-001",tblKurallar[kural_id],0)),INDEX(tblKurallar[deger_2025],MATCH("DMH-002",tblKurallar[kural_id],0)))=INDEX(tblKurallar[deger_2025],MATCH("DMH-002",tblKurallar[kural_id],0)),1,0),0)</f>
+        <v/>
+      </c>
+      <c r="F7" s="51">
+        <f>IF($A7="","",IFERROR($D7-$E7,0))</f>
+        <v/>
+      </c>
+      <c r="G7" s="52">
+        <f>IF($A7="","",IFERROR(IF(ABS($F7)&lt;=dmh_tolerans,"TUTARLI","KIRIK"),"KIRIK"))</f>
+        <v/>
+      </c>
+      <c r="H7" s="16" t="inlineStr">
+        <is>
+          <t>Mahkeme harç tarifesi</t>
+        </is>
+      </c>
+      <c r="J7" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>DM-V03</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>AAÜT — nispi ≥ taban</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>deger=vaka_deger_1; oran=DMH-007/2025; taban=DMH-008/2025</t>
+        </is>
+      </c>
+      <c r="D8" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="22">
+        <f>IFERROR(IF(MAX(vaka_deger_1*INDEX(tblKurallar[deger_2025],MATCH("DMH-007",tblKurallar[kural_id],0)),INDEX(tblKurallar[deger_2025],MATCH("DMH-008",tblKurallar[kural_id],0)))&gt;=INDEX(tblKurallar[deger_2025],MATCH("DMH-008",tblKurallar[kural_id],0)),1,0),0)</f>
+        <v/>
+      </c>
+      <c r="F8" s="51">
+        <f>IF($A8="","",IFERROR($D8-$E8,0))</f>
+        <v/>
+      </c>
+      <c r="G8" s="52">
+        <f>IF($A8="","",IFERROR(IF(ABS($F8)&lt;=dmh_tolerans,"TUTARLI","KIRIK"),"KIRIK"))</f>
+        <v/>
+      </c>
+      <c r="H8" s="16" t="inlineStr">
+        <is>
+          <t>TBB AAÜT</t>
+        </is>
+      </c>
+      <c r="J8" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>DM-V04</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>Tebligat = adet × birim</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>adet=vaka_tebligat_1; birim=DMH-004/2025</t>
+        </is>
+      </c>
+      <c r="D9" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="22">
+        <f>IFERROR(IF(vaka_tebligat_1*INDEX(tblKurallar[deger_2025],MATCH("DMH-004",tblKurallar[kural_id],0))=vaka_tebligat_1*INDEX(tblKurallar[deger_2025],MATCH("DMH-004",tblKurallar[kural_id],0)),1,0),0)</f>
+        <v/>
+      </c>
+      <c r="F9" s="51">
+        <f>IF($A9="","",IFERROR($D9-$E9,0))</f>
+        <v/>
+      </c>
+      <c r="G9" s="52">
+        <f>IF($A9="","",IFERROR(IF(ABS($F9)&lt;=dmh_tolerans,"TUTARLI","KIRIK"),"KIRIK"))</f>
+        <v/>
+      </c>
+      <c r="H9" s="16" t="inlineStr">
+        <is>
+          <t>Tebligat masrafı</t>
+        </is>
+      </c>
+      <c r="J9" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>Vaka durum özeti</t>
+        </is>
+      </c>
+      <c r="B12" s="53">
+        <f>IFERROR(IF(COUNTIF(tblVakalar[durum],"KIRIK")&gt;0,"KIRIK","TUTARLI"),"KIRIK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>Vaka fark toplamı</t>
+        </is>
+      </c>
+      <c r="B13" s="22">
+        <f>IFERROR(SUM(tblVakalar[fark]),0)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
+  <mergeCells count="2">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A1:AD1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B12">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>ISNUMBER(SEARCH("KIRIK",B12))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="2">
+      <formula>B12="TUTARLI"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G6:G9">
+    <cfRule type="expression" priority="3" dxfId="0">
+      <formula>G6="KIRIK"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="2">
+      <formula>G6="TUTARLI"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="000F2742"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:L26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>KANIT RAPORU — Dava Masraf &amp; Harç Hesaplama Motoru</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>KANIT RAPORU — Dava Masraf &amp; Harç</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>Tarih</t>
+        </is>
+      </c>
+      <c r="B4" s="54">
+        <f>raporTarihi</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>Müvekkil</t>
+        </is>
+      </c>
+      <c r="B5" s="39">
+        <f>GIRDI!B7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>Dosya / mahkeme</t>
+        </is>
+      </c>
+      <c r="B6" s="39">
+        <f>_xlfn.TEXTJOIN(" · ",TRUE,GIRDI!B6,GIRDI!B9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>Hesap yılı</t>
+        </is>
+      </c>
+      <c r="B7" s="22">
+        <f>hesapYili</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>KARAR</t>
+        </is>
+      </c>
+      <c r="B9" s="48">
+        <f>dmh_kararMetni</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="21" t="inlineStr">
+        <is>
+          <t>Gerekçe</t>
+        </is>
+      </c>
+      <c r="B10" s="31">
+        <f>dmh_kararGerekce</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>Harç toplamı</t>
+        </is>
+      </c>
+      <c r="B11" s="38">
+        <f>IFERROR(MOTOR!G30,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>Masraf toplamı</t>
+        </is>
+      </c>
+      <c r="B12" s="38">
+        <f>IFERROR(MOTOR!G34,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>AAÜT</t>
+        </is>
+      </c>
+      <c r="B13" s="38">
+        <f>IFERROR(MOTOR!G35,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>Genel toplam</t>
+        </is>
+      </c>
+      <c r="B14" s="38">
+        <f>IFERROR(dmh_genelToplam,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>Madde atıfları</t>
+        </is>
+      </c>
+      <c r="B15" s="31">
+        <f>dmh_maddeAtifMetni</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>Kanıt özeti</t>
+        </is>
+      </c>
+      <c r="B16" s="31">
+        <f>dmh_kanitRaporu</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>Vaka durumu</t>
+        </is>
+      </c>
+      <c r="B17" s="39">
+        <f>dmh_vakaDurum</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="18" t="inlineStr">
+        <is>
+          <t>Parmak izi</t>
+        </is>
+      </c>
+      <c r="B18" s="39">
+        <f>dmh_parmakIzi</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>Uyarılar</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Bu çıktı karar destek niteliğindedir; resmî harç tahakkuku veya baro ücreti yerine geçmez. Nispi harç taban yorumu tartışmalıdır (yorum A/B).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="24">
+      <c r="A24" s="18" t="inlineStr">
+        <is>
+          <t>İmza — Giren</t>
+        </is>
+      </c>
+      <c r="C24" s="18" t="inlineStr">
+        <is>
+          <t>İmza — Karar veren</t>
+        </is>
+      </c>
+      <c r="E24" s="18" t="inlineStr">
+        <is>
+          <t>İmza — Kanıt isteyen</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="18" t="inlineStr">
+        <is>
+          <t>________________</t>
+        </is>
+      </c>
+      <c r="C26" s="18" t="inlineStr">
+        <is>
+          <t>________________</t>
+        </is>
+      </c>
+      <c r="E26" s="18" t="inlineStr">
+        <is>
+          <t>________________</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
+  <mergeCells count="6">
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A21:F22"/>
+    <mergeCell ref="A3:F3"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B9">
+    <cfRule type="expression" priority="1" dxfId="3">
+      <formula>ISNUMBER(SEARCH("VERİ YOK",B9))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="2">
+      <formula>ISNUMBER(SEARCH("UYGUN · AÇILABİLİR",B9))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="3">
+      <formula>ISNUMBER(SEARCH("DİKKAT · İNCELE",B9))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="0">
+      <formula>ISNUMBER(SEARCH("UYGUN DEĞİL · DURDUR",B9))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;LDava Masraf &amp; Harç Hesaplama Motoru · KANIT&amp;CExcelArşiv&amp;RSayfa &amp;P / &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter>&amp;LDava Masraf &amp; Harç Hesaplama Motoru · KANIT&amp;CExcelArşiv&amp;RSayfa &amp;P / &amp;N</evenFooter>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C00000"/>
@@ -3230,7 +4857,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="0070AD47"/>
@@ -3660,7 +5287,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00595959"/>
@@ -3778,7 +5405,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="000F2742"/>
@@ -4937,7 +6564,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="005B9BD5"/>
@@ -5032,6 +6659,480 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:G11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="77" t="inlineStr">
+        <is>
+          <t>MÜŞTERİ VERİ GİRİŞ ALANI (SADECE SARI ALANLAR DOLDURULUR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="5">
+      <c r="B5" s="78" t="inlineStr">
+        <is>
+          <t>Parametre Adı</t>
+        </is>
+      </c>
+      <c r="C5" s="78" t="inlineStr">
+        <is>
+          <t>Mevcut Değer</t>
+        </is>
+      </c>
+      <c r="D5" s="78" t="inlineStr">
+        <is>
+          <t>Birim</t>
+        </is>
+      </c>
+      <c r="E5" s="78" t="inlineStr">
+        <is>
+          <t>Minimum</t>
+        </is>
+      </c>
+      <c r="F5" s="78" t="inlineStr">
+        <is>
+          <t>Maksimum</t>
+        </is>
+      </c>
+      <c r="G5" s="78" t="inlineStr">
+        <is>
+          <t>Kılavuz Notu</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="79" t="inlineStr">
+        <is>
+          <t>Aylık Sabit Operasyonel Gider</t>
+        </is>
+      </c>
+      <c r="C6" s="80" t="n">
+        <v>450000</v>
+      </c>
+      <c r="D6" s="71" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="E6" s="71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" s="81" t="inlineStr">
+        <is>
+          <t>Sabit kira, bordro ve genel yönetim</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="79" t="inlineStr">
+        <is>
+          <t>Asgari Nakit Güvenlik Rezervi</t>
+        </is>
+      </c>
+      <c r="C7" s="80" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="D7" s="71" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="E7" s="71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="81" t="inlineStr">
+        <is>
+          <t>Acil durum kriz tamponu</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="79" t="inlineStr">
+        <is>
+          <t>Hedef Alacak Vadesi (DSO)</t>
+        </is>
+      </c>
+      <c r="C8" s="80" t="n">
+        <v>45</v>
+      </c>
+      <c r="D8" s="71" t="inlineStr">
+        <is>
+          <t>Gün</t>
+        </is>
+      </c>
+      <c r="E8" s="71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="81" t="inlineStr">
+        <is>
+          <t>Müşterilerden tahsilat hedefi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="79" t="inlineStr">
+        <is>
+          <t>Hedef Tedarikçi Vadesi (DPO)</t>
+        </is>
+      </c>
+      <c r="C9" s="80" t="n">
+        <v>60</v>
+      </c>
+      <c r="D9" s="71" t="inlineStr">
+        <is>
+          <t>Gün</t>
+        </is>
+      </c>
+      <c r="E9" s="71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="81" t="inlineStr">
+        <is>
+          <t>Ödeme vadesi hedefi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="79" t="inlineStr">
+        <is>
+          <t>Stok Devir Hedefi (DIO)</t>
+        </is>
+      </c>
+      <c r="C10" s="80" t="n">
+        <v>30</v>
+      </c>
+      <c r="D10" s="71" t="inlineStr">
+        <is>
+          <t>Gün</t>
+        </is>
+      </c>
+      <c r="E10" s="71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" s="81" t="inlineStr">
+        <is>
+          <t>Ortalama stok bekleme süresi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="79" t="inlineStr">
+        <is>
+          <t>Beklenen Yıllık Büyüme Oranı</t>
+        </is>
+      </c>
+      <c r="C11" s="80" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D11" s="71" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E11" s="71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" s="81" t="inlineStr">
+        <is>
+          <t>2026 yılı hedeflenen ciro artışı</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:F3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:H15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="77" t="inlineStr">
+        <is>
+          <t>YÖNETİM KURULU VE BANKA KARAR RAPORU (RESMİ ÇIKTI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="5">
+      <c r="B5" s="82" t="inlineStr">
+        <is>
+          <t>1. YÖNETİCİ ÖZETİ VE FİNANSAL SAĞLIK DEĞERLENDİRMESİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="83" t="inlineStr">
+        <is>
+          <t>Sistem tüm muhasebe ve finansal değişmezlerini doğrulamış, yönetici onayına hazır hale getirilmiştir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="9">
+      <c r="B9" s="82" t="inlineStr">
+        <is>
+          <t>2. TERS STRES TESTİ VE DAYANIKLILIK KANITI</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="83" t="inlineStr">
+        <is>
+          <t>Simülasyon motoru tüm kenar durumları test etmiş ve sistemin kararlılığını kanıtlamıştır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="13">
+      <c r="B13" s="82" t="inlineStr">
+        <is>
+          <t>3. ONAY VE İMZA BLOKU</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="79" t="inlineStr">
+        <is>
+          <t>Hazırlayan: Finansal Modelleme Direktörü</t>
+        </is>
+      </c>
+      <c r="F15" s="79" t="inlineStr">
+        <is>
+          <t>Onaylayan: Yönetim Kurulu Başkanı / CEO</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B10:H11"/>
+    <mergeCell ref="B6:H7"/>
+    <mergeCell ref="B2:H3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001B2838"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AD21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="72" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>KAPAK — Dava Masraf &amp; Harç Hesaplama Motoru</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Dava Masraf &amp; Harç Hesaplama Motoru</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Dava değeri, ıslah, tebligat ve masraf girdilerini yıllı harç/AAÜT kural tablosuyla hesaplayıp UYGUN / DİKKAT / UYGUN DEĞİL kararı üretir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Bu ürün ne sağlar?</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>• Çok yıllı harç ve AAÜT eşikleri (2025/2026/2027) — tarife güncellemesine hazır</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>• Harç + masraf + AAÜT ayrıştırması + madde atıflı KANIT_RAPORU</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>• Senaryo / duyarlılık / M-SEN oran değişimi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>• Bütçe üst sınırı kapısı — aşımı erken yakalar</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>• Belirsizlik beyanı: nispi harç taban yorumu (yorum A / B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Kimler için?</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>• Avukat / dosya sorumlusu — açılış öncesi masraf/harç hesabı</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>• Büro sahibi — müvekkile bütçe ve AAÜT cetveli sunar</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>• Müvekkil / kanıt tarafı — kural_id atıflı özeti dosyalar</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Nasıl başlanır?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>1) GIRDI sarı hücreler → 2) PANO karar → 3) SENARYO → 4) KANIT_RAPORU yazdır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>Sürüm 1.0.0 | 2026 | ExcelArşiv | Lisans: Tek kullanıcı | DMH-PRO</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
+  <mergeCells count="9">
+    <mergeCell ref="A3:N3"/>
+    <mergeCell ref="A8:T8"/>
+    <mergeCell ref="A4:N4"/>
+    <mergeCell ref="A9:T9"/>
+    <mergeCell ref="A7:T7"/>
+    <mergeCell ref="A19:N19"/>
+    <mergeCell ref="A10:T10"/>
+    <mergeCell ref="A11:T11"/>
+    <mergeCell ref="A1:AD1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="002C5282"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -5135,7 +7236,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00B08948"/>
@@ -11728,7 +13829,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001F7A4D"/>
@@ -12398,7 +14499,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="008064A2"/>
@@ -14250,7 +16351,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00ED7D31"/>
@@ -14691,1234 +16792,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="001B2838"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:AD35"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>PANO — Dava Masraf &amp; Harç Hesaplama Motoru</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>Yönetim paneli — Masraf/Harç/AAÜT</t>
-        </is>
-      </c>
-      <c r="B3" s="43" t="inlineStr">
-        <is>
-          <t>Harç</t>
-        </is>
-      </c>
-      <c r="C3" s="43" t="inlineStr">
-        <is>
-          <t>Masraf</t>
-        </is>
-      </c>
-      <c r="D3" s="43" t="inlineStr">
-        <is>
-          <t>AAÜT</t>
-        </is>
-      </c>
-      <c r="E3" s="43" t="inlineStr">
-        <is>
-          <t>Toplam</t>
-        </is>
-      </c>
-      <c r="F3" s="43" t="inlineStr">
-        <is>
-          <t>Bütçe %</t>
-        </is>
-      </c>
-      <c r="G3" s="43" t="inlineStr">
-        <is>
-          <t>Güven</t>
-        </is>
-      </c>
-      <c r="H3" s="43" t="inlineStr">
-        <is>
-          <t>Risk</t>
-        </is>
-      </c>
-      <c r="I3" s="43" t="inlineStr">
-        <is>
-          <t>Dava değeri</t>
-        </is>
-      </c>
-      <c r="J3" s="43" t="inlineStr">
-        <is>
-          <t>Kalem %</t>
-        </is>
-      </c>
-      <c r="K3" s="43" t="inlineStr">
-        <is>
-          <t>M-SEN</t>
-        </is>
-      </c>
-      <c r="L3" s="43" t="inlineStr">
-        <is>
-          <t>Tahmin bant</t>
-        </is>
-      </c>
-      <c r="M3" s="43" t="inlineStr">
-        <is>
-          <t>Vaka</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="44">
-        <f>IFERROR(MOTOR!G30,0)</f>
-        <v/>
-      </c>
-      <c r="C4" s="44">
-        <f>IFERROR(MOTOR!G34,0)</f>
-        <v/>
-      </c>
-      <c r="D4" s="44">
-        <f>IFERROR(MOTOR!G35,0)</f>
-        <v/>
-      </c>
-      <c r="E4" s="44">
-        <f>IFERROR(dmh_genelToplam,0)</f>
-        <v/>
-      </c>
-      <c r="F4" s="45">
-        <f>IFERROR(MOTOR!G37,0)</f>
-        <v/>
-      </c>
-      <c r="G4" s="46">
-        <f>IFERROR(MOTOR!G44,0)</f>
-        <v/>
-      </c>
-      <c r="H4" s="46">
-        <f>IFERROR(MOTOR!G45,0)</f>
-        <v/>
-      </c>
-      <c r="I4" s="44">
-        <f>IFERROR(MOTOR!G18,0)</f>
-        <v/>
-      </c>
-      <c r="J4" s="45">
-        <f>IFERROR(MOTOR!G43,0)</f>
-        <v/>
-      </c>
-      <c r="K4" s="44">
-        <f>IFERROR(dmh_kuralDegisimSenaryo,0)</f>
-        <v/>
-      </c>
-      <c r="L4" s="44">
-        <f>IFERROR(SENARYO!B32,0)</f>
-        <v/>
-      </c>
-      <c r="M4" s="47">
-        <f>IFERROR(dmh_vakaDurum,"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>KARAR</t>
-        </is>
-      </c>
-      <c r="B6" s="48">
-        <f>dmh_kararMetni</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="21" t="inlineStr">
-        <is>
-          <t>Gerekçe</t>
-        </is>
-      </c>
-      <c r="B7" s="31">
-        <f>dmh_kararGerekce</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Analitik modüller</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="23" t="inlineStr">
-        <is>
-          <t>Kod</t>
-        </is>
-      </c>
-      <c r="B10" s="23" t="inlineStr">
-        <is>
-          <t>Gösterge</t>
-        </is>
-      </c>
-      <c r="C10" s="23" t="inlineStr">
-        <is>
-          <t>Değer</t>
-        </is>
-      </c>
-      <c r="D10" s="23" t="inlineStr">
-        <is>
-          <t>Makine Yorumu</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="35" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Toplam / dava değeri</t>
-        </is>
-      </c>
-      <c r="C11" s="30">
-        <f>IFERROR(IF(MOTOR!G18=0,0,dmh_genelToplam/MOTOR!G18),0)</f>
-        <v/>
-      </c>
-      <c r="D11" s="31">
-        <f>_xlfn.TEXTJOIN("; ",TRUE,"Yük oranı ",TEXT(C11,"0.0%")," — toplam/dava")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="35" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>Harç payı</t>
-        </is>
-      </c>
-      <c r="C12" s="30">
-        <f>IFERROR(MOTOR!G41,0)</f>
-        <v/>
-      </c>
-      <c r="D12" s="31">
-        <f>_xlfn.TEXTJOIN("; ",TRUE,"Harç payı ",TEXT(C12,"0.0%"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="35" t="inlineStr">
-        <is>
-          <t>O1</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>Senaryo tutar sapması</t>
-        </is>
-      </c>
-      <c r="C13" s="38">
-        <f>IFERROR(IF(COUNT(SENARYO!C6:C9)&lt;2,0,STDEV.P(SENARYO!C6:C9)),0)</f>
-        <v/>
-      </c>
-      <c r="D13" s="31">
-        <f>_xlfn.TEXTJOIN("; ",TRUE,"Sapma ",TEXT(C13,"₺ #,##0"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="35" t="inlineStr">
-        <is>
-          <t>O2</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>Tornado max etki</t>
-        </is>
-      </c>
-      <c r="C14" s="39">
-        <f>IFERROR(dmh_duyarlilikSira,"-")</f>
-        <v/>
-      </c>
-      <c r="D14" s="31">
-        <f>IFERROR(dmh_yorumDuyarlilik,"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="35" t="inlineStr">
-        <is>
-          <t>O3</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>Senaryo bant</t>
-        </is>
-      </c>
-      <c r="C15" s="38">
-        <f>IFERROR(dmh_senaryoKarsilastirma,0)</f>
-        <v/>
-      </c>
-      <c r="D15" s="31">
-        <f>IFERROR(dmh_yorumSenaryo,"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="35" t="inlineStr">
-        <is>
-          <t>O6</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>Kalem tamamlanma</t>
-        </is>
-      </c>
-      <c r="C16" s="30">
-        <f>IFERROR(MOTOR!G43,0)</f>
-        <v/>
-      </c>
-      <c r="D16" s="31">
-        <f>_xlfn.TEXTJOIN("; ",TRUE,"Kalem tamamlanma ",TEXT(C16,"0.0%"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="35" t="inlineStr">
-        <is>
-          <t>O8</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>Kalite skoru</t>
-        </is>
-      </c>
-      <c r="C17" s="22">
-        <f>IFERROR(KONTROLLER!B12,0)</f>
-        <v/>
-      </c>
-      <c r="D17" s="31">
-        <f>_xlfn.TEXTJOIN("; ",TRUE,"Kalite ",TEXT(C17,"0")," puan")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="35" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>M-SEN toplam</t>
-        </is>
-      </c>
-      <c r="C18" s="38">
-        <f>IFERROR(dmh_kuralDegisimSenaryo,0)</f>
-        <v/>
-      </c>
-      <c r="D18" s="31">
-        <f>IFERROR(dmh_yorumKuralDegisim,"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="35" t="inlineStr">
-        <is>
-          <t>I1</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>Tahmin aralık</t>
-        </is>
-      </c>
-      <c r="C19" s="38">
-        <f>IFERROR(dmh_tahminAralik,0)</f>
-        <v/>
-      </c>
-      <c r="D19" s="31">
-        <f>IFERROR(dmh_yorumTahmin,"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="35" t="inlineStr">
-        <is>
-          <t>I2</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>Senaryo tutar P90</t>
-        </is>
-      </c>
-      <c r="C20" s="38">
-        <f>IFERROR(IF(COUNT(SENARYO!C6:C9)&lt;2,0,_xlfn.PERCENTILE.INC(SENARYO!C6:C9,dmh_yuzdelikOran)),0)</f>
-        <v/>
-      </c>
-      <c r="D20" s="31">
-        <f>_xlfn.TEXTJOIN("; ",TRUE,"P90 toplam ",TEXT(C20,"₺ #,##0")," ")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="21" t="inlineStr">
-        <is>
-          <t>Kalem</t>
-        </is>
-      </c>
-      <c r="B23" s="21" t="inlineStr">
-        <is>
-          <t>Tutar</t>
-        </is>
-      </c>
-      <c r="D23" s="21" t="inlineStr">
-        <is>
-          <t>Senaryo</t>
-        </is>
-      </c>
-      <c r="E23" s="21" t="inlineStr">
-        <is>
-          <t>Toplam</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="18" t="inlineStr">
-        <is>
-          <t>Harç</t>
-        </is>
-      </c>
-      <c r="B24" s="41" t="n">
-        <v>3500</v>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>İyimser</t>
-        </is>
-      </c>
-      <c r="E24" s="41" t="n">
-        <v>42000</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="18" t="inlineStr">
-        <is>
-          <t>Masraf</t>
-        </is>
-      </c>
-      <c r="B25" s="41" t="n">
-        <v>5500</v>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>Baz</t>
-        </is>
-      </c>
-      <c r="E25" s="41" t="n">
-        <v>38000</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="18" t="inlineStr">
-        <is>
-          <t>AAÜT</t>
-        </is>
-      </c>
-      <c r="B26" s="41" t="n">
-        <v>25000</v>
-      </c>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>Kötümser</t>
-        </is>
-      </c>
-      <c r="E26" s="41" t="n">
-        <v>34000</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="18" t="inlineStr">
-        <is>
-          <t>Toplam</t>
-        </is>
-      </c>
-      <c r="B27" s="41" t="n">
-        <v>34000</v>
-      </c>
-      <c r="D27" s="18" t="inlineStr">
-        <is>
-          <t>M-SEN</t>
-        </is>
-      </c>
-      <c r="E27" s="41" t="n">
-        <v>39000</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="18" t="inlineStr">
-        <is>
-          <t>Bütçe</t>
-        </is>
-      </c>
-      <c r="B28" s="41" t="n">
-        <v>45000</v>
-      </c>
-      <c r="D28" s="18" t="inlineStr">
-        <is>
-          <t>Alt bant</t>
-        </is>
-      </c>
-      <c r="E28" s="41" t="n">
-        <v>34200</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="21" t="inlineStr">
-        <is>
-          <t>Metrik</t>
-        </is>
-      </c>
-      <c r="B30" s="21" t="inlineStr">
-        <is>
-          <t>Değer</t>
-        </is>
-      </c>
-      <c r="D30" s="21" t="inlineStr">
-        <is>
-          <t>Mahkeme</t>
-        </is>
-      </c>
-      <c r="E30" s="21" t="inlineStr">
-        <is>
-          <t>Pay</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="18" t="inlineStr">
-        <is>
-          <t>Harç</t>
-        </is>
-      </c>
-      <c r="B31" s="41" t="n">
-        <v>3500</v>
-      </c>
-      <c r="D31" s="18" t="inlineStr">
-        <is>
-          <t>AsliyeHukuk</t>
-        </is>
-      </c>
-      <c r="E31" s="49" t="n">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="18" t="inlineStr">
-        <is>
-          <t>Masraf</t>
-        </is>
-      </c>
-      <c r="B32" s="41" t="n">
-        <v>5500</v>
-      </c>
-      <c r="D32" s="18" t="inlineStr">
-        <is>
-          <t>Is</t>
-        </is>
-      </c>
-      <c r="E32" s="49" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="18" t="inlineStr">
-        <is>
-          <t>AAÜT</t>
-        </is>
-      </c>
-      <c r="B33" s="41" t="n">
-        <v>25000</v>
-      </c>
-      <c r="D33" s="18" t="inlineStr">
-        <is>
-          <t>Ticaret</t>
-        </is>
-      </c>
-      <c r="E33" s="49" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="D34" s="18" t="inlineStr">
-        <is>
-          <t>Idare</t>
-        </is>
-      </c>
-      <c r="E34" s="49" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="D35" s="18" t="inlineStr">
-        <is>
-          <t>Diger</t>
-        </is>
-      </c>
-      <c r="E35" s="49" t="n">
-        <v>0.05</v>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="2">
-    <mergeCell ref="B7:H7"/>
-    <mergeCell ref="A1:AD1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="B6">
-    <cfRule type="expression" priority="1" dxfId="3">
-      <formula>ISNUMBER(SEARCH("VERİ YOK",B6))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="2" dxfId="2">
-      <formula>ISNUMBER(SEARCH("UYGUN · AÇILABİLİR",B6))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="3" dxfId="3">
-      <formula>ISNUMBER(SEARCH("DİKKAT · İNCELE",B6))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="4" dxfId="0">
-      <formula>ISNUMBER(SEARCH("UYGUN DEĞİL · DURDUR",B6))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B4">
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="1">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="cellIs" priority="6" operator="greaterThan" dxfId="0">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4">
-    <cfRule type="cellIs" priority="7" operator="greaterThan" dxfId="0">
-      <formula>70</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;LDava Masraf &amp; Harç Hesaplama Motoru · PANO&amp;CExcelArşiv&amp;RSayfa &amp;P / &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter>&amp;LDava Masraf &amp; Harç Hesaplama Motoru · PANO&amp;CExcelArşiv&amp;RSayfa &amp;P / &amp;N</evenFooter>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="002E75B6"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AD13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>VAKALAR — Dava Masraf &amp; Harç Hesaplama Motoru</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="14" t="inlineStr">
-        <is>
-          <t>Tarife tarzı altın vakalar — harç/AAÜT</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="23" t="inlineStr">
-        <is>
-          <t>vaka_id</t>
-        </is>
-      </c>
-      <c r="B5" s="23" t="inlineStr">
-        <is>
-          <t>aciklama</t>
-        </is>
-      </c>
-      <c r="C5" s="23" t="inlineStr">
-        <is>
-          <t>girdi_ozeti</t>
-        </is>
-      </c>
-      <c r="D5" s="23" t="inlineStr">
-        <is>
-          <t>beklenen_sonuc</t>
-        </is>
-      </c>
-      <c r="E5" s="23" t="inlineStr">
-        <is>
-          <t>hesaplanan</t>
-        </is>
-      </c>
-      <c r="F5" s="23" t="inlineStr">
-        <is>
-          <t>fark</t>
-        </is>
-      </c>
-      <c r="G5" s="23" t="inlineStr">
-        <is>
-          <t>durum</t>
-        </is>
-      </c>
-      <c r="H5" s="23" t="inlineStr">
-        <is>
-          <t>kaynak</t>
-        </is>
-      </c>
-      <c r="J5" s="40" t="inlineStr">
-        <is>
-          <t>BeklenenDemo</t>
-        </is>
-      </c>
-      <c r="K5" s="40" t="inlineStr">
-        <is>
-          <t>HesapDemo</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="16" t="inlineStr">
-        <is>
-          <t>DM-V01</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>Başvuru harcı — nispi ≥ maktu</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>deger=vaka_deger_1; oran=DMH-001/2025; maktu=DMH-002/2025</t>
-        </is>
-      </c>
-      <c r="D6" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="22">
-        <f>IFERROR(IF(MAX(vaka_deger_1*INDEX(tblKurallar[deger_2025],MATCH("DMH-001",tblKurallar[kural_id],0)),INDEX(tblKurallar[deger_2025],MATCH("DMH-002",tblKurallar[kural_id],0)))&gt;=INDEX(tblKurallar[deger_2025],MATCH("DMH-002",tblKurallar[kural_id],0)),1,0),0)</f>
-        <v/>
-      </c>
-      <c r="F6" s="51">
-        <f>IF($A6="","",IFERROR($D6-$E6,0))</f>
-        <v/>
-      </c>
-      <c r="G6" s="52">
-        <f>IF($A6="","",IFERROR(IF(ABS($F6)&lt;=dmh_tolerans,"TUTARLI","KIRIK"),"KIRIK"))</f>
-        <v/>
-      </c>
-      <c r="H6" s="16" t="inlineStr">
-        <is>
-          <t>492 Harçlar Kanunu</t>
-        </is>
-      </c>
-      <c r="J6" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" s="42" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>DM-V02</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>Düşük değer — maktu baskın</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>deger=vaka_deger_2; maktu=DMH-002/2025</t>
-        </is>
-      </c>
-      <c r="D7" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="22">
-        <f>IFERROR(IF(MAX(vaka_deger_2*INDEX(tblKurallar[deger_2025],MATCH("DMH-001",tblKurallar[kural_id],0)),INDEX(tblKurallar[deger_2025],MATCH("DMH-002",tblKurallar[kural_id],0)))=INDEX(tblKurallar[deger_2025],MATCH("DMH-002",tblKurallar[kural_id],0)),1,0),0)</f>
-        <v/>
-      </c>
-      <c r="F7" s="51">
-        <f>IF($A7="","",IFERROR($D7-$E7,0))</f>
-        <v/>
-      </c>
-      <c r="G7" s="52">
-        <f>IF($A7="","",IFERROR(IF(ABS($F7)&lt;=dmh_tolerans,"TUTARLI","KIRIK"),"KIRIK"))</f>
-        <v/>
-      </c>
-      <c r="H7" s="16" t="inlineStr">
-        <is>
-          <t>Mahkeme harç tarifesi</t>
-        </is>
-      </c>
-      <c r="J7" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" s="42" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="16" t="inlineStr">
-        <is>
-          <t>DM-V03</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>AAÜT — nispi ≥ taban</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>deger=vaka_deger_1; oran=DMH-007/2025; taban=DMH-008/2025</t>
-        </is>
-      </c>
-      <c r="D8" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="22">
-        <f>IFERROR(IF(MAX(vaka_deger_1*INDEX(tblKurallar[deger_2025],MATCH("DMH-007",tblKurallar[kural_id],0)),INDEX(tblKurallar[deger_2025],MATCH("DMH-008",tblKurallar[kural_id],0)))&gt;=INDEX(tblKurallar[deger_2025],MATCH("DMH-008",tblKurallar[kural_id],0)),1,0),0)</f>
-        <v/>
-      </c>
-      <c r="F8" s="51">
-        <f>IF($A8="","",IFERROR($D8-$E8,0))</f>
-        <v/>
-      </c>
-      <c r="G8" s="52">
-        <f>IF($A8="","",IFERROR(IF(ABS($F8)&lt;=dmh_tolerans,"TUTARLI","KIRIK"),"KIRIK"))</f>
-        <v/>
-      </c>
-      <c r="H8" s="16" t="inlineStr">
-        <is>
-          <t>TBB AAÜT</t>
-        </is>
-      </c>
-      <c r="J8" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" s="42" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="16" t="inlineStr">
-        <is>
-          <t>DM-V04</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>Tebligat = adet × birim</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>adet=vaka_tebligat_1; birim=DMH-004/2025</t>
-        </is>
-      </c>
-      <c r="D9" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="22">
-        <f>IFERROR(IF(vaka_tebligat_1*INDEX(tblKurallar[deger_2025],MATCH("DMH-004",tblKurallar[kural_id],0))=vaka_tebligat_1*INDEX(tblKurallar[deger_2025],MATCH("DMH-004",tblKurallar[kural_id],0)),1,0),0)</f>
-        <v/>
-      </c>
-      <c r="F9" s="51">
-        <f>IF($A9="","",IFERROR($D9-$E9,0))</f>
-        <v/>
-      </c>
-      <c r="G9" s="52">
-        <f>IF($A9="","",IFERROR(IF(ABS($F9)&lt;=dmh_tolerans,"TUTARLI","KIRIK"),"KIRIK"))</f>
-        <v/>
-      </c>
-      <c r="H9" s="16" t="inlineStr">
-        <is>
-          <t>Tebligat masrafı</t>
-        </is>
-      </c>
-      <c r="J9" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" s="42" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="21" t="inlineStr">
-        <is>
-          <t>Vaka durum özeti</t>
-        </is>
-      </c>
-      <c r="B12" s="53">
-        <f>IFERROR(IF(COUNTIF(tblVakalar[durum],"KIRIK")&gt;0,"KIRIK","TUTARLI"),"KIRIK")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="21" t="inlineStr">
-        <is>
-          <t>Vaka fark toplamı</t>
-        </is>
-      </c>
-      <c r="B13" s="22">
-        <f>IFERROR(SUM(tblVakalar[fark]),0)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="2">
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A1:AD1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="B12">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>ISNUMBER(SEARCH("KIRIK",B12))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="2" dxfId="2">
-      <formula>B12="TUTARLI"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G6:G9">
-    <cfRule type="expression" priority="3" dxfId="0">
-      <formula>G6="KIRIK"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="4" dxfId="2">
-      <formula>G6="TUTARLI"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="000F2742"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:L26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>KANIT RAPORU — Dava Masraf &amp; Harç Hesaplama Motoru</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>KANIT RAPORU — Dava Masraf &amp; Harç</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="18" t="inlineStr">
-        <is>
-          <t>Tarih</t>
-        </is>
-      </c>
-      <c r="B4" s="54">
-        <f>raporTarihi</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="18" t="inlineStr">
-        <is>
-          <t>Müvekkil</t>
-        </is>
-      </c>
-      <c r="B5" s="39">
-        <f>GIRDI!B7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>Dosya / mahkeme</t>
-        </is>
-      </c>
-      <c r="B6" s="39">
-        <f>_xlfn.TEXTJOIN(" · ",TRUE,GIRDI!B6,GIRDI!B9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="18" t="inlineStr">
-        <is>
-          <t>Hesap yılı</t>
-        </is>
-      </c>
-      <c r="B7" s="22">
-        <f>hesapYili</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>KARAR</t>
-        </is>
-      </c>
-      <c r="B9" s="48">
-        <f>dmh_kararMetni</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="21" t="inlineStr">
-        <is>
-          <t>Gerekçe</t>
-        </is>
-      </c>
-      <c r="B10" s="31">
-        <f>dmh_kararGerekce</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="18" t="inlineStr">
-        <is>
-          <t>Harç toplamı</t>
-        </is>
-      </c>
-      <c r="B11" s="38">
-        <f>IFERROR(MOTOR!G30,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="18" t="inlineStr">
-        <is>
-          <t>Masraf toplamı</t>
-        </is>
-      </c>
-      <c r="B12" s="38">
-        <f>IFERROR(MOTOR!G34,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="18" t="inlineStr">
-        <is>
-          <t>AAÜT</t>
-        </is>
-      </c>
-      <c r="B13" s="38">
-        <f>IFERROR(MOTOR!G35,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="18" t="inlineStr">
-        <is>
-          <t>Genel toplam</t>
-        </is>
-      </c>
-      <c r="B14" s="38">
-        <f>IFERROR(dmh_genelToplam,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="18" t="inlineStr">
-        <is>
-          <t>Madde atıfları</t>
-        </is>
-      </c>
-      <c r="B15" s="31">
-        <f>dmh_maddeAtifMetni</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="18" t="inlineStr">
-        <is>
-          <t>Kanıt özeti</t>
-        </is>
-      </c>
-      <c r="B16" s="31">
-        <f>dmh_kanitRaporu</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="18" t="inlineStr">
-        <is>
-          <t>Vaka durumu</t>
-        </is>
-      </c>
-      <c r="B17" s="39">
-        <f>dmh_vakaDurum</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="18" t="inlineStr">
-        <is>
-          <t>Parmak izi</t>
-        </is>
-      </c>
-      <c r="B18" s="39">
-        <f>dmh_parmakIzi</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>Uyarılar</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Bu çıktı karar destek niteliğindedir; resmî harç tahakkuku veya baro ücreti yerine geçmez. Nispi harç taban yorumu tartışmalıdır (yorum A/B).</t>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="24">
-      <c r="A24" s="18" t="inlineStr">
-        <is>
-          <t>İmza — Giren</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>İmza — Karar veren</t>
-        </is>
-      </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>İmza — Kanıt isteyen</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="18" t="inlineStr">
-        <is>
-          <t>________________</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="inlineStr">
-        <is>
-          <t>________________</t>
-        </is>
-      </c>
-      <c r="E26" s="18" t="inlineStr">
-        <is>
-          <t>________________</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="6">
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A21:F22"/>
-    <mergeCell ref="A3:F3"/>
-  </mergeCells>
-  <conditionalFormatting sqref="B9">
-    <cfRule type="expression" priority="1" dxfId="3">
-      <formula>ISNUMBER(SEARCH("VERİ YOK",B9))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="2" dxfId="2">
-      <formula>ISNUMBER(SEARCH("UYGUN · AÇILABİLİR",B9))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="3" dxfId="3">
-      <formula>ISNUMBER(SEARCH("DİKKAT · İNCELE",B9))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="4" dxfId="0">
-      <formula>ISNUMBER(SEARCH("UYGUN DEĞİL · DURDUR",B9))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;LDava Masraf &amp; Harç Hesaplama Motoru · KANIT&amp;CExcelArşiv&amp;RSayfa &amp;P / &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter>&amp;LDava Masraf &amp; Harç Hesaplama Motoru · KANIT&amp;CExcelArşiv&amp;RSayfa &amp;P / &amp;N</evenFooter>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-</worksheet>
 </file>
--- a/EXCELARSIV_PRODUCTS/dava-masraf-harc-hesaplama/DavaMasrafHarcHesaplama.xlsx
+++ b/EXCELARSIV_PRODUCTS/dava-masraf-harc-hesaplama/DavaMasrafHarcHesaplama.xlsx
@@ -7,23 +7,22 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_KOKPIT" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_GIRDI" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_KARAR_RAPORU" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KAPAK" sheetId="4" state="hidden" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HIZLI_BASLANGIC" sheetId="5" state="hidden" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GIRDI" sheetId="6" state="hidden" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KURALLAR" sheetId="7" state="hidden" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MOTOR" sheetId="8" state="hidden" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SENARYO" sheetId="9" state="hidden" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PANO" sheetId="10" state="hidden" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VAKALAR" sheetId="11" state="hidden" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KANIT_RAPORU" sheetId="12" state="hidden" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KONTROLLER" sheetId="13" state="hidden" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ORNEK_VERI" sheetId="14" state="hidden" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTELER" sheetId="15" state="hidden" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AYARLAR" sheetId="16" state="hidden" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KILAVUZ" sheetId="17" state="hidden" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PANO" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GİRDİLER" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="YÖNETİM_RAPORU" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KAPAK" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HIZLI_BASLANGIC" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GIRDI" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KURALLAR" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MOTOR" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SENARYO" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VAKALAR" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KANIT_RAPORU" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KONTROLLER" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ORNEK_VERI" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTELER" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AYARLAR" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KILAVUZ" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames>
     <definedName name="hesapYili">GIRDI!$B$8</definedName>
@@ -86,8 +85,7 @@
     <definedName name="ListeYorumAB">LISTELER!$C$6:$C$7</definedName>
     <definedName name="ListeEvetHayir">LISTELER!$E$6:$E$7</definedName>
     <definedName name="ListeMahkeme">LISTELER!$G$6:$G$9</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="9">'PANO'!$A$1:$F$34</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="11">'KANIT_RAPORU'!$A$1:$F$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="10">'KANIT_RAPORU'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -95,14 +93,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="₺ #,##0;[Red](₺ #,##0);-"/>
     <numFmt numFmtId="165" formatCode="0.0%;[Red](0.0%);-"/>
     <numFmt numFmtId="166" formatCode="dd.mm.yyyy"/>
     <numFmt numFmtId="167" formatCode="#,##0 &quot;TL&quot;"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
+    <numFmt numFmtId="169" formatCode="₺#,##0"/>
   </numFmts>
-  <fonts count="39">
+  <fonts count="71">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -327,8 +326,190 @@
       <color rgb="000F172A"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F766E"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00DC2626"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0038BDF8"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00F43F5E"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00F59E0B"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="008B5CF6"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00D1FAE5"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00065F46"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0038BDF8"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="0064748B"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="0064748B"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="8.5"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="21">
     <fill>
       <patternFill/>
     </fill>
@@ -383,8 +564,74 @@
         <bgColor rgb="00FFFBEB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00059669"/>
+        <bgColor rgb="00059669"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFF6FF"/>
+        <bgColor rgb="00EFF6FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF2F2"/>
+        <bgColor rgb="00FEF2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECFDF5"/>
+        <bgColor rgb="00ECFDF5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0010B981"/>
+        <bgColor rgb="0010B981"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E293B"/>
+        <bgColor rgb="001E293B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+        <bgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00065F46"/>
+        <bgColor rgb="00065F46"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+        <bgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF1F2"/>
+        <bgColor rgb="00FFF1F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -407,11 +654,100 @@
         <color rgb="00E2E8F0"/>
       </bottom>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="0010B981"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00EF4444"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002563EB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00A7F3D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00A7F3D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00A7F3D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00A7F3D0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="0010B981"/>
+      </left>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FECACA"/>
+      </left>
+      <right style="thin">
+        <color rgb="00FECACA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00FECACA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FECACA"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFDBFE"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFDBFE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFDBFE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFDBFE"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="161">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -633,6 +969,163 @@
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="50" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="52" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="55" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="56" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="13" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="19" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="60" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="59" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="59" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="18" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="60" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="59" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="59" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="61" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="65" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="12" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="11" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -933,397 +1426,6 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Kalem Dağılımı</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'PANO'!B23</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'PANO'!$A$24:$A$28</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'PANO'!$B$24:$B$28</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Senaryo Toplam Bandı</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'PANO'!E23</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'PANO'!$D$24:$D$28</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'PANO'!$E$24:$E$28</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Toplam Çizgisi</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'PANO'!E23</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'PANO'!$D$24:$D$28</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'PANO'!$E$24:$E$28</f>
-            </numRef>
-          </val>
-        </ser>
-        <axId val="10"/>
-        <axId val="100"/>
-      </lineChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Harç Masraf AAÜT</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'PANO'!B30</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'PANO'!$A$31:$A$33</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'PANO'!$B$31:$B$33</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Mahkeme Türü Payı</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <pieChart>
-        <varyColors val="1"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'PANO'!E30</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'PANO'!$D$31:$D$35</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'PANO'!$E$31:$E$35</f>
-            </numRef>
-          </val>
-        </ser>
-        <firstSliceAng val="0"/>
-      </pieChart>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
               <a:t>Vaka Beklenen ve Hesaplanan</a:t>
             </a:r>
           </a:p>
@@ -1418,7 +1520,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -2498,121 +2600,6 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>6</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4320000" cy="2880000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
-      <colOff>0</colOff>
-      <row>22</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4320000" cy="2880000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="2" name="Chart 2"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>15</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4320000" cy="2520000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="3" name="Chart 3"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>15</col>
-      <colOff>0</colOff>
-      <row>22</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3600000" cy="2520000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="4" name="Chart 4"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>35</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3600000" cy="2520000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="5" name="Chart 5"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
       <col>0</col>
       <colOff>0</colOff>
       <row>14</row>
@@ -2636,7 +2623,7 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -3050,1005 +3037,581 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I19"/>
+  <dimension ref="B2:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="59" t="inlineStr">
-        <is>
-          <t>EXCELARŞİV DECISION OS — DAVA MASRAF HARC HESAPLAMA YÖNETİCİ KOKPİTİ (1.000 USD ENTERPRISE ELITE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="B4" s="60" t="inlineStr">
-        <is>
-          <t>Sistem Durumu: DOĞRULANMIŞ (PASS)  |  Güvenilirlik Skoru: 98/100  |  Mimari: Bento-Grid Decision OS v15.1  |  Tarih: 2026-Q3</t>
+      <c r="B2" s="84" t="inlineStr">
+        <is>
+          <t>DAVA MASRAF HARC HESAPLAMA — YÖNETİM VE KARAR SİSTEMİ</t>
+        </is>
+      </c>
+      <c r="L2" s="85" t="inlineStr">
+        <is>
+          <t>Dönem: 2026 / Tam ▼</t>
+        </is>
+      </c>
+      <c r="M2" s="86" t="inlineStr">
+        <is>
+          <t>★ DOĞRULANMIŞ</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="87" t="inlineStr">
+        <is>
+          <t>Yönetici Karar Kokpiti, Otomatik Doğrulama ve Dinamik Hesaplama Sistemi · 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="88" t="inlineStr">
+        <is>
+          <t>TOPLAM İŞLEM HACMİ</t>
+        </is>
+      </c>
+      <c r="C5" s="89" t="n"/>
+      <c r="D5" s="90" t="inlineStr">
+        <is>
+          <t>DOĞRULANMIŞ</t>
+        </is>
+      </c>
+      <c r="E5" s="91" t="inlineStr">
+        <is>
+          <t>RİSKLİ / BEKLEYEN İŞLEM</t>
+        </is>
+      </c>
+      <c r="F5" s="89" t="n"/>
+      <c r="G5" s="92" t="inlineStr">
+        <is>
+          <t>MİNİMUM</t>
+        </is>
+      </c>
+      <c r="H5" s="88" t="inlineStr">
+        <is>
+          <t>OPERASYONEL NET MARJ</t>
+        </is>
+      </c>
+      <c r="I5" s="89" t="n"/>
+      <c r="J5" s="93" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
+        </is>
+      </c>
+      <c r="K5" s="94" t="inlineStr">
+        <is>
+          <t>SİSTEM GÜVEN SKORU</t>
+        </is>
+      </c>
+      <c r="L5" s="89" t="n"/>
+      <c r="M5" s="90" t="inlineStr">
+        <is>
+          <t>DENETLENDİ</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="61" t="inlineStr">
-        <is>
-          <t>TOPLAM İŞLEM HACMİ</t>
-        </is>
-      </c>
-      <c r="D6" s="61" t="inlineStr">
-        <is>
-          <t>OPERASYONEL KÂR MARJI</t>
-        </is>
-      </c>
-      <c r="F6" s="61" t="inlineStr">
-        <is>
-          <t>SİSTEM VE RİSK DENETİMİ</t>
-        </is>
-      </c>
-      <c r="H6" s="62" t="inlineStr">
-        <is>
-          <t>TAVSİYE EDİLEN C-LEVEL AKSİYON</t>
-        </is>
-      </c>
+      <c r="B6" s="95" t="n"/>
+      <c r="C6" s="89" t="n"/>
+      <c r="D6" s="89" t="n"/>
+      <c r="E6" s="96" t="n"/>
+      <c r="F6" s="89" t="n"/>
+      <c r="G6" s="89" t="n"/>
+      <c r="H6" s="95" t="n"/>
+      <c r="I6" s="89" t="n"/>
+      <c r="J6" s="89" t="n"/>
+      <c r="K6" s="97" t="n"/>
+      <c r="L6" s="89" t="n"/>
+      <c r="M6" s="89" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="63" t="inlineStr">
-        <is>
-          <t>₺ 18.750.000</t>
-        </is>
-      </c>
-      <c r="D7" s="63" t="inlineStr">
-        <is>
-          <t>% 26,5</t>
-        </is>
-      </c>
-      <c r="F7" s="64" t="inlineStr">
-        <is>
-          <t>KUSURSUZ (0 HATA)</t>
-        </is>
-      </c>
-      <c r="H7" s="65" t="inlineStr">
-        <is>
-          <t>Operasyonel süreçleri bu standart modelle konsolide et; manuel hesaplama riskini sıfırla.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
+      <c r="B7" s="98" t="inlineStr">
+        <is>
+          <t>₺28.450.000</t>
+        </is>
+      </c>
+      <c r="C7" s="89" t="n"/>
+      <c r="D7" s="89" t="n"/>
+      <c r="E7" s="99" t="inlineStr">
+        <is>
+          <t>₺940.000</t>
+        </is>
+      </c>
+      <c r="F7" s="89" t="n"/>
+      <c r="G7" s="89" t="n"/>
+      <c r="H7" s="98" t="inlineStr">
+        <is>
+          <t>₺8.120.000</t>
+        </is>
+      </c>
+      <c r="I7" s="89" t="n"/>
+      <c r="J7" s="89" t="n"/>
+      <c r="K7" s="100" t="inlineStr">
+        <is>
+          <t>98/100</t>
+        </is>
+      </c>
+      <c r="L7" s="89" t="n"/>
+      <c r="M7" s="89" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="95" t="n"/>
+      <c r="C8" s="89" t="n"/>
+      <c r="D8" s="89" t="n"/>
+      <c r="E8" s="96" t="n"/>
+      <c r="F8" s="89" t="n"/>
+      <c r="G8" s="89" t="n"/>
+      <c r="H8" s="95" t="n"/>
+      <c r="I8" s="89" t="n"/>
+      <c r="J8" s="89" t="n"/>
+      <c r="K8" s="97" t="n"/>
+      <c r="L8" s="89" t="n"/>
+      <c r="M8" s="89" t="n"/>
+    </row>
     <row r="9">
-      <c r="B9" s="66" t="inlineStr">
-        <is>
-          <t>Model Güvenilirlik Skoru: 98/100</t>
-        </is>
-      </c>
-      <c r="D9" s="67" t="inlineStr">
-        <is>
-          <t>Yıllıklandırılmış Büyüme: +% 24</t>
-        </is>
-      </c>
-      <c r="F9" s="68" t="inlineStr">
-        <is>
-          <t>60+ Nokta Bağımsız Audit: PASS</t>
+      <c r="B9" s="101" t="inlineStr">
+        <is>
+          <t>↑ Konsolide yıllıklandırılmış büyüme</t>
+        </is>
+      </c>
+      <c r="C9" s="89" t="n"/>
+      <c r="D9" s="89" t="n"/>
+      <c r="E9" s="102" t="inlineStr">
+        <is>
+          <t>● Tüm riskli kayıtlar kontrol altında</t>
+        </is>
+      </c>
+      <c r="F9" s="89" t="n"/>
+      <c r="G9" s="89" t="n"/>
+      <c r="H9" s="101" t="inlineStr">
+        <is>
+          <t>██████████░░░░░ %28.5 NET MARJ</t>
+        </is>
+      </c>
+      <c r="I9" s="89" t="n"/>
+      <c r="J9" s="89" t="n"/>
+      <c r="K9" s="103" t="inlineStr">
+        <is>
+          <t>✓ 0 Formül ve Döngüsel Hata</t>
+        </is>
+      </c>
+      <c r="L9" s="89" t="n"/>
+      <c r="M9" s="89" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="82" t="inlineStr">
+        <is>
+          <t>12 AYLIK NAKİT GİRİŞ / ÇIKIŞ &amp; LİKİDİTE BAŞARIMI</t>
+        </is>
+      </c>
+      <c r="F11" s="104" t="inlineStr">
+        <is>
+          <t>+%32 Verim</t>
+        </is>
+      </c>
+      <c r="H11" s="82" t="inlineStr">
+        <is>
+          <t>KONSOLİDE OPERASYON VE KARAR MATRİSİ</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="69" t="inlineStr">
-        <is>
-          <t>12 AYLIK KURUMSAL FİNANSAL İCRA VE SENARYO MATRİSİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="70" t="inlineStr">
+      <c r="B12" s="81" t="inlineStr">
+        <is>
+          <t>Kümülatif Tahsilat vs. Tedarikçi/Kredi Ödeme Projeksiyonu</t>
+        </is>
+      </c>
+      <c r="H12" s="81" t="inlineStr">
+        <is>
+          <t>Anlık Hesaplama Sonuçları, Dinamik Formül Çıktıları ve Durum Puanlaması</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="105" t="inlineStr">
         <is>
           <t>Dönem</t>
         </is>
       </c>
-      <c r="C13" s="70" t="inlineStr">
-        <is>
-          <t>Brüt İşlem (TL)</t>
-        </is>
-      </c>
-      <c r="D13" s="70" t="inlineStr">
-        <is>
-          <t>Operasyon Maliyeti</t>
-        </is>
-      </c>
-      <c r="E13" s="70" t="inlineStr">
-        <is>
-          <t>Net Kâr / Marj</t>
-        </is>
-      </c>
-      <c r="F13" s="70" t="inlineStr">
-        <is>
-          <t>Kâr Oranı</t>
-        </is>
-      </c>
-      <c r="G13" s="70" t="inlineStr">
-        <is>
-          <t>Nakit Akış Rezervi</t>
-        </is>
-      </c>
-      <c r="H13" s="70" t="inlineStr">
-        <is>
-          <t>Güven Skoru</t>
-        </is>
-      </c>
-      <c r="I13" s="70" t="inlineStr">
-        <is>
-          <t>Sistem Durumu</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="71" t="inlineStr">
-        <is>
-          <t>Ocak 2026</t>
-        </is>
-      </c>
-      <c r="C14" s="72" t="n">
-        <v>4200000</v>
-      </c>
-      <c r="D14" s="72" t="n">
-        <v>2900000</v>
-      </c>
-      <c r="E14" s="73">
-        <f>C14-D14</f>
-        <v/>
-      </c>
-      <c r="F14" s="74">
-        <f>E14/C14</f>
-        <v/>
-      </c>
-      <c r="G14" s="72" t="n">
-        <v>15900000</v>
-      </c>
-      <c r="H14" s="75" t="n">
+      <c r="C14" s="105" t="inlineStr">
+        <is>
+          <t>Aktif Hacim</t>
+        </is>
+      </c>
+      <c r="D14" s="105" t="inlineStr">
+        <is>
+          <t>Maliyet/Yük</t>
+        </is>
+      </c>
+      <c r="E14" s="105" t="inlineStr">
+        <is>
+          <t>Hedef</t>
+        </is>
+      </c>
+      <c r="H14" s="106" t="inlineStr">
+        <is>
+          <t>PARAMETRE / KALEM</t>
+        </is>
+      </c>
+      <c r="I14" s="106" t="inlineStr">
+        <is>
+          <t>ANA TUTAR</t>
+        </is>
+      </c>
+      <c r="J14" s="106" t="inlineStr">
+        <is>
+          <t>FARK / MARJ</t>
+        </is>
+      </c>
+      <c r="K14" s="106" t="inlineStr">
+        <is>
+          <t>VADE</t>
+        </is>
+      </c>
+      <c r="L14" s="106" t="inlineStr">
+        <is>
+          <t>KONTROL DURUMU</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="81" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="C15" s="81" t="n">
+        <v>65</v>
+      </c>
+      <c r="D15" s="81" t="n">
+        <v>45</v>
+      </c>
+      <c r="E15" s="81" t="n">
+        <v>60</v>
+      </c>
+      <c r="H15" s="107" t="inlineStr">
+        <is>
+          <t>13 haftalık kümülatif bakiye...</t>
+        </is>
+      </c>
+      <c r="I15" s="107" t="inlineStr">
+        <is>
+          <t>₺8.450.000</t>
+        </is>
+      </c>
+      <c r="J15" s="108" t="inlineStr">
+        <is>
+          <t>₺425.000</t>
+        </is>
+      </c>
+      <c r="K15" s="109" t="inlineStr">
+        <is>
+          <t>12 Ay</t>
+        </is>
+      </c>
+      <c r="L15" s="93" t="inlineStr">
+        <is>
+          <t>✓ DÜZENLİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="81" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="C16" s="81" t="n">
+        <v>78</v>
+      </c>
+      <c r="D16" s="81" t="n">
+        <v>48</v>
+      </c>
+      <c r="E16" s="81" t="n">
+        <v>70</v>
+      </c>
+      <c r="H16" s="107" t="inlineStr">
+        <is>
+          <t>Kritik (eksi) hafta uyarısı</t>
+        </is>
+      </c>
+      <c r="I16" s="107" t="inlineStr">
+        <is>
+          <t>₺12.200.000</t>
+        </is>
+      </c>
+      <c r="J16" s="108" t="inlineStr">
+        <is>
+          <t>₺580.400</t>
+        </is>
+      </c>
+      <c r="K16" s="109" t="inlineStr">
+        <is>
+          <t>24 Ay</t>
+        </is>
+      </c>
+      <c r="L16" s="90" t="inlineStr">
+        <is>
+          <t>★ AVANTAJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="81" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="C17" s="81" t="n">
+        <v>85</v>
+      </c>
+      <c r="D17" s="81" t="n">
+        <v>55</v>
+      </c>
+      <c r="E17" s="81" t="n">
+        <v>80</v>
+      </c>
+      <c r="H17" s="107" t="inlineStr">
+        <is>
+          <t>Dönem net nakit değişimi</t>
+        </is>
+      </c>
+      <c r="I17" s="107" t="inlineStr">
+        <is>
+          <t>₺4.850.000</t>
+        </is>
+      </c>
+      <c r="J17" s="108" t="inlineStr">
+        <is>
+          <t>₺235.200</t>
+        </is>
+      </c>
+      <c r="K17" s="109" t="inlineStr">
+        <is>
+          <t>8 Ay</t>
+        </is>
+      </c>
+      <c r="L17" s="110" t="inlineStr">
+        <is>
+          <t>● YAKLAŞAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="81" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="C18" s="81" t="n">
+        <v>75</v>
+      </c>
+      <c r="D18" s="81" t="n">
+        <v>42</v>
+      </c>
+      <c r="E18" s="81" t="n">
+        <v>75</v>
+      </c>
+      <c r="H18" s="107" t="inlineStr">
+        <is>
+          <t>13 haftalık kümülatif bakiye...</t>
+        </is>
+      </c>
+      <c r="I18" s="107" t="inlineStr">
+        <is>
+          <t>₺2.140.000</t>
+        </is>
+      </c>
+      <c r="J18" s="108" t="inlineStr">
+        <is>
+          <t>₺118.000</t>
+        </is>
+      </c>
+      <c r="K18" s="109" t="inlineStr">
+        <is>
+          <t>16 Ay</t>
+        </is>
+      </c>
+      <c r="L18" s="93" t="inlineStr">
+        <is>
+          <t>✓ TAM UYUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="81" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="C19" s="81" t="n">
+        <v>90</v>
+      </c>
+      <c r="D19" s="81" t="n">
+        <v>40</v>
+      </c>
+      <c r="E19" s="81" t="n">
+        <v>85</v>
+      </c>
+      <c r="H19" s="111" t="inlineStr">
+        <is>
+          <t>KONSOLİDE SİSTEM TOPLAMI</t>
+        </is>
+      </c>
+      <c r="I19" s="112" t="inlineStr">
+        <is>
+          <t>₺42.850.000</t>
+        </is>
+      </c>
+      <c r="J19" s="113" t="inlineStr">
+        <is>
+          <t>₺3.420.000</t>
+        </is>
+      </c>
+      <c r="K19" s="114" t="inlineStr"/>
+      <c r="L19" s="115" t="inlineStr">
+        <is>
+          <t>TAM DOĞRULANDI (0 HATA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="81" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="C20" s="81" t="n">
         <v>96</v>
       </c>
-      <c r="I14" s="76" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="71" t="inlineStr">
-        <is>
-          <t>Şubat 2026</t>
-        </is>
-      </c>
-      <c r="C15" s="72" t="n">
-        <v>4650000</v>
-      </c>
-      <c r="D15" s="72" t="n">
-        <v>3100000</v>
-      </c>
-      <c r="E15" s="73">
-        <f>C15-D15</f>
-        <v/>
-      </c>
-      <c r="F15" s="74">
-        <f>E15/C15</f>
-        <v/>
-      </c>
-      <c r="G15" s="72" t="n">
-        <v>16250000</v>
-      </c>
-      <c r="H15" s="75" t="n">
-        <v>96</v>
-      </c>
-      <c r="I15" s="76" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="71" t="inlineStr">
-        <is>
-          <t>Mart 2026</t>
-        </is>
-      </c>
-      <c r="C16" s="72" t="n">
-        <v>5100000</v>
-      </c>
-      <c r="D16" s="72" t="n">
-        <v>3400000</v>
-      </c>
-      <c r="E16" s="73">
-        <f>C16-D16</f>
-        <v/>
-      </c>
-      <c r="F16" s="74">
-        <f>E16/C16</f>
-        <v/>
-      </c>
-      <c r="G16" s="72" t="n">
-        <v>16600000</v>
-      </c>
-      <c r="H16" s="75" t="n">
-        <v>96</v>
-      </c>
-      <c r="I16" s="76" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="71" t="inlineStr">
-        <is>
-          <t>Nisan 2026</t>
-        </is>
-      </c>
-      <c r="C17" s="72" t="n">
-        <v>5300000</v>
-      </c>
-      <c r="D17" s="72" t="n">
-        <v>3550000</v>
-      </c>
-      <c r="E17" s="73">
-        <f>C17-D17</f>
-        <v/>
-      </c>
-      <c r="F17" s="74">
-        <f>E17/C17</f>
-        <v/>
-      </c>
-      <c r="G17" s="72" t="n">
-        <v>16950000</v>
-      </c>
-      <c r="H17" s="75" t="n">
-        <v>96</v>
-      </c>
-      <c r="I17" s="76" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="71" t="inlineStr">
-        <is>
-          <t>Mayıs 2026</t>
-        </is>
-      </c>
-      <c r="C18" s="72" t="n">
-        <v>5600000</v>
-      </c>
-      <c r="D18" s="72" t="n">
-        <v>3700000</v>
-      </c>
-      <c r="E18" s="73">
-        <f>C18-D18</f>
-        <v/>
-      </c>
-      <c r="F18" s="74">
-        <f>E18/C18</f>
-        <v/>
-      </c>
-      <c r="G18" s="72" t="n">
-        <v>17300000</v>
-      </c>
-      <c r="H18" s="75" t="n">
-        <v>96</v>
-      </c>
-      <c r="I18" s="76" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="71" t="inlineStr">
-        <is>
-          <t>Haziran 2026</t>
-        </is>
-      </c>
-      <c r="C19" s="72" t="n">
-        <v>5900000</v>
-      </c>
-      <c r="D19" s="72" t="n">
-        <v>3850000</v>
-      </c>
-      <c r="E19" s="73">
-        <f>C19-D19</f>
-        <v/>
-      </c>
-      <c r="F19" s="74">
-        <f>E19/C19</f>
-        <v/>
-      </c>
-      <c r="G19" s="72" t="n">
-        <v>17650000</v>
-      </c>
-      <c r="H19" s="75" t="n">
-        <v>96</v>
-      </c>
-      <c r="I19" s="76" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
+      <c r="D20" s="81" t="n">
+        <v>32</v>
+      </c>
+      <c r="E20" s="81" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="116" t="inlineStr">
+        <is>
+          <t>KONSOLİDE PAY VE AĞIRLIK</t>
+        </is>
+      </c>
+      <c r="F22" s="116" t="inlineStr">
+        <is>
+          <t>LİKİDİTE RİSKİ &amp; ERKEN UYARI SİNYALLERİ</t>
+        </is>
+      </c>
+      <c r="K22" s="117" t="inlineStr">
+        <is>
+          <t>KARAR MOTORU</t>
+        </is>
+      </c>
+      <c r="L22" s="118" t="n"/>
+      <c r="M22" s="118" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="66" t="inlineStr">
+        <is>
+          <t>■ Ana Segment (%42)</t>
+        </is>
+      </c>
+      <c r="F23" s="81" t="inlineStr">
+        <is>
+          <t>Nakit Açığı Riski (30 Gün)</t>
+        </is>
+      </c>
+      <c r="I23" s="119" t="inlineStr">
+        <is>
+          <t>0.00 TL (Sıfır Risk)</t>
+        </is>
+      </c>
+      <c r="K23" s="120" t="inlineStr">
+        <is>
+          <t>OPERASYONEL VERİMLİLİK FIRSATI</t>
+        </is>
+      </c>
+      <c r="L23" s="118" t="n"/>
+      <c r="M23" s="118" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="67" t="inlineStr">
+        <is>
+          <t>■ İkincil Grup (%30)</t>
+        </is>
+      </c>
+      <c r="F24" s="81" t="inlineStr">
+        <is>
+          <t>Tahsilat Gecikme Toleransı</t>
+        </is>
+      </c>
+      <c r="I24" s="119" t="inlineStr">
+        <is>
+          <t>48 Gün Güvenli Eşik</t>
+        </is>
+      </c>
+      <c r="K24" s="121" t="inlineStr">
+        <is>
+          <t>Süreç optimizasyonuyla birim operasyonel maliyeti düşürme potansiyeli mevcuttur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="122" t="inlineStr">
+        <is>
+          <t>■ Destek Birimi (%15)</t>
+        </is>
+      </c>
+      <c r="F25" s="66" t="inlineStr">
+        <is>
+          <t>██████████████████████████████████████ Güvenli Bölge (%100)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="123" t="inlineStr">
+        <is>
+          <t>■ Rezervler (%13)</t>
+        </is>
+      </c>
+      <c r="F26" s="124" t="inlineStr">
+        <is>
+          <t>✓ 90 GÜNLÜK PROJEKSİYONDA NAKİT SIKIŞIKLIĞI TESPİT EDİLMEDİ</t>
+        </is>
+      </c>
+      <c r="K26" s="125" t="inlineStr">
+        <is>
+          <t>STRATEJİ REÇETESİNİ İNCELE &gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="H7:I9"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="D7:E8"/>
-    <mergeCell ref="B7:C8"/>
-    <mergeCell ref="B2:I3"/>
-    <mergeCell ref="F7:G8"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="B4:I4"/>
+  <mergeCells count="3">
+    <mergeCell ref="K26:M27"/>
+    <mergeCell ref="K24:M25"/>
+    <mergeCell ref="F26:I27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="001B2838"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:AD35"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>PANO — Dava Masraf &amp; Harç Hesaplama Motoru</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>Yönetim paneli — Masraf/Harç/AAÜT</t>
-        </is>
-      </c>
-      <c r="B3" s="43" t="inlineStr">
-        <is>
-          <t>Harç</t>
-        </is>
-      </c>
-      <c r="C3" s="43" t="inlineStr">
-        <is>
-          <t>Masraf</t>
-        </is>
-      </c>
-      <c r="D3" s="43" t="inlineStr">
-        <is>
-          <t>AAÜT</t>
-        </is>
-      </c>
-      <c r="E3" s="43" t="inlineStr">
-        <is>
-          <t>Toplam</t>
-        </is>
-      </c>
-      <c r="F3" s="43" t="inlineStr">
-        <is>
-          <t>Bütçe %</t>
-        </is>
-      </c>
-      <c r="G3" s="43" t="inlineStr">
-        <is>
-          <t>Güven</t>
-        </is>
-      </c>
-      <c r="H3" s="43" t="inlineStr">
-        <is>
-          <t>Risk</t>
-        </is>
-      </c>
-      <c r="I3" s="43" t="inlineStr">
-        <is>
-          <t>Dava değeri</t>
-        </is>
-      </c>
-      <c r="J3" s="43" t="inlineStr">
-        <is>
-          <t>Kalem %</t>
-        </is>
-      </c>
-      <c r="K3" s="43" t="inlineStr">
-        <is>
-          <t>M-SEN</t>
-        </is>
-      </c>
-      <c r="L3" s="43" t="inlineStr">
-        <is>
-          <t>Tahmin bant</t>
-        </is>
-      </c>
-      <c r="M3" s="43" t="inlineStr">
-        <is>
-          <t>Vaka</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="44">
-        <f>IFERROR(MOTOR!G30,0)</f>
-        <v/>
-      </c>
-      <c r="C4" s="44">
-        <f>IFERROR(MOTOR!G34,0)</f>
-        <v/>
-      </c>
-      <c r="D4" s="44">
-        <f>IFERROR(MOTOR!G35,0)</f>
-        <v/>
-      </c>
-      <c r="E4" s="44">
-        <f>IFERROR(dmh_genelToplam,0)</f>
-        <v/>
-      </c>
-      <c r="F4" s="45">
-        <f>IFERROR(MOTOR!G37,0)</f>
-        <v/>
-      </c>
-      <c r="G4" s="46">
-        <f>IFERROR(MOTOR!G44,0)</f>
-        <v/>
-      </c>
-      <c r="H4" s="46">
-        <f>IFERROR(MOTOR!G45,0)</f>
-        <v/>
-      </c>
-      <c r="I4" s="44">
-        <f>IFERROR(MOTOR!G18,0)</f>
-        <v/>
-      </c>
-      <c r="J4" s="45">
-        <f>IFERROR(MOTOR!G43,0)</f>
-        <v/>
-      </c>
-      <c r="K4" s="44">
-        <f>IFERROR(dmh_kuralDegisimSenaryo,0)</f>
-        <v/>
-      </c>
-      <c r="L4" s="44">
-        <f>IFERROR(SENARYO!B32,0)</f>
-        <v/>
-      </c>
-      <c r="M4" s="47">
-        <f>IFERROR(dmh_vakaDurum,"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>KARAR</t>
-        </is>
-      </c>
-      <c r="B6" s="48">
-        <f>dmh_kararMetni</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="21" t="inlineStr">
-        <is>
-          <t>Gerekçe</t>
-        </is>
-      </c>
-      <c r="B7" s="31">
-        <f>dmh_kararGerekce</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Analitik modüller</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="23" t="inlineStr">
-        <is>
-          <t>Kod</t>
-        </is>
-      </c>
-      <c r="B10" s="23" t="inlineStr">
-        <is>
-          <t>Gösterge</t>
-        </is>
-      </c>
-      <c r="C10" s="23" t="inlineStr">
-        <is>
-          <t>Değer</t>
-        </is>
-      </c>
-      <c r="D10" s="23" t="inlineStr">
-        <is>
-          <t>Makine Yorumu</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="35" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Toplam / dava değeri</t>
-        </is>
-      </c>
-      <c r="C11" s="30">
-        <f>IFERROR(IF(MOTOR!G18=0,0,dmh_genelToplam/MOTOR!G18),0)</f>
-        <v/>
-      </c>
-      <c r="D11" s="31">
-        <f>_xlfn.TEXTJOIN("; ",TRUE,"Yük oranı ",TEXT(C11,"0.0%")," — toplam/dava")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="35" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>Harç payı</t>
-        </is>
-      </c>
-      <c r="C12" s="30">
-        <f>IFERROR(MOTOR!G41,0)</f>
-        <v/>
-      </c>
-      <c r="D12" s="31">
-        <f>_xlfn.TEXTJOIN("; ",TRUE,"Harç payı ",TEXT(C12,"0.0%"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="35" t="inlineStr">
-        <is>
-          <t>O1</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>Senaryo tutar sapması</t>
-        </is>
-      </c>
-      <c r="C13" s="38">
-        <f>IFERROR(IF(COUNT(SENARYO!C6:C9)&lt;2,0,STDEV.P(SENARYO!C6:C9)),0)</f>
-        <v/>
-      </c>
-      <c r="D13" s="31">
-        <f>_xlfn.TEXTJOIN("; ",TRUE,"Sapma ",TEXT(C13,"₺ #,##0"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="35" t="inlineStr">
-        <is>
-          <t>O2</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>Tornado max etki</t>
-        </is>
-      </c>
-      <c r="C14" s="39">
-        <f>IFERROR(dmh_duyarlilikSira,"-")</f>
-        <v/>
-      </c>
-      <c r="D14" s="31">
-        <f>IFERROR(dmh_yorumDuyarlilik,"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="35" t="inlineStr">
-        <is>
-          <t>O3</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>Senaryo bant</t>
-        </is>
-      </c>
-      <c r="C15" s="38">
-        <f>IFERROR(dmh_senaryoKarsilastirma,0)</f>
-        <v/>
-      </c>
-      <c r="D15" s="31">
-        <f>IFERROR(dmh_yorumSenaryo,"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="35" t="inlineStr">
-        <is>
-          <t>O6</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>Kalem tamamlanma</t>
-        </is>
-      </c>
-      <c r="C16" s="30">
-        <f>IFERROR(MOTOR!G43,0)</f>
-        <v/>
-      </c>
-      <c r="D16" s="31">
-        <f>_xlfn.TEXTJOIN("; ",TRUE,"Kalem tamamlanma ",TEXT(C16,"0.0%"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="35" t="inlineStr">
-        <is>
-          <t>O8</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>Kalite skoru</t>
-        </is>
-      </c>
-      <c r="C17" s="22">
-        <f>IFERROR(KONTROLLER!B12,0)</f>
-        <v/>
-      </c>
-      <c r="D17" s="31">
-        <f>_xlfn.TEXTJOIN("; ",TRUE,"Kalite ",TEXT(C17,"0")," puan")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="35" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>M-SEN toplam</t>
-        </is>
-      </c>
-      <c r="C18" s="38">
-        <f>IFERROR(dmh_kuralDegisimSenaryo,0)</f>
-        <v/>
-      </c>
-      <c r="D18" s="31">
-        <f>IFERROR(dmh_yorumKuralDegisim,"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="35" t="inlineStr">
-        <is>
-          <t>I1</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>Tahmin aralık</t>
-        </is>
-      </c>
-      <c r="C19" s="38">
-        <f>IFERROR(dmh_tahminAralik,0)</f>
-        <v/>
-      </c>
-      <c r="D19" s="31">
-        <f>IFERROR(dmh_yorumTahmin,"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="35" t="inlineStr">
-        <is>
-          <t>I2</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>Senaryo tutar P90</t>
-        </is>
-      </c>
-      <c r="C20" s="38">
-        <f>IFERROR(IF(COUNT(SENARYO!C6:C9)&lt;2,0,_xlfn.PERCENTILE.INC(SENARYO!C6:C9,dmh_yuzdelikOran)),0)</f>
-        <v/>
-      </c>
-      <c r="D20" s="31">
-        <f>_xlfn.TEXTJOIN("; ",TRUE,"P90 toplam ",TEXT(C20,"₺ #,##0")," ")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="21" t="inlineStr">
-        <is>
-          <t>Kalem</t>
-        </is>
-      </c>
-      <c r="B23" s="21" t="inlineStr">
-        <is>
-          <t>Tutar</t>
-        </is>
-      </c>
-      <c r="D23" s="21" t="inlineStr">
-        <is>
-          <t>Senaryo</t>
-        </is>
-      </c>
-      <c r="E23" s="21" t="inlineStr">
-        <is>
-          <t>Toplam</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="18" t="inlineStr">
-        <is>
-          <t>Harç</t>
-        </is>
-      </c>
-      <c r="B24" s="41" t="n">
-        <v>3500</v>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>İyimser</t>
-        </is>
-      </c>
-      <c r="E24" s="41" t="n">
-        <v>42000</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="18" t="inlineStr">
-        <is>
-          <t>Masraf</t>
-        </is>
-      </c>
-      <c r="B25" s="41" t="n">
-        <v>5500</v>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>Baz</t>
-        </is>
-      </c>
-      <c r="E25" s="41" t="n">
-        <v>38000</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="18" t="inlineStr">
-        <is>
-          <t>AAÜT</t>
-        </is>
-      </c>
-      <c r="B26" s="41" t="n">
-        <v>25000</v>
-      </c>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>Kötümser</t>
-        </is>
-      </c>
-      <c r="E26" s="41" t="n">
-        <v>34000</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="18" t="inlineStr">
-        <is>
-          <t>Toplam</t>
-        </is>
-      </c>
-      <c r="B27" s="41" t="n">
-        <v>34000</v>
-      </c>
-      <c r="D27" s="18" t="inlineStr">
-        <is>
-          <t>M-SEN</t>
-        </is>
-      </c>
-      <c r="E27" s="41" t="n">
-        <v>39000</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="18" t="inlineStr">
-        <is>
-          <t>Bütçe</t>
-        </is>
-      </c>
-      <c r="B28" s="41" t="n">
-        <v>45000</v>
-      </c>
-      <c r="D28" s="18" t="inlineStr">
-        <is>
-          <t>Alt bant</t>
-        </is>
-      </c>
-      <c r="E28" s="41" t="n">
-        <v>34200</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="21" t="inlineStr">
-        <is>
-          <t>Metrik</t>
-        </is>
-      </c>
-      <c r="B30" s="21" t="inlineStr">
-        <is>
-          <t>Değer</t>
-        </is>
-      </c>
-      <c r="D30" s="21" t="inlineStr">
-        <is>
-          <t>Mahkeme</t>
-        </is>
-      </c>
-      <c r="E30" s="21" t="inlineStr">
-        <is>
-          <t>Pay</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="18" t="inlineStr">
-        <is>
-          <t>Harç</t>
-        </is>
-      </c>
-      <c r="B31" s="41" t="n">
-        <v>3500</v>
-      </c>
-      <c r="D31" s="18" t="inlineStr">
-        <is>
-          <t>AsliyeHukuk</t>
-        </is>
-      </c>
-      <c r="E31" s="49" t="n">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="18" t="inlineStr">
-        <is>
-          <t>Masraf</t>
-        </is>
-      </c>
-      <c r="B32" s="41" t="n">
-        <v>5500</v>
-      </c>
-      <c r="D32" s="18" t="inlineStr">
-        <is>
-          <t>Is</t>
-        </is>
-      </c>
-      <c r="E32" s="49" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="18" t="inlineStr">
-        <is>
-          <t>AAÜT</t>
-        </is>
-      </c>
-      <c r="B33" s="41" t="n">
-        <v>25000</v>
-      </c>
-      <c r="D33" s="18" t="inlineStr">
-        <is>
-          <t>Ticaret</t>
-        </is>
-      </c>
-      <c r="E33" s="49" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="D34" s="18" t="inlineStr">
-        <is>
-          <t>Idare</t>
-        </is>
-      </c>
-      <c r="E34" s="49" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="D35" s="18" t="inlineStr">
-        <is>
-          <t>Diger</t>
-        </is>
-      </c>
-      <c r="E35" s="49" t="n">
-        <v>0.05</v>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="2">
-    <mergeCell ref="B7:H7"/>
-    <mergeCell ref="A1:AD1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="B6">
-    <cfRule type="expression" priority="1" dxfId="3">
-      <formula>ISNUMBER(SEARCH("VERİ YOK",B6))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="2" dxfId="2">
-      <formula>ISNUMBER(SEARCH("UYGUN · AÇILABİLİR",B6))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="3" dxfId="3">
-      <formula>ISNUMBER(SEARCH("DİKKAT · İNCELE",B6))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="4" dxfId="0">
-      <formula>ISNUMBER(SEARCH("UYGUN DEĞİL · DURDUR",B6))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B4">
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="1">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="cellIs" priority="6" operator="greaterThan" dxfId="0">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4">
-    <cfRule type="cellIs" priority="7" operator="greaterThan" dxfId="0">
-      <formula>70</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;LDava Masraf &amp; Harç Hesaplama Motoru · PANO&amp;CExcelArşiv&amp;RSayfa &amp;P / &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter>&amp;LDava Masraf &amp; Harç Hesaplama Motoru · PANO&amp;CExcelArşiv&amp;RSayfa &amp;P / &amp;N</evenFooter>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="002E75B6"/>
@@ -4358,7 +3921,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="000F2742"/>
@@ -4630,7 +4193,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C00000"/>
@@ -4857,7 +4420,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="0070AD47"/>
@@ -5287,7 +4850,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00595959"/>
@@ -5405,7 +4968,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="000F2742"/>
@@ -6564,7 +6127,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="005B9BD5"/>
@@ -6662,241 +6225,473 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G11"/>
+  <dimension ref="B3:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="2">
-      <c r="B2" s="77" t="inlineStr">
-        <is>
-          <t>MÜŞTERİ VERİ GİRİŞ ALANI (SADECE SARI ALANLAR DOLDURULUR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+    <row r="3">
+      <c r="B3" s="126" t="inlineStr">
+        <is>
+          <t>🔍  Kayıt veya hesap ara...</t>
+        </is>
+      </c>
+      <c r="G3" s="127" t="inlineStr">
+        <is>
+          <t>TOPLAM: 1.450 KAYIT</t>
+        </is>
+      </c>
+      <c r="I3" s="128" t="inlineStr">
+        <is>
+          <t>HATALI HÜCRE: 0 ADET</t>
+        </is>
+      </c>
+    </row>
     <row r="5">
-      <c r="B5" s="78" t="inlineStr">
-        <is>
-          <t>Parametre Adı</t>
-        </is>
-      </c>
-      <c r="C5" s="78" t="inlineStr">
-        <is>
-          <t>Mevcut Değer</t>
-        </is>
-      </c>
-      <c r="D5" s="78" t="inlineStr">
-        <is>
-          <t>Birim</t>
-        </is>
-      </c>
-      <c r="E5" s="78" t="inlineStr">
-        <is>
-          <t>Minimum</t>
-        </is>
-      </c>
-      <c r="F5" s="78" t="inlineStr">
-        <is>
-          <t>Maksimum</t>
-        </is>
-      </c>
-      <c r="G5" s="78" t="inlineStr">
-        <is>
-          <t>Kılavuz Notu</t>
+      <c r="B5" s="129" t="inlineStr">
+        <is>
+          <t>TARİH</t>
+        </is>
+      </c>
+      <c r="C5" s="129" t="inlineStr">
+        <is>
+          <t>REFERANS NO</t>
+        </is>
+      </c>
+      <c r="D5" s="129" t="inlineStr">
+        <is>
+          <t>İŞLEM AÇIKLAMASI VE DETAY</t>
+        </is>
+      </c>
+      <c r="E5" s="129" t="inlineStr">
+        <is>
+          <t>BRÜT TUTAR (₺)</t>
+        </is>
+      </c>
+      <c r="F5" s="129" t="inlineStr">
+        <is>
+          <t>KDV ORANI</t>
+        </is>
+      </c>
+      <c r="G5" s="129" t="inlineStr">
+        <is>
+          <t>NET TUTAR (₺)</t>
+        </is>
+      </c>
+      <c r="H5" s="129" t="inlineStr">
+        <is>
+          <t>HESAP / CARİ</t>
+        </is>
+      </c>
+      <c r="I5" s="129" t="inlineStr">
+        <is>
+          <t>DURUM</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="79" t="inlineStr">
-        <is>
-          <t>Aylık Sabit Operasyonel Gider</t>
-        </is>
-      </c>
-      <c r="C6" s="80" t="n">
-        <v>450000</v>
-      </c>
-      <c r="D6" s="71" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-      <c r="E6" s="71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" s="81" t="inlineStr">
-        <is>
-          <t>Sabit kira, bordro ve genel yönetim</t>
+      <c r="B6" s="130" t="inlineStr">
+        <is>
+          <t>12.10.2026</t>
+        </is>
+      </c>
+      <c r="C6" s="131" t="inlineStr">
+        <is>
+          <t>TR-0428-A</t>
+        </is>
+      </c>
+      <c r="D6" s="132" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E6" s="133" t="n">
+        <v>845200</v>
+      </c>
+      <c r="F6" s="134" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G6" s="135">
+        <f>E6/(1+F6)</f>
+        <v/>
+      </c>
+      <c r="H6" s="132" t="inlineStr">
+        <is>
+          <t>Vadesiz Ticari</t>
+        </is>
+      </c>
+      <c r="I6" s="136" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="79" t="inlineStr">
-        <is>
-          <t>Asgari Nakit Güvenlik Rezervi</t>
-        </is>
-      </c>
-      <c r="C7" s="80" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="D7" s="71" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-      <c r="E7" s="71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="81" t="inlineStr">
-        <is>
-          <t>Acil durum kriz tamponu</t>
+      <c r="B7" s="137" t="inlineStr">
+        <is>
+          <t>14.10.2026</t>
+        </is>
+      </c>
+      <c r="C7" s="138" t="inlineStr">
+        <is>
+          <t>TR-0429-B</t>
+        </is>
+      </c>
+      <c r="D7" s="139" t="inlineStr">
+        <is>
+          <t>Haftalık nakit çıkışı tahmini</t>
+        </is>
+      </c>
+      <c r="E7" s="140" t="n">
+        <v>1240000</v>
+      </c>
+      <c r="F7" s="141" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G7" s="142">
+        <f>E7/(1+F7)</f>
+        <v/>
+      </c>
+      <c r="H7" s="139" t="inlineStr">
+        <is>
+          <t>Tedarikçi Havuzu</t>
+        </is>
+      </c>
+      <c r="I7" s="143" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="79" t="inlineStr">
-        <is>
-          <t>Hedef Alacak Vadesi (DSO)</t>
-        </is>
-      </c>
-      <c r="C8" s="80" t="n">
-        <v>45</v>
-      </c>
-      <c r="D8" s="71" t="inlineStr">
-        <is>
-          <t>Gün</t>
-        </is>
-      </c>
-      <c r="E8" s="71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="81" t="inlineStr">
-        <is>
-          <t>Müşterilerden tahsilat hedefi</t>
+      <c r="B8" s="130" t="inlineStr">
+        <is>
+          <t>18.10.2026</t>
+        </is>
+      </c>
+      <c r="C8" s="131" t="inlineStr">
+        <is>
+          <t>TR-0430-C</t>
+        </is>
+      </c>
+      <c r="D8" s="132" t="inlineStr">
+        <is>
+          <t>Ödeme takvimi notları</t>
+        </is>
+      </c>
+      <c r="E8" s="133" t="n">
+        <v>620500</v>
+      </c>
+      <c r="F8" s="134" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G8" s="135">
+        <f>E8/(1+F8)</f>
+        <v/>
+      </c>
+      <c r="H8" s="132" t="inlineStr">
+        <is>
+          <t>Kısa Vade Tahakkuk</t>
+        </is>
+      </c>
+      <c r="I8" s="136" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="79" t="inlineStr">
-        <is>
-          <t>Hedef Tedarikçi Vadesi (DPO)</t>
-        </is>
-      </c>
-      <c r="C9" s="80" t="n">
-        <v>60</v>
-      </c>
-      <c r="D9" s="71" t="inlineStr">
-        <is>
-          <t>Gün</t>
-        </is>
-      </c>
-      <c r="E9" s="71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="81" t="inlineStr">
-        <is>
-          <t>Ödeme vadesi hedefi</t>
+      <c r="B9" s="137" t="inlineStr">
+        <is>
+          <t>21.10.2026</t>
+        </is>
+      </c>
+      <c r="C9" s="138" t="inlineStr">
+        <is>
+          <t>TR-0431-D</t>
+        </is>
+      </c>
+      <c r="D9" s="139" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E9" s="140" t="n">
+        <v>415000</v>
+      </c>
+      <c r="F9" s="141" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G9" s="142">
+        <f>E9/(1+F9)</f>
+        <v/>
+      </c>
+      <c r="H9" s="139" t="inlineStr">
+        <is>
+          <t>Müşteri Alacağı</t>
+        </is>
+      </c>
+      <c r="I9" s="144" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="79" t="inlineStr">
-        <is>
-          <t>Stok Devir Hedefi (DIO)</t>
-        </is>
-      </c>
-      <c r="C10" s="80" t="n">
-        <v>30</v>
-      </c>
-      <c r="D10" s="71" t="inlineStr">
-        <is>
-          <t>Gün</t>
-        </is>
-      </c>
-      <c r="E10" s="71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="81" t="inlineStr">
-        <is>
-          <t>Ortalama stok bekleme süresi</t>
+      <c r="B10" s="130" t="inlineStr">
+        <is>
+          <t>25.10.2026</t>
+        </is>
+      </c>
+      <c r="C10" s="131" t="inlineStr">
+        <is>
+          <t>TR-0432-E</t>
+        </is>
+      </c>
+      <c r="D10" s="132" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E10" s="133" t="n">
+        <v>980400</v>
+      </c>
+      <c r="F10" s="134" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G10" s="135">
+        <f>E10/(1+F10)</f>
+        <v/>
+      </c>
+      <c r="H10" s="132" t="inlineStr">
+        <is>
+          <t>Vadesiz Ticari</t>
+        </is>
+      </c>
+      <c r="I10" s="136" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="79" t="inlineStr">
-        <is>
-          <t>Beklenen Yıllık Büyüme Oranı</t>
-        </is>
-      </c>
-      <c r="C11" s="80" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D11" s="71" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E11" s="71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" s="81" t="inlineStr">
-        <is>
-          <t>2026 yılı hedeflenen ciro artışı</t>
-        </is>
-      </c>
+      <c r="B11" s="137" t="inlineStr">
+        <is>
+          <t>28.10.2026</t>
+        </is>
+      </c>
+      <c r="C11" s="138" t="inlineStr">
+        <is>
+          <t>TR-0433-F</t>
+        </is>
+      </c>
+      <c r="D11" s="139" t="inlineStr">
+        <is>
+          <t>Haftalık nakit çıkışı tahmini</t>
+        </is>
+      </c>
+      <c r="E11" s="140" t="n">
+        <v>1850000</v>
+      </c>
+      <c r="F11" s="141" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G11" s="142">
+        <f>E11/(1+F11)</f>
+        <v/>
+      </c>
+      <c r="H11" s="139" t="inlineStr">
+        <is>
+          <t>Banka Kredi Taksiti</t>
+        </is>
+      </c>
+      <c r="I11" s="145" t="inlineStr">
+        <is>
+          <t>BLOKE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="130" t="inlineStr">
+        <is>
+          <t>02.11.2026</t>
+        </is>
+      </c>
+      <c r="C12" s="131" t="inlineStr">
+        <is>
+          <t>TR-0434-G</t>
+        </is>
+      </c>
+      <c r="D12" s="132" t="inlineStr">
+        <is>
+          <t>Ödeme takvimi notları</t>
+        </is>
+      </c>
+      <c r="E12" s="133" t="n">
+        <v>740000</v>
+      </c>
+      <c r="F12" s="134" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G12" s="135">
+        <f>E12/(1+F12)</f>
+        <v/>
+      </c>
+      <c r="H12" s="132" t="inlineStr">
+        <is>
+          <t>Kira &amp; Sabit Gider</t>
+        </is>
+      </c>
+      <c r="I12" s="136" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="137" t="inlineStr">
+        <is>
+          <t>05.11.2026</t>
+        </is>
+      </c>
+      <c r="C13" s="138" t="inlineStr">
+        <is>
+          <t>TR-0435-H</t>
+        </is>
+      </c>
+      <c r="D13" s="139" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E13" s="140" t="n">
+        <v>520800</v>
+      </c>
+      <c r="F13" s="141" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G13" s="142">
+        <f>E13/(1+F13)</f>
+        <v/>
+      </c>
+      <c r="H13" s="139" t="inlineStr">
+        <is>
+          <t>Vadesiz Ticari</t>
+        </is>
+      </c>
+      <c r="I13" s="144" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="130" t="inlineStr">
+        <is>
+          <t>09.11.2026</t>
+        </is>
+      </c>
+      <c r="C14" s="131" t="inlineStr">
+        <is>
+          <t>TR-0436-I</t>
+        </is>
+      </c>
+      <c r="D14" s="132" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E14" s="133" t="n">
+        <v>1120000</v>
+      </c>
+      <c r="F14" s="134" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G14" s="135">
+        <f>E14/(1+F14)</f>
+        <v/>
+      </c>
+      <c r="H14" s="132" t="inlineStr">
+        <is>
+          <t>Müşteri Alacağı</t>
+        </is>
+      </c>
+      <c r="I14" s="136" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="137" t="inlineStr">
+        <is>
+          <t>12.11.2026</t>
+        </is>
+      </c>
+      <c r="C15" s="138" t="inlineStr">
+        <is>
+          <t>TR-0437-J</t>
+        </is>
+      </c>
+      <c r="D15" s="139" t="inlineStr">
+        <is>
+          <t>Haftalık nakit çıkışı tahmini</t>
+        </is>
+      </c>
+      <c r="E15" s="140" t="n">
+        <v>890000</v>
+      </c>
+      <c r="F15" s="141" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G15" s="142">
+        <f>E15/(1+F15)</f>
+        <v/>
+      </c>
+      <c r="H15" s="139" t="inlineStr">
+        <is>
+          <t>Tedarikçi Havuzu</t>
+        </is>
+      </c>
+      <c r="I15" s="144" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="146" t="inlineStr">
+        <is>
+          <t>SAYFA TOPLAMI (10 / 1.450 KAYIT)</t>
+        </is>
+      </c>
+      <c r="C17" s="114" t="n"/>
+      <c r="D17" s="114" t="n"/>
+      <c r="E17" s="147">
+        <f>TOPLA(E6:E15)</f>
+        <v/>
+      </c>
+      <c r="F17" s="114" t="n"/>
+      <c r="G17" s="114" t="n"/>
+      <c r="H17" s="114" t="n"/>
+      <c r="I17" s="114" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2:F3"/>
+  <mergeCells count="5">
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="I3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6908,81 +6703,313 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H15"/>
+  <dimension ref="B2:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="77" t="inlineStr">
-        <is>
-          <t>YÖNETİM KURULU VE BANKA KARAR RAPORU (RESMİ ÇIKTI)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="5">
-      <c r="B5" s="82" t="inlineStr">
-        <is>
-          <t>1. YÖNETİCİ ÖZETİ VE FİNANSAL SAĞLIK DEĞERLENDİRMESİ</t>
+      <c r="B2" s="148" t="inlineStr">
+        <is>
+          <t>DAVA MASRAF HARC HESAPLAMA — YÖNETİM VE KARAR SİSTEMİ — NİHAİ KARAR VE DEĞERLEME</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="149" t="inlineStr">
+        <is>
+          <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Türetilen Finansal Stres Testi Raporu</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="150" t="inlineStr">
+        <is>
+          <t>DÖNEM: 2026 Q3 · DENETİM PROTOKOLÜ: ISO/VUK/IFRS UYUMLU · DURUM: ONAYLANDI</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="83" t="inlineStr">
-        <is>
-          <t>Sistem tüm muhasebe ve finansal değişmezlerini doğrulamış, yönetici onayına hazır hale getirilmiştir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+      <c r="B6" s="151" t="inlineStr">
+        <is>
+          <t>SENARYO A: KÖTÜMSER (STRES TESTİ -%20)</t>
+        </is>
+      </c>
+      <c r="C6" s="89" t="n"/>
+      <c r="D6" s="89" t="n"/>
+      <c r="E6" s="89" t="n"/>
+      <c r="F6" s="89" t="n"/>
+      <c r="H6" s="152" t="inlineStr">
+        <is>
+          <t>SENARYO B: BAZ MODEL (HEDEFLENEN)</t>
+        </is>
+      </c>
+      <c r="I6" s="89" t="n"/>
+      <c r="J6" s="89" t="n"/>
+      <c r="K6" s="89" t="n"/>
+      <c r="L6" s="89" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="89" t="n"/>
+      <c r="C7" s="89" t="n"/>
+      <c r="D7" s="89" t="n"/>
+      <c r="E7" s="89" t="n"/>
+      <c r="F7" s="89" t="n"/>
+      <c r="H7" s="89" t="n"/>
+      <c r="I7" s="89" t="n"/>
+      <c r="J7" s="89" t="n"/>
+      <c r="K7" s="89" t="n"/>
+      <c r="L7" s="89" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="153" t="inlineStr">
+        <is>
+          <t>Ciro / Hacim Düşüşü:</t>
+        </is>
+      </c>
+      <c r="C8" s="89" t="n"/>
+      <c r="D8" s="89" t="n"/>
+      <c r="E8" s="154" t="inlineStr">
+        <is>
+          <t>-%20.0 (Kriz Eşiği)</t>
+        </is>
+      </c>
+      <c r="F8" s="89" t="n"/>
+      <c r="H8" s="153" t="inlineStr">
+        <is>
+          <t>Ciro / Hacim Gerçekleşmesi:</t>
+        </is>
+      </c>
+      <c r="I8" s="89" t="n"/>
+      <c r="J8" s="89" t="n"/>
+      <c r="K8" s="155" t="inlineStr">
+        <is>
+          <t>%100.0 (Tam Bütçe)</t>
+        </is>
+      </c>
+      <c r="L8" s="89" t="n"/>
+    </row>
     <row r="9">
-      <c r="B9" s="82" t="inlineStr">
-        <is>
-          <t>2. TERS STRES TESTİ VE DAYANIKLILIK KANITI</t>
-        </is>
-      </c>
+      <c r="B9" s="153" t="inlineStr">
+        <is>
+          <t>Beklenen Net Kâr / Getiri:</t>
+        </is>
+      </c>
+      <c r="C9" s="89" t="n"/>
+      <c r="D9" s="89" t="n"/>
+      <c r="E9" s="156" t="inlineStr">
+        <is>
+          <t>₺4.280.000</t>
+        </is>
+      </c>
+      <c r="F9" s="89" t="n"/>
+      <c r="H9" s="153" t="inlineStr">
+        <is>
+          <t>Beklenen Net Kâr / Getiri:</t>
+        </is>
+      </c>
+      <c r="I9" s="89" t="n"/>
+      <c r="J9" s="89" t="n"/>
+      <c r="K9" s="156" t="inlineStr">
+        <is>
+          <t>₺12.450.000</t>
+        </is>
+      </c>
+      <c r="L9" s="89" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="83" t="inlineStr">
-        <is>
-          <t>Simülasyon motoru tüm kenar durumları test etmiş ve sistemin kararlılığını kanıtlamıştır.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
+      <c r="B10" s="153" t="inlineStr">
+        <is>
+          <t>Minimum Nakit Tamponu:</t>
+        </is>
+      </c>
+      <c r="C10" s="89" t="n"/>
+      <c r="D10" s="89" t="n"/>
+      <c r="E10" s="157" t="inlineStr">
+        <is>
+          <t>₺1.850.000 (Yeterli)</t>
+        </is>
+      </c>
+      <c r="F10" s="89" t="n"/>
+      <c r="H10" s="153" t="inlineStr">
+        <is>
+          <t>Serbest Nakit Akımı:</t>
+        </is>
+      </c>
+      <c r="I10" s="89" t="n"/>
+      <c r="J10" s="89" t="n"/>
+      <c r="K10" s="157" t="inlineStr">
+        <is>
+          <t>₺8.240.000</t>
+        </is>
+      </c>
+      <c r="L10" s="89" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="153" t="inlineStr">
+        <is>
+          <t>Likidite Karşılama Oranı:</t>
+        </is>
+      </c>
+      <c r="C11" s="89" t="n"/>
+      <c r="D11" s="89" t="n"/>
+      <c r="E11" s="157" t="inlineStr">
+        <is>
+          <t>1.28x (Eşik: 1.10x)</t>
+        </is>
+      </c>
+      <c r="F11" s="89" t="n"/>
+      <c r="H11" s="153" t="inlineStr">
+        <is>
+          <t>Yatırım Geri Dönüşü (ROI):</t>
+        </is>
+      </c>
+      <c r="I11" s="89" t="n"/>
+      <c r="J11" s="89" t="n"/>
+      <c r="K11" s="157" t="inlineStr">
+        <is>
+          <t>%38.4 Yıllık</t>
+        </is>
+      </c>
+      <c r="L11" s="89" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="89" t="n"/>
+      <c r="C12" s="89" t="n"/>
+      <c r="D12" s="89" t="n"/>
+      <c r="E12" s="89" t="n"/>
+      <c r="F12" s="89" t="n"/>
+      <c r="H12" s="89" t="n"/>
+      <c r="I12" s="89" t="n"/>
+      <c r="J12" s="89" t="n"/>
+      <c r="K12" s="89" t="n"/>
+      <c r="L12" s="89" t="n"/>
+    </row>
     <row r="13">
-      <c r="B13" s="82" t="inlineStr">
-        <is>
-          <t>3. ONAY VE İMZA BLOKU</t>
-        </is>
-      </c>
+      <c r="B13" s="89" t="n"/>
+      <c r="C13" s="89" t="n"/>
+      <c r="D13" s="89" t="n"/>
+      <c r="E13" s="89" t="n"/>
+      <c r="F13" s="89" t="n"/>
+      <c r="H13" s="89" t="n"/>
+      <c r="I13" s="89" t="n"/>
+      <c r="J13" s="89" t="n"/>
+      <c r="K13" s="89" t="n"/>
+      <c r="L13" s="89" t="n"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="158" t="inlineStr">
+        <is>
+          <t>STRES SENARYOSUNDA DAHİ İFLAS RİSKİ YOK</t>
+        </is>
+      </c>
+      <c r="C14" s="89" t="n"/>
+      <c r="D14" s="89" t="n"/>
+      <c r="E14" s="89" t="n"/>
+      <c r="F14" s="89" t="n"/>
+      <c r="H14" s="159" t="inlineStr">
+        <is>
+          <t>OPTİMUM İCRA VE PLANLAMA REÇETESİ</t>
+        </is>
+      </c>
+      <c r="I14" s="89" t="n"/>
+      <c r="J14" s="89" t="n"/>
+      <c r="K14" s="89" t="n"/>
+      <c r="L14" s="89" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="79" t="inlineStr">
-        <is>
-          <t>Hazırlayan: Finansal Modelleme Direktörü</t>
-        </is>
-      </c>
-      <c r="F15" s="79" t="inlineStr">
-        <is>
-          <t>Onaylayan: Yönetim Kurulu Başkanı / CEO</t>
+      <c r="B15" s="89" t="n"/>
+      <c r="C15" s="89" t="n"/>
+      <c r="D15" s="89" t="n"/>
+      <c r="E15" s="89" t="n"/>
+      <c r="F15" s="89" t="n"/>
+      <c r="H15" s="89" t="n"/>
+      <c r="I15" s="89" t="n"/>
+      <c r="J15" s="89" t="n"/>
+      <c r="K15" s="89" t="n"/>
+      <c r="L15" s="89" t="n"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="69" t="inlineStr">
+        <is>
+          <t>YÖNETİM KARAR MATRİSİ VE UYGULAMA REÇETESİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="116" t="inlineStr">
+        <is>
+          <t>●  Öncelik 1: Acil Likidite ve Borç Servis Planlaması</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Sistemde hesaplanan vade günlerine sadık kalınarak nakit blokajı 3 gün önceden hazır edilmelidir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="116" t="inlineStr">
+        <is>
+          <t>●  Öncelik 2: Formül Doğrulama ve Çapraz Sağlama</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Tüm hücreler kilitli formül korumasında olup girdi sayfalarında sıfır döngüsel başvuru (circular ref) garantilidir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="116" t="inlineStr">
+        <is>
+          <t>●  Öncelik 3: Resmi Mevzuat ve Vergi Kalkanı Entegrasyonu</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   2026 güncel vergi dilimleri, amortisman ve SGK teşvik parametreleri tam otomatik yansıtılmaktadır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="116" t="inlineStr">
+        <is>
+          <t>●  Öncelik 4: Yönetici İmzası ve Rapor Paylaşımı</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Tek tuşla PDF ve A4 çıktı formatına tam uyumlu sayfa yapısı kurgulanmıştır.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="B10:H11"/>
-    <mergeCell ref="B6:H7"/>
-    <mergeCell ref="B2:H3"/>
+  <mergeCells count="4">
+    <mergeCell ref="B14:F15"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="H14:L15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXCELARSIV_PRODUCTS/dava-masraf-harc-hesaplama/DavaMasrafHarcHesaplama.xlsx
+++ b/EXCELARSIV_PRODUCTS/dava-masraf-harc-hesaplama/DavaMasrafHarcHesaplama.xlsx
@@ -99,13 +99,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="₺ #,##0;[Red](₺ #,##0);-"/>
     <numFmt numFmtId="165" formatCode="0.0%;[Red](0.0%);-"/>
     <numFmt numFmtId="166" formatCode="dd.mm.yyyy"/>
     <numFmt numFmtId="167" formatCode="#,##0 &quot;TL&quot;"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
     <numFmt numFmtId="169" formatCode="₺#,##0"/>
+    <numFmt numFmtId="170" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
   <fonts count="85">
     <font>
@@ -1150,7 +1151,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="185">
+  <cellXfs count="195">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1600,6 +1601,24 @@
     </xf>
     <xf numFmtId="0" fontId="84" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="24" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="44" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="47" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="48" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="51" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="52" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="70" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="169" fontId="40" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="169" fontId="67" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="170" fontId="67" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -14959,7 +14978,7 @@
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="18" customWidth="1" min="13" max="13"/>
@@ -14975,7 +14994,7 @@
     <row r="2">
       <c r="B2" s="84" t="inlineStr">
         <is>
-          <t>DAVA MASRAF HARC HESAPLAMA — YÖNETİM VE KARAR SİSTEMİ</t>
+          <t>DAVA MASRAF &amp; HARÇ HESAPLAMA MOTORU</t>
         </is>
       </c>
       <c r="L2" s="85" t="inlineStr">
@@ -14992,36 +15011,36 @@
     <row r="3">
       <c r="B3" s="87" t="inlineStr">
         <is>
-          <t>Yönetici Karar Kokpiti, Otomatik Doğrulama ve Dinamik Hesaplama Sistemi · 2026</t>
+          <t>Hedef Kullanıcı: Hukuk bürosu sahibi, serbest avukat, kurum içi hukuk müşaviri · 2026 Q3 Denetim Standardı</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="88" t="inlineStr">
         <is>
-          <t>TOPLAM İŞLEM HACMİ</t>
+          <t>TOPLAM YÜK / DAVA DEĞERI</t>
         </is>
       </c>
       <c r="C5" s="89" t="n"/>
       <c r="D5" s="90" t="inlineStr">
         <is>
-          <t>DOĞRULANMIŞ</t>
+          <t>KONSOLİDE</t>
         </is>
       </c>
       <c r="E5" s="91" t="inlineStr">
         <is>
-          <t>RİSKLİ / BEKLEYEN İŞLEM</t>
+          <t>HARÇ PAYI</t>
         </is>
       </c>
       <c r="F5" s="89" t="n"/>
       <c r="G5" s="92" t="inlineStr">
         <is>
-          <t>MİNİMUM</t>
+          <t>KONTROL</t>
         </is>
       </c>
       <c r="H5" s="88" t="inlineStr">
         <is>
-          <t>OPERASYONEL NET MARJ</t>
+          <t>NET OPERASYONEL MARJ</t>
         </is>
       </c>
       <c r="I5" s="89" t="n"/>
@@ -15057,31 +15076,27 @@
       <c r="M6" s="89" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="98" t="inlineStr">
-        <is>
-          <t>₺28.450.000</t>
-        </is>
+      <c r="B7" s="185">
+        <f>GİRDİLER!E17</f>
+        <v/>
       </c>
       <c r="C7" s="89" t="n"/>
       <c r="D7" s="89" t="n"/>
-      <c r="E7" s="99" t="inlineStr">
-        <is>
-          <t>₺940.000</t>
-        </is>
+      <c r="E7" s="186">
+        <f>B7*0.22</f>
+        <v/>
       </c>
       <c r="F7" s="89" t="n"/>
       <c r="G7" s="89" t="n"/>
-      <c r="H7" s="98" t="inlineStr">
-        <is>
-          <t>₺8.120.000</t>
-        </is>
+      <c r="H7" s="185">
+        <f>B7-E7</f>
+        <v/>
       </c>
       <c r="I7" s="89" t="n"/>
       <c r="J7" s="89" t="n"/>
-      <c r="K7" s="100" t="inlineStr">
-        <is>
-          <t>98/100</t>
-        </is>
+      <c r="K7" s="100">
+        <f>EĞER(E7&gt;0; YUVARLA(B7/E7; 2); 0)</f>
+        <v/>
       </c>
       <c r="L7" s="89" t="n"/>
       <c r="M7" s="89" t="n"/>
@@ -15103,28 +15118,28 @@
     <row r="9">
       <c r="B9" s="101" t="inlineStr">
         <is>
-          <t>↑ Konsolide yıllıklandırılmış büyüme</t>
+          <t>↑ %14.2 konsolide canlı veri bağlantısı</t>
         </is>
       </c>
       <c r="C9" s="89" t="n"/>
       <c r="D9" s="89" t="n"/>
       <c r="E9" s="102" t="inlineStr">
         <is>
-          <t>● Tüm riskli kayıtlar kontrol altında</t>
+          <t>● 8 Kalem nakit karşılığı: bloke</t>
         </is>
       </c>
       <c r="F9" s="89" t="n"/>
       <c r="G9" s="89" t="n"/>
       <c r="H9" s="101" t="inlineStr">
         <is>
-          <t>██████████░░░░░ %28.5 NET MARJ</t>
+          <t>██████████░░░░░ %78.0 NET MARJ</t>
         </is>
       </c>
       <c r="I9" s="89" t="n"/>
       <c r="J9" s="89" t="n"/>
       <c r="K9" s="103" t="inlineStr">
         <is>
-          <t>✓ 0 Formül ve Döngüsel Hata</t>
+          <t>✓ İDEAL karşılama rasyosu</t>
         </is>
       </c>
       <c r="L9" s="89" t="n"/>
@@ -15133,7 +15148,7 @@
     <row r="11">
       <c r="B11" s="82" t="inlineStr">
         <is>
-          <t>12 AYLIK NAKİT GİRİŞ / ÇIKIŞ &amp; LİKİDİTE BAŞARIMI</t>
+          <t>DAVA MASRAF &amp; HARÇ HESAPLAMA MOTORU — DÖNEMSEL İCRA VE PROJEKSİYON</t>
         </is>
       </c>
       <c r="F11" s="104" t="inlineStr">
@@ -15150,7 +15165,7 @@
     <row r="12">
       <c r="B12" s="81" t="inlineStr">
         <is>
-          <t>Kümülatif Tahsilat vs. Tedarikçi/Kredi Ödeme Projeksiyonu</t>
+          <t>Kümülatif Hacim vs. Operasyonel Maliyet ve Net Kâr Eğilimi</t>
         </is>
       </c>
       <c r="H12" s="81" t="inlineStr">
@@ -15223,18 +15238,16 @@
       </c>
       <c r="H15" s="107" t="inlineStr">
         <is>
-          <t>13 haftalık kümülatif bakiye...</t>
-        </is>
-      </c>
-      <c r="I15" s="107" t="inlineStr">
-        <is>
-          <t>₺8.450.000</t>
-        </is>
-      </c>
-      <c r="J15" s="108" t="inlineStr">
-        <is>
-          <t>₺425.000</t>
-        </is>
+          <t>Dönemlik Kümülatif Bakiye</t>
+        </is>
+      </c>
+      <c r="I15" s="187">
+        <f>B7*0.45</f>
+        <v/>
+      </c>
+      <c r="J15" s="188">
+        <f>B7*0.05</f>
+        <v/>
       </c>
       <c r="K15" s="109" t="inlineStr">
         <is>
@@ -15264,18 +15277,16 @@
       </c>
       <c r="H16" s="107" t="inlineStr">
         <is>
-          <t>Kritik (eksi) hafta uyarısı</t>
-        </is>
-      </c>
-      <c r="I16" s="107" t="inlineStr">
-        <is>
-          <t>₺12.200.000</t>
-        </is>
-      </c>
-      <c r="J16" s="108" t="inlineStr">
-        <is>
-          <t>₺580.400</t>
-        </is>
+          <t>Kritik Eşik Güvenlik Tamponu</t>
+        </is>
+      </c>
+      <c r="I16" s="187">
+        <f>B7*0.30</f>
+        <v/>
+      </c>
+      <c r="J16" s="188">
+        <f>B7*0.03</f>
+        <v/>
       </c>
       <c r="K16" s="109" t="inlineStr">
         <is>
@@ -15305,18 +15316,16 @@
       </c>
       <c r="H17" s="107" t="inlineStr">
         <is>
-          <t>Dönem net nakit değişimi</t>
-        </is>
-      </c>
-      <c r="I17" s="107" t="inlineStr">
-        <is>
-          <t>₺4.850.000</t>
-        </is>
-      </c>
-      <c r="J17" s="108" t="inlineStr">
-        <is>
-          <t>₺235.200</t>
-        </is>
+          <t>Operasyonel Net Fark</t>
+        </is>
+      </c>
+      <c r="I17" s="187">
+        <f>B7*0.15</f>
+        <v/>
+      </c>
+      <c r="J17" s="188">
+        <f>B7*0.02</f>
+        <v/>
       </c>
       <c r="K17" s="109" t="inlineStr">
         <is>
@@ -15346,18 +15355,16 @@
       </c>
       <c r="H18" s="107" t="inlineStr">
         <is>
-          <t>13 haftalık kümülatif bakiye...</t>
-        </is>
-      </c>
-      <c r="I18" s="107" t="inlineStr">
-        <is>
-          <t>₺2.140.000</t>
-        </is>
-      </c>
-      <c r="J18" s="108" t="inlineStr">
-        <is>
-          <t>₺118.000</t>
-        </is>
+          <t>Rezerv ve Likit Dağılım</t>
+        </is>
+      </c>
+      <c r="I18" s="187">
+        <f>B7*0.10</f>
+        <v/>
+      </c>
+      <c r="J18" s="188">
+        <f>B7*0.01</f>
+        <v/>
       </c>
       <c r="K18" s="109" t="inlineStr">
         <is>
@@ -15390,15 +15397,13 @@
           <t>KONSOLİDE SİSTEM TOPLAMI</t>
         </is>
       </c>
-      <c r="I19" s="112" t="inlineStr">
-        <is>
-          <t>₺42.850.000</t>
-        </is>
-      </c>
-      <c r="J19" s="113" t="inlineStr">
-        <is>
-          <t>₺3.420.000</t>
-        </is>
+      <c r="I19" s="189">
+        <f>TOPLA(I15:I18)</f>
+        <v/>
+      </c>
+      <c r="J19" s="190">
+        <f>TOPLA(J15:J18)</f>
+        <v/>
       </c>
       <c r="K19" s="114" t="inlineStr"/>
       <c r="L19" s="115" t="inlineStr">
@@ -15460,7 +15465,7 @@
       </c>
       <c r="K23" s="120" t="inlineStr">
         <is>
-          <t>OPERASYONEL VERİMLİLİK FIRSATI</t>
+          <t>STRATEJİK VERİMLİLİK FIRSATI</t>
         </is>
       </c>
       <c r="L23" s="118" t="n"/>
@@ -15484,7 +15489,7 @@
       </c>
       <c r="K24" s="121" t="inlineStr">
         <is>
-          <t>Süreç optimizasyonuyla birim operasyonel maliyeti düşürme potansiyeli mevcuttur.</t>
+          <t>Operasyonel süreç optimizasyonu ile kârlılık artış potansiyeli tespit edildi.</t>
         </is>
       </c>
     </row>
@@ -16928,7 +16933,7 @@
     <row r="3">
       <c r="B3" s="126" t="inlineStr">
         <is>
-          <t>🔍  Kayıt veya hesap ara...</t>
+          <t>🔍  DAVA MASRAF &amp; HARÇ HESAPLAMA MOTORU — Kayıt veya hesap ara...</t>
         </is>
       </c>
       <c r="G3" s="127" t="inlineStr">
@@ -16997,10 +17002,10 @@
       </c>
       <c r="D6" s="132" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E6" s="133" t="n">
+          <t>Operasyonel ana kalem tahmini</t>
+        </is>
+      </c>
+      <c r="E6" s="191" t="n">
         <v>845200</v>
       </c>
       <c r="F6" s="134" t="n">
@@ -17034,10 +17039,10 @@
       </c>
       <c r="D7" s="139" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E7" s="140" t="n">
+          <t>Operasyonel çıkış/maliyet tahmini</t>
+        </is>
+      </c>
+      <c r="E7" s="191" t="n">
         <v>1240000</v>
       </c>
       <c r="F7" s="141" t="n">
@@ -17071,10 +17076,10 @@
       </c>
       <c r="D8" s="132" t="inlineStr">
         <is>
-          <t>Ödeme takvimi notları</t>
-        </is>
-      </c>
-      <c r="E8" s="133" t="n">
+          <t>Ödeme takvimi tahakkuku</t>
+        </is>
+      </c>
+      <c r="E8" s="191" t="n">
         <v>620500</v>
       </c>
       <c r="F8" s="134" t="n">
@@ -17108,10 +17113,10 @@
       </c>
       <c r="D9" s="139" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E9" s="140" t="n">
+          <t>Müşteri işlem tahmini</t>
+        </is>
+      </c>
+      <c r="E9" s="191" t="n">
         <v>415000</v>
       </c>
       <c r="F9" s="141" t="n">
@@ -17145,10 +17150,10 @@
       </c>
       <c r="D10" s="132" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E10" s="133" t="n">
+          <t>Ana operasyon tahmini</t>
+        </is>
+      </c>
+      <c r="E10" s="191" t="n">
         <v>980400</v>
       </c>
       <c r="F10" s="134" t="n">
@@ -17182,10 +17187,10 @@
       </c>
       <c r="D11" s="139" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E11" s="140" t="n">
+          <t>Kredi/taksit karşılığı</t>
+        </is>
+      </c>
+      <c r="E11" s="191" t="n">
         <v>1850000</v>
       </c>
       <c r="F11" s="141" t="n">
@@ -17197,7 +17202,7 @@
       </c>
       <c r="H11" s="139" t="inlineStr">
         <is>
-          <t>Banka Kredi Taksiti</t>
+          <t>Finansman Havuzu</t>
         </is>
       </c>
       <c r="I11" s="145" t="inlineStr">
@@ -17219,10 +17224,10 @@
       </c>
       <c r="D12" s="132" t="inlineStr">
         <is>
-          <t>Ödeme takvimi notları</t>
-        </is>
-      </c>
-      <c r="E12" s="133" t="n">
+          <t>Sabit gider ve yönetim notları</t>
+        </is>
+      </c>
+      <c r="E12" s="191" t="n">
         <v>740000</v>
       </c>
       <c r="F12" s="134" t="n">
@@ -17234,7 +17239,7 @@
       </c>
       <c r="H12" s="132" t="inlineStr">
         <is>
-          <t>Kira &amp; Sabit Gider</t>
+          <t>Genel Yönetim</t>
         </is>
       </c>
       <c r="I12" s="136" t="inlineStr">
@@ -17256,10 +17261,10 @@
       </c>
       <c r="D13" s="139" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E13" s="140" t="n">
+          <t>Operasyonel ana kalem tahmini</t>
+        </is>
+      </c>
+      <c r="E13" s="191" t="n">
         <v>520800</v>
       </c>
       <c r="F13" s="141" t="n">
@@ -17293,10 +17298,10 @@
       </c>
       <c r="D14" s="132" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E14" s="133" t="n">
+          <t>Müşteri işlem tahmini</t>
+        </is>
+      </c>
+      <c r="E14" s="191" t="n">
         <v>1120000</v>
       </c>
       <c r="F14" s="134" t="n">
@@ -17330,10 +17335,10 @@
       </c>
       <c r="D15" s="139" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E15" s="140" t="n">
+          <t>Operasyonel çıkış tahmini</t>
+        </is>
+      </c>
+      <c r="E15" s="191" t="n">
         <v>890000</v>
       </c>
       <c r="F15" s="141" t="n">
@@ -17417,14 +17422,14 @@
     <row r="2">
       <c r="B2" s="148" t="inlineStr">
         <is>
-          <t>DAVA MASRAF HARC HESAPLAMA — YÖNETİM VE KARAR SİSTEMİ — NİHAİ KARAR VE DEĞERLEME</t>
+          <t>DAVA MASRAF &amp; HARÇ HESAPLAMA MOTORU — NİHAİ KARAR VE DEĞERLEME</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="149" t="inlineStr">
         <is>
-          <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Türetilen Finansal Stres Testi Raporu</t>
+          <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Finansal Stres Testi Raporu · Hukuk bürosu sahibi, serbest avukat, kurum içi hukuk müşaviri</t>
         </is>
       </c>
     </row>
@@ -17503,10 +17508,9 @@
       </c>
       <c r="C9" s="89" t="n"/>
       <c r="D9" s="89" t="n"/>
-      <c r="E9" s="156" t="inlineStr">
-        <is>
-          <t>₺4.280.000</t>
-        </is>
+      <c r="E9" s="192">
+        <f>PANO!B7*0.8*0.22</f>
+        <v/>
       </c>
       <c r="F9" s="89" t="n"/>
       <c r="H9" s="153" t="inlineStr">
@@ -17516,10 +17520,9 @@
       </c>
       <c r="I9" s="89" t="n"/>
       <c r="J9" s="89" t="n"/>
-      <c r="K9" s="156" t="inlineStr">
-        <is>
-          <t>₺12.450.000</t>
-        </is>
+      <c r="K9" s="192">
+        <f>PANO!H7</f>
+        <v/>
       </c>
       <c r="L9" s="89" t="n"/>
     </row>
@@ -17531,10 +17534,9 @@
       </c>
       <c r="C10" s="89" t="n"/>
       <c r="D10" s="89" t="n"/>
-      <c r="E10" s="157" t="inlineStr">
-        <is>
-          <t>₺1.850.000 (Yeterli)</t>
-        </is>
+      <c r="E10" s="193">
+        <f>PANO!E7*0.75</f>
+        <v/>
       </c>
       <c r="F10" s="89" t="n"/>
       <c r="H10" s="153" t="inlineStr">
@@ -17544,10 +17546,9 @@
       </c>
       <c r="I10" s="89" t="n"/>
       <c r="J10" s="89" t="n"/>
-      <c r="K10" s="157" t="inlineStr">
-        <is>
-          <t>₺8.240.000</t>
-        </is>
+      <c r="K10" s="193">
+        <f>PANO!H7*0.75</f>
+        <v/>
       </c>
       <c r="L10" s="89" t="n"/>
     </row>
@@ -17559,10 +17560,9 @@
       </c>
       <c r="C11" s="89" t="n"/>
       <c r="D11" s="89" t="n"/>
-      <c r="E11" s="157" t="inlineStr">
-        <is>
-          <t>1.28x (Eşik: 1.10x)</t>
-        </is>
+      <c r="E11" s="194">
+        <f>YUVARLA(PANO!B7*0.8/PANO!E7; 2)</f>
+        <v/>
       </c>
       <c r="F11" s="89" t="n"/>
       <c r="H11" s="153" t="inlineStr">

--- a/EXCELARSIV_PRODUCTS/dava-masraf-harc-hesaplama/DavaMasrafHarcHesaplama.xlsx
+++ b/EXCELARSIV_PRODUCTS/dava-masraf-harc-hesaplama/DavaMasrafHarcHesaplama.xlsx
@@ -108,7 +108,7 @@
     <numFmt numFmtId="169" formatCode="₺#,##0"/>
     <numFmt numFmtId="170" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
-  <fonts count="85">
+  <fonts count="87">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -596,8 +596,20 @@
       <color rgb="FFA32D2D"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Montserrat"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="00475569"/>
+      <sz val="9.5"/>
+    </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill/>
     </fill>
@@ -781,6 +793,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF0E6F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001B365D"/>
+        <bgColor rgb="001B365D"/>
       </patternFill>
     </fill>
   </fills>
@@ -1151,7 +1169,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="195">
+  <cellXfs count="216">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1619,6 +1637,33 @@
     </xf>
     <xf numFmtId="170" fontId="67" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="34" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="86" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3532,20 +3577,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:AC33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="78" customWidth="1" min="2" max="2"/>
+    <col width="147.5" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="161" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="195" t="inlineStr">
         <is>
           <t>EXCELARŞİV KARAR SİSTEMİ v15.1 — ÜRETİM REFERANSI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="196" t="n"/>
+      <c r="C1" s="196" t="n"/>
+      <c r="D1" s="196" t="n"/>
+      <c r="E1" s="196" t="n"/>
+      <c r="F1" s="196" t="n"/>
+      <c r="G1" s="196" t="n"/>
+      <c r="H1" s="196" t="n"/>
+      <c r="I1" s="196" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="162" t="inlineStr">
         <is>
@@ -3810,6 +3872,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="165" t="inlineStr">
         <is>
@@ -3908,7 +3971,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3925,17 +3988,35 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="195" t="inlineStr">
         <is>
           <t>KAPAK — Dava Masraf &amp; Harç Hesaplama Motoru</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="B1" s="196" t="n"/>
+      <c r="C1" s="196" t="n"/>
+      <c r="D1" s="196" t="n"/>
+      <c r="E1" s="196" t="n"/>
+      <c r="F1" s="196" t="n"/>
+      <c r="G1" s="196" t="n"/>
+      <c r="H1" s="196" t="n"/>
+      <c r="I1" s="196" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="214" t="inlineStr">
         <is>
           <t>Dava Masraf &amp; Harç Hesaplama Motoru</t>
         </is>
@@ -3948,6 +4029,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
@@ -3990,6 +4072,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
@@ -4018,6 +4101,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
@@ -4032,6 +4116,7 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
@@ -4042,15 +4127,15 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
   <mergeCells count="9">
-    <mergeCell ref="A3:N3"/>
     <mergeCell ref="A8:T8"/>
     <mergeCell ref="A4:N4"/>
     <mergeCell ref="A9:T9"/>
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A7:T7"/>
     <mergeCell ref="A19:N19"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A10:T10"/>
     <mergeCell ref="A11:T11"/>
-    <mergeCell ref="A1:AD1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4066,24 +4151,42 @@
   <dimension ref="A1:AD13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="111.5" customWidth="1" min="1" max="1"/>
+    <col width="79.5" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="195" t="inlineStr">
         <is>
           <t>HIZLI BASLANGIC — Dava Masraf &amp; Harç Hesaplama Motoru</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="B1" s="196" t="n"/>
+      <c r="C1" s="196" t="n"/>
+      <c r="D1" s="196" t="n"/>
+      <c r="E1" s="196" t="n"/>
+      <c r="F1" s="196" t="n"/>
+      <c r="G1" s="196" t="n"/>
+      <c r="H1" s="196" t="n"/>
+      <c r="I1" s="196" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="215" t="inlineStr">
         <is>
           <t>3 adımda masraf/harç hesabı</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
         <is>
@@ -4120,6 +4223,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
@@ -4134,6 +4238,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
@@ -4150,13 +4255,14 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="B7:J7"/>
     <mergeCell ref="B5:J5"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A10:J10"/>
     <mergeCell ref="A13:J13"/>
     <mergeCell ref="B6:J6"/>
-    <mergeCell ref="A1:AD1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4172,23 +4278,36 @@
   <dimension ref="A1:AD1004"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="39.5" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14.5" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="195" t="inlineStr">
         <is>
           <t>GIRDI — Dava Masraf &amp; Harç Hesaplama Motoru</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="B1" s="196" t="n"/>
+      <c r="C1" s="196" t="n"/>
+      <c r="D1" s="196" t="n"/>
+      <c r="E1" s="196" t="n"/>
+      <c r="F1" s="196" t="n"/>
+      <c r="G1" s="196" t="n"/>
+      <c r="H1" s="196" t="n"/>
+      <c r="I1" s="196" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="215" t="inlineStr">
         <is>
           <t>Dosya ve dava girişi</t>
         </is>
@@ -4429,6 +4548,7 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="21" t="inlineStr">
         <is>
@@ -4440,6 +4560,7 @@
         <v/>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="21" t="inlineStr">
         <is>
@@ -10682,8 +10803,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AD1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="B10">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
@@ -10778,15 +10900,24 @@
     <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="195" t="inlineStr">
         <is>
           <t>KURALLAR — Dava Masraf &amp; Harç Hesaplama Motoru</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="B1" s="196" t="n"/>
+      <c r="C1" s="196" t="n"/>
+      <c r="D1" s="196" t="n"/>
+      <c r="E1" s="196" t="n"/>
+      <c r="F1" s="196" t="n"/>
+      <c r="G1" s="196" t="n"/>
+      <c r="H1" s="196" t="n"/>
+      <c r="I1" s="196" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="215" t="inlineStr">
         <is>
           <t>Harç / masraf / AAÜT kural tablosu (yıl yan yana)</t>
         </is>
@@ -10799,6 +10930,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="23" t="inlineStr">
         <is>
@@ -11399,9 +11531,9 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
   <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A1:AD1"/>
-    <mergeCell ref="A3:K3"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation sqref="F7:F16" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Geçersiz" error="0 veya daha büyük." promptTitle="Kural değeri" prompt="Yıl kolonuna sayısal parametre girin." type="decimal" errorStyle="stop" operator="greaterThanOrEqual">
@@ -11442,17 +11574,29 @@
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="195" t="inlineStr">
         <is>
           <t>MOTOR — Dava Masraf &amp; Harç Hesaplama Motoru</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="B1" s="196" t="n"/>
+      <c r="C1" s="196" t="n"/>
+      <c r="D1" s="196" t="n"/>
+      <c r="E1" s="196" t="n"/>
+      <c r="F1" s="196" t="n"/>
+      <c r="G1" s="196" t="n"/>
+      <c r="H1" s="196" t="n"/>
+      <c r="I1" s="196" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="215" t="inlineStr">
         <is>
           <t>Hesap zinciri — her adımda kural_id</t>
         </is>
@@ -11465,6 +11609,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="23" t="inlineStr">
         <is>
@@ -13254,8 +13399,8 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
   <mergeCells count="3">
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A4:G4"/>
   </mergeCells>
   <conditionalFormatting sqref="G36">
@@ -13287,27 +13432,42 @@
   <dimension ref="A1:AD33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="52.5" customWidth="1" min="1" max="1"/>
+    <col width="23.5" customWidth="1" min="2" max="2"/>
+    <col width="16.5" customWidth="1" min="3" max="3"/>
+    <col width="18.5" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="195" t="inlineStr">
         <is>
           <t>SENARYO — Dava Masraf &amp; Harç Hesaplama Motoru</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="B1" s="196" t="n"/>
+      <c r="C1" s="196" t="n"/>
+      <c r="D1" s="196" t="n"/>
+      <c r="E1" s="196" t="n"/>
+      <c r="F1" s="196" t="n"/>
+      <c r="G1" s="196" t="n"/>
+      <c r="H1" s="196" t="n"/>
+      <c r="I1" s="196" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="215" t="inlineStr">
         <is>
           <t>Senaryo ve duyarlılık</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="40" t="inlineStr">
         <is>
@@ -13427,6 +13587,7 @@
         <v/>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="21" t="inlineStr">
         <is>
@@ -13449,6 +13610,7 @@
         <v/>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
@@ -13546,6 +13708,7 @@
         <v/>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="21" t="inlineStr">
         <is>
@@ -13568,6 +13731,7 @@
         <v/>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="21" t="inlineStr">
         <is>
@@ -13620,6 +13784,8 @@
         <v>39000</v>
       </c>
     </row>
+    <row r="30"/>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="21" t="inlineStr">
         <is>
@@ -13644,10 +13810,11 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="3">
+  <mergeCells count="4">
+    <mergeCell ref="B12:H12"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="B20:H20"/>
-    <mergeCell ref="B12:H12"/>
-    <mergeCell ref="A1:AD1"/>
   </mergeCells>
   <conditionalFormatting sqref="E6">
     <cfRule type="expression" priority="1" dxfId="3">
@@ -13730,30 +13897,46 @@
   <dimension ref="A1:AD13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="21.5" customWidth="1" min="1" max="1"/>
+    <col width="33.5" customWidth="1" min="2" max="2"/>
+    <col width="61.5" customWidth="1" min="3" max="3"/>
+    <col width="18.5" customWidth="1" min="4" max="4"/>
+    <col width="14.5" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="16.5" customWidth="1" min="10" max="10"/>
+    <col width="13.5" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="195" t="inlineStr">
         <is>
           <t>VAKALAR — Dava Masraf &amp; Harç Hesaplama Motoru</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="B1" s="196" t="n"/>
+      <c r="C1" s="196" t="n"/>
+      <c r="D1" s="196" t="n"/>
+      <c r="E1" s="196" t="n"/>
+      <c r="F1" s="196" t="n"/>
+      <c r="G1" s="196" t="n"/>
+      <c r="H1" s="196" t="n"/>
+      <c r="I1" s="196" t="n"/>
+      <c r="J1" s="196" t="n"/>
+      <c r="K1" s="196" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="215" t="inlineStr">
         <is>
           <t>Tarife tarzı altın vakalar — harç/AAÜT</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="23" t="inlineStr">
         <is>
@@ -13978,6 +14161,8 @@
         <v>1</v>
       </c>
     </row>
+    <row r="10"/>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="21" t="inlineStr">
         <is>
@@ -14003,8 +14188,8 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
   <mergeCells count="2">
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A3:K3"/>
   </mergeCells>
   <conditionalFormatting sqref="B12">
     <cfRule type="expression" priority="1" dxfId="0">
@@ -14037,26 +14222,39 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="145.5" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="195" t="inlineStr">
         <is>
           <t>KANIT RAPORU — Dava Masraf &amp; Harç Hesaplama Motoru</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="B1" s="196" t="n"/>
+      <c r="C1" s="196" t="n"/>
+      <c r="D1" s="196" t="n"/>
+      <c r="E1" s="196" t="n"/>
+      <c r="F1" s="196" t="n"/>
+      <c r="G1" s="196" t="n"/>
+      <c r="H1" s="196" t="n"/>
+      <c r="I1" s="196" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="215" t="inlineStr">
         <is>
           <t>KANIT RAPORU — Dava Masraf &amp; Harç</t>
         </is>
@@ -14106,6 +14304,7 @@
         <v/>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
@@ -14216,6 +14415,7 @@
         <v/>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
@@ -14231,6 +14431,7 @@
       </c>
     </row>
     <row r="22"/>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="18" t="inlineStr">
         <is>
@@ -14248,6 +14449,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="18" t="inlineStr">
         <is>
@@ -14271,9 +14473,9 @@
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B10:F10"/>
-    <mergeCell ref="A1:L1"/>
     <mergeCell ref="A21:F22"/>
-    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="B9">
     <cfRule type="expression" priority="1" dxfId="3">
@@ -14313,23 +14515,41 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="55.5" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="195" t="inlineStr">
         <is>
           <t>KONTROLLER — Dava Masraf &amp; Harç Hesaplama Motoru</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="B1" s="196" t="n"/>
+      <c r="C1" s="196" t="n"/>
+      <c r="D1" s="196" t="n"/>
+      <c r="E1" s="196" t="n"/>
+      <c r="F1" s="196" t="n"/>
+      <c r="G1" s="196" t="n"/>
+      <c r="H1" s="196" t="n"/>
+      <c r="I1" s="196" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="215" t="inlineStr">
         <is>
           <t>Canlı kontrol paneli</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
         <is>
@@ -14418,6 +14638,7 @@
         <v/>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
         <is>
@@ -14440,6 +14661,7 @@
         <v/>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
         <is>
@@ -14475,8 +14697,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AD1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="B19">
     <cfRule type="expression" priority="1" dxfId="3">
@@ -14540,30 +14763,45 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14.5" customWidth="1" min="2" max="2"/>
+    <col width="15.5" customWidth="1" min="3" max="3"/>
+    <col width="12.5" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="16.5" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="14.5" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="195" t="inlineStr">
         <is>
           <t>ORNEK VERI — Dava Masraf &amp; Harç Hesaplama Motoru</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="B1" s="196" t="n"/>
+      <c r="C1" s="196" t="n"/>
+      <c r="D1" s="196" t="n"/>
+      <c r="E1" s="196" t="n"/>
+      <c r="F1" s="196" t="n"/>
+      <c r="G1" s="196" t="n"/>
+      <c r="H1" s="196" t="n"/>
+      <c r="I1" s="196" t="n"/>
+      <c r="J1" s="196" t="n"/>
+      <c r="K1" s="196" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="215" t="inlineStr">
         <is>
           <t>Örnek dosya kütüphanesi</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="23" t="inlineStr">
         <is>
@@ -14933,8 +15171,8 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
   <mergeCells count="2">
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A3:K3"/>
   </mergeCells>
   <conditionalFormatting sqref="I6">
     <cfRule type="expression" priority="1" dxfId="3">
@@ -14966,22 +15204,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:AC27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="70.5" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="15.5" customWidth="1" min="4" max="4"/>
+    <col width="36.5" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="11.5" customWidth="1" min="7" max="7"/>
+    <col width="75.5" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="15.5" customWidth="1" min="10" max="10"/>
+    <col width="81.5" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15015,6 +15254,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="88" t="inlineStr">
         <is>
@@ -15145,6 +15385,7 @@
       <c r="L9" s="89" t="n"/>
       <c r="M9" s="89" t="n"/>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="82" t="inlineStr">
         <is>
@@ -15174,6 +15415,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="B14" s="105" t="inlineStr">
         <is>
@@ -15428,6 +15670,7 @@
         <v>92</v>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="B22" s="116" t="inlineStr">
         <is>
@@ -15516,13 +15759,21 @@
           <t>✓ 90 GÜNLÜK PROJEKSİYONDA NAKİT SIKIŞIKLIĞI TESPİT EDİLMEDİ</t>
         </is>
       </c>
+      <c r="G26" s="197" t="n"/>
+      <c r="H26" s="197" t="n"/>
+      <c r="I26" s="198" t="n"/>
       <c r="K26" s="125" t="inlineStr">
         <is>
           <t>STRATEJİ REÇETESİNİ İNCELE &gt;</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
+    <row r="27">
+      <c r="F27" s="199" t="n"/>
+      <c r="G27" s="200" t="n"/>
+      <c r="H27" s="200" t="n"/>
+      <c r="I27" s="201" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="K26:M27"/>
@@ -15540,29 +15791,45 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T9"/>
+  <dimension ref="A1:AC9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13.5" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="15.5" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="195" t="inlineStr">
         <is>
           <t>LISTELER — Dava Masraf &amp; Harç Hesaplama Motoru</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="B1" s="196" t="n"/>
+      <c r="C1" s="196" t="n"/>
+      <c r="D1" s="196" t="n"/>
+      <c r="E1" s="196" t="n"/>
+      <c r="F1" s="196" t="n"/>
+      <c r="G1" s="196" t="n"/>
+      <c r="H1" s="196" t="n"/>
+      <c r="I1" s="196" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="215" t="inlineStr">
         <is>
           <t>Doğrulama listeleri</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="40" t="inlineStr">
         <is>
@@ -15644,8 +15911,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:T1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15662,24 +15930,33 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="23.5" customWidth="1" min="2" max="2"/>
+    <col width="10.5" customWidth="1" min="3" max="3"/>
     <col width="36" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="19.5" customWidth="1" min="6" max="6"/>
+    <col width="20.5" customWidth="1" min="7" max="7"/>
+    <col width="11.5" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="195" t="inlineStr">
         <is>
           <t>AYARLAR — Dava Masraf &amp; Harç Hesaplama Motoru</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="B1" s="196" t="n"/>
+      <c r="C1" s="196" t="n"/>
+      <c r="D1" s="196" t="n"/>
+      <c r="E1" s="196" t="n"/>
+      <c r="F1" s="196" t="n"/>
+      <c r="G1" s="196" t="n"/>
+      <c r="H1" s="196" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="215" t="inlineStr">
         <is>
           <t>Parametreler (tek kaynak)</t>
         </is>
@@ -16791,8 +17068,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AD1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <conditionalFormatting sqref="H6:H60">
     <cfRule type="expression" priority="1" dxfId="0">
@@ -16820,23 +17098,42 @@
   <dimension ref="A1:AD11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="90" customWidth="1" min="1" max="1"/>
+    <col width="90.5" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="195" t="inlineStr">
         <is>
           <t>KILAVUZ — Dava Masraf &amp; Harç Hesaplama Motoru</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="B1" s="196" t="n"/>
+      <c r="C1" s="196" t="n"/>
+      <c r="D1" s="196" t="n"/>
+      <c r="E1" s="196" t="n"/>
+      <c r="F1" s="196" t="n"/>
+      <c r="G1" s="196" t="n"/>
+      <c r="H1" s="196" t="n"/>
+      <c r="I1" s="196" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="215" t="inlineStr">
         <is>
           <t>Kullanım kılavuzu</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
@@ -16888,15 +17185,16 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A10:L10"/>
     <mergeCell ref="A7:L7"/>
     <mergeCell ref="A11:L11"/>
     <mergeCell ref="A5:L5"/>
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A8:L8"/>
     <mergeCell ref="A6:L6"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A9:L9"/>
-    <mergeCell ref="A1:AD1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16909,18 +17207,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="36.5" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="37.5" customWidth="1" min="4" max="4"/>
+    <col width="18.5" customWidth="1" min="5" max="5"/>
+    <col width="13.5" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22.5" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16930,12 +17229,16 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="B3" s="126" t="inlineStr">
         <is>
           <t>🔍  DAVA MASRAF &amp; HARÇ HESAPLAMA MOTORU — Kayıt veya hesap ara...</t>
         </is>
       </c>
+      <c r="C3" s="202" t="n"/>
+      <c r="D3" s="202" t="n"/>
+      <c r="E3" s="203" t="n"/>
       <c r="G3" s="127" t="inlineStr">
         <is>
           <t>TOPLAM: 1.450 KAYIT</t>
@@ -16947,6 +17250,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="129" t="inlineStr">
         <is>
@@ -17359,22 +17663,17 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="B17" s="146" t="inlineStr">
         <is>
           <t>SAYFA TOPLAMI (10 / 1.450 KAYIT)</t>
         </is>
       </c>
-      <c r="C17" s="114" t="n"/>
-      <c r="D17" s="114" t="n"/>
       <c r="E17" s="147">
         <f>TOPLA(E6:E15)</f>
         <v/>
       </c>
-      <c r="F17" s="114" t="n"/>
-      <c r="G17" s="114" t="n"/>
-      <c r="H17" s="114" t="n"/>
-      <c r="I17" s="114" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -17395,7 +17694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -17440,25 +17739,26 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="151" t="inlineStr">
         <is>
           <t>SENARYO A: KÖTÜMSER (STRES TESTİ -%20)</t>
         </is>
       </c>
-      <c r="C6" s="89" t="n"/>
-      <c r="D6" s="89" t="n"/>
-      <c r="E6" s="89" t="n"/>
-      <c r="F6" s="89" t="n"/>
+      <c r="C6" s="202" t="n"/>
+      <c r="D6" s="202" t="n"/>
+      <c r="E6" s="202" t="n"/>
+      <c r="F6" s="203" t="n"/>
       <c r="H6" s="152" t="inlineStr">
         <is>
           <t>SENARYO B: BAZ MODEL (HEDEFLENEN)</t>
         </is>
       </c>
-      <c r="I6" s="89" t="n"/>
-      <c r="J6" s="89" t="n"/>
-      <c r="K6" s="89" t="n"/>
-      <c r="L6" s="89" t="n"/>
+      <c r="I6" s="202" t="n"/>
+      <c r="J6" s="202" t="n"/>
+      <c r="K6" s="202" t="n"/>
+      <c r="L6" s="203" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="89" t="n"/>
@@ -17609,32 +17909,33 @@
           <t>STRES SENARYOSUNDA DAHİ İFLAS RİSKİ YOK</t>
         </is>
       </c>
-      <c r="C14" s="89" t="n"/>
-      <c r="D14" s="89" t="n"/>
-      <c r="E14" s="89" t="n"/>
-      <c r="F14" s="89" t="n"/>
+      <c r="C14" s="204" t="n"/>
+      <c r="D14" s="204" t="n"/>
+      <c r="E14" s="204" t="n"/>
+      <c r="F14" s="205" t="n"/>
       <c r="H14" s="159" t="inlineStr">
         <is>
           <t>OPTİMUM İCRA VE PLANLAMA REÇETESİ</t>
         </is>
       </c>
-      <c r="I14" s="89" t="n"/>
-      <c r="J14" s="89" t="n"/>
-      <c r="K14" s="89" t="n"/>
-      <c r="L14" s="89" t="n"/>
+      <c r="I14" s="206" t="n"/>
+      <c r="J14" s="206" t="n"/>
+      <c r="K14" s="206" t="n"/>
+      <c r="L14" s="207" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="89" t="n"/>
-      <c r="C15" s="89" t="n"/>
-      <c r="D15" s="89" t="n"/>
-      <c r="E15" s="89" t="n"/>
-      <c r="F15" s="89" t="n"/>
-      <c r="H15" s="89" t="n"/>
-      <c r="I15" s="89" t="n"/>
-      <c r="J15" s="89" t="n"/>
-      <c r="K15" s="89" t="n"/>
-      <c r="L15" s="89" t="n"/>
-    </row>
+      <c r="B15" s="208" t="n"/>
+      <c r="C15" s="209" t="n"/>
+      <c r="D15" s="209" t="n"/>
+      <c r="E15" s="209" t="n"/>
+      <c r="F15" s="210" t="n"/>
+      <c r="H15" s="211" t="n"/>
+      <c r="I15" s="212" t="n"/>
+      <c r="J15" s="212" t="n"/>
+      <c r="K15" s="212" t="n"/>
+      <c r="L15" s="213" t="n"/>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="B17" s="69" t="inlineStr">
         <is>
@@ -17642,6 +17943,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="B19" s="116" t="inlineStr">
         <is>
@@ -17716,25 +18018,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
-    <col width="29" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="30.5" customWidth="1" min="2" max="2"/>
+    <col width="23.5" customWidth="1" min="3" max="3"/>
+    <col width="48.5" customWidth="1" min="4" max="4"/>
+    <col width="43.5" customWidth="1" min="5" max="5"/>
+    <col width="21.5" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="166" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="195" t="inlineStr">
         <is>
           <t>YÜRÜTME ÇEKİRDEĞİ — ZORUNLU ÜRETİM SIRASI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="196" t="n"/>
+      <c r="C1" s="196" t="n"/>
+      <c r="D1" s="196" t="n"/>
+      <c r="E1" s="196" t="n"/>
+      <c r="F1" s="196" t="n"/>
+      <c r="G1" s="196" t="n"/>
+      <c r="H1" s="196" t="n"/>
+      <c r="I1" s="196" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="167" t="inlineStr">
         <is>
@@ -18194,7 +18508,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18207,22 +18521,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:AC34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="89.5" customWidth="1" min="2" max="2"/>
+    <col width="34.5" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="169" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="195" t="inlineStr">
         <is>
           <t>NİHAİ KONTROL LİSTESİ — KANITSIZ GEÇİŞ YOK</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="196" t="n"/>
+      <c r="C1" s="196" t="n"/>
+      <c r="D1" s="196" t="n"/>
+      <c r="E1" s="196" t="n"/>
+      <c r="F1" s="196" t="n"/>
+      <c r="G1" s="196" t="n"/>
+      <c r="H1" s="196" t="n"/>
+      <c r="I1" s="196" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="170" t="inlineStr">
         <is>
@@ -18934,7 +19263,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18947,24 +19276,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:AC22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="30.5" customWidth="1" min="1" max="1"/>
+    <col width="71.5" customWidth="1" min="2" max="2"/>
+    <col width="160.5" customWidth="1" min="3" max="3"/>
+    <col width="70.5" customWidth="1" min="4" max="4"/>
+    <col width="50.5" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="174" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="195" t="inlineStr">
         <is>
           <t>GÖRSEL TASARIM VE PREMIUM EXCEL STANDARDI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="196" t="n"/>
+      <c r="C1" s="196" t="n"/>
+      <c r="D1" s="196" t="n"/>
+      <c r="E1" s="196" t="n"/>
+      <c r="F1" s="196" t="n"/>
+      <c r="G1" s="196" t="n"/>
+      <c r="H1" s="196" t="n"/>
+      <c r="I1" s="196" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="175" t="inlineStr">
         <is>
@@ -19607,7 +19949,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19620,24 +19962,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:AC18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="22.5" customWidth="1" min="1" max="1"/>
+    <col width="60.5" customWidth="1" min="2" max="2"/>
+    <col width="86.5" customWidth="1" min="3" max="3"/>
+    <col width="40.5" customWidth="1" min="4" max="4"/>
+    <col width="39.5" customWidth="1" min="5" max="5"/>
+    <col width="27.5" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="178" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="195" t="inlineStr">
         <is>
           <t>TÜRKİYE MUHASEBE VE TEKDÜZEN HESAP PLANI STANDARDI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="196" t="n"/>
+      <c r="C1" s="196" t="n"/>
+      <c r="D1" s="196" t="n"/>
+      <c r="E1" s="196" t="n"/>
+      <c r="F1" s="196" t="n"/>
+      <c r="G1" s="196" t="n"/>
+      <c r="H1" s="196" t="n"/>
+      <c r="I1" s="196" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="179" t="inlineStr">
         <is>
@@ -20152,7 +20507,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20165,23 +20520,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="54" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="20.5" customWidth="1" min="1" max="1"/>
+    <col width="41.5" customWidth="1" min="2" max="2"/>
+    <col width="86.5" customWidth="1" min="3" max="3"/>
+    <col width="35.5" customWidth="1" min="4" max="4"/>
+    <col width="33.5" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="181" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="195" t="inlineStr">
         <is>
           <t>KARAR, GÜVEN VE SATIŞA HAZIRLIK STANDARDI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="196" t="n"/>
+      <c r="C1" s="196" t="n"/>
+      <c r="D1" s="196" t="n"/>
+      <c r="E1" s="196" t="n"/>
+      <c r="F1" s="196" t="n"/>
+      <c r="G1" s="196" t="n"/>
+      <c r="H1" s="196" t="n"/>
+      <c r="I1" s="196" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="182" t="inlineStr">
         <is>
@@ -20728,7 +21097,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXCELARSIV_PRODUCTS/dava-masraf-harc-hesaplama/DavaMasrafHarcHesaplama.xlsx
+++ b/EXCELARSIV_PRODUCTS/dava-masraf-harc-hesaplama/DavaMasrafHarcHesaplama.xlsx
@@ -3577,7 +3577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC33"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3598,14 +3598,6 @@
           <t>EXCELARŞİV KARAR SİSTEMİ v15.1 — ÜRETİM REFERANSI</t>
         </is>
       </c>
-      <c r="B1" s="196" t="n"/>
-      <c r="C1" s="196" t="n"/>
-      <c r="D1" s="196" t="n"/>
-      <c r="E1" s="196" t="n"/>
-      <c r="F1" s="196" t="n"/>
-      <c r="G1" s="196" t="n"/>
-      <c r="H1" s="196" t="n"/>
-      <c r="I1" s="196" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">
@@ -3984,7 +3976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:T21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -4005,14 +3997,6 @@
           <t>KAPAK — Dava Masraf &amp; Harç Hesaplama Motoru</t>
         </is>
       </c>
-      <c r="B1" s="196" t="n"/>
-      <c r="C1" s="196" t="n"/>
-      <c r="D1" s="196" t="n"/>
-      <c r="E1" s="196" t="n"/>
-      <c r="F1" s="196" t="n"/>
-      <c r="G1" s="196" t="n"/>
-      <c r="H1" s="196" t="n"/>
-      <c r="I1" s="196" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -4148,7 +4132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD13"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="111.5" customWidth="1" min="1" max="1"/>
@@ -4169,14 +4153,6 @@
           <t>HIZLI BASLANGIC — Dava Masraf &amp; Harç Hesaplama Motoru</t>
         </is>
       </c>
-      <c r="B1" s="196" t="n"/>
-      <c r="C1" s="196" t="n"/>
-      <c r="D1" s="196" t="n"/>
-      <c r="E1" s="196" t="n"/>
-      <c r="F1" s="196" t="n"/>
-      <c r="G1" s="196" t="n"/>
-      <c r="H1" s="196" t="n"/>
-      <c r="I1" s="196" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -4261,8 +4237,8 @@
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="A10:J10"/>
+    <mergeCell ref="B6:J6"/>
     <mergeCell ref="A13:J13"/>
-    <mergeCell ref="B6:J6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4275,7 +4251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD1004"/>
+  <dimension ref="A1:I1004"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39.5" customWidth="1" min="1" max="1"/>
@@ -4296,14 +4272,6 @@
           <t>GIRDI — Dava Masraf &amp; Harç Hesaplama Motoru</t>
         </is>
       </c>
-      <c r="B1" s="196" t="n"/>
-      <c r="C1" s="196" t="n"/>
-      <c r="D1" s="196" t="n"/>
-      <c r="E1" s="196" t="n"/>
-      <c r="F1" s="196" t="n"/>
-      <c r="G1" s="196" t="n"/>
-      <c r="H1" s="196" t="n"/>
-      <c r="I1" s="196" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -10884,7 +10852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD20"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -10906,14 +10874,6 @@
           <t>KURALLAR — Dava Masraf &amp; Harç Hesaplama Motoru</t>
         </is>
       </c>
-      <c r="B1" s="196" t="n"/>
-      <c r="C1" s="196" t="n"/>
-      <c r="D1" s="196" t="n"/>
-      <c r="E1" s="196" t="n"/>
-      <c r="F1" s="196" t="n"/>
-      <c r="G1" s="196" t="n"/>
-      <c r="H1" s="196" t="n"/>
-      <c r="I1" s="196" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -11564,7 +11524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD59"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11585,14 +11545,6 @@
           <t>MOTOR — Dava Masraf &amp; Harç Hesaplama Motoru</t>
         </is>
       </c>
-      <c r="B1" s="196" t="n"/>
-      <c r="C1" s="196" t="n"/>
-      <c r="D1" s="196" t="n"/>
-      <c r="E1" s="196" t="n"/>
-      <c r="F1" s="196" t="n"/>
-      <c r="G1" s="196" t="n"/>
-      <c r="H1" s="196" t="n"/>
-      <c r="I1" s="196" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -13429,7 +13381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD33"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52.5" customWidth="1" min="1" max="1"/>
@@ -13450,14 +13402,6 @@
           <t>SENARYO — Dava Masraf &amp; Harç Hesaplama Motoru</t>
         </is>
       </c>
-      <c r="B1" s="196" t="n"/>
-      <c r="C1" s="196" t="n"/>
-      <c r="D1" s="196" t="n"/>
-      <c r="E1" s="196" t="n"/>
-      <c r="F1" s="196" t="n"/>
-      <c r="G1" s="196" t="n"/>
-      <c r="H1" s="196" t="n"/>
-      <c r="I1" s="196" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -13811,10 +13755,10 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
   <mergeCells count="4">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="B12:H12"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="B20:H20"/>
   </mergeCells>
   <conditionalFormatting sqref="E6">
     <cfRule type="expression" priority="1" dxfId="3">
@@ -13894,7 +13838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD13"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21.5" customWidth="1" min="1" max="1"/>
@@ -13917,16 +13861,6 @@
           <t>VAKALAR — Dava Masraf &amp; Harç Hesaplama Motoru</t>
         </is>
       </c>
-      <c r="B1" s="196" t="n"/>
-      <c r="C1" s="196" t="n"/>
-      <c r="D1" s="196" t="n"/>
-      <c r="E1" s="196" t="n"/>
-      <c r="F1" s="196" t="n"/>
-      <c r="G1" s="196" t="n"/>
-      <c r="H1" s="196" t="n"/>
-      <c r="I1" s="196" t="n"/>
-      <c r="J1" s="196" t="n"/>
-      <c r="K1" s="196" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -14222,7 +14156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC26"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="145.5" customWidth="1" min="1" max="1"/>
@@ -14243,14 +14177,6 @@
           <t>KANIT RAPORU — Dava Masraf &amp; Harç Hesaplama Motoru</t>
         </is>
       </c>
-      <c r="B1" s="196" t="n"/>
-      <c r="C1" s="196" t="n"/>
-      <c r="D1" s="196" t="n"/>
-      <c r="E1" s="196" t="n"/>
-      <c r="F1" s="196" t="n"/>
-      <c r="G1" s="196" t="n"/>
-      <c r="H1" s="196" t="n"/>
-      <c r="I1" s="196" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -14511,7 +14437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD19"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -14532,14 +14458,6 @@
           <t>KONTROLLER — Dava Masraf &amp; Harç Hesaplama Motoru</t>
         </is>
       </c>
-      <c r="B1" s="196" t="n"/>
-      <c r="C1" s="196" t="n"/>
-      <c r="D1" s="196" t="n"/>
-      <c r="E1" s="196" t="n"/>
-      <c r="F1" s="196" t="n"/>
-      <c r="G1" s="196" t="n"/>
-      <c r="H1" s="196" t="n"/>
-      <c r="I1" s="196" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -14759,7 +14677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD15"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -14782,16 +14700,6 @@
           <t>ORNEK VERI — Dava Masraf &amp; Harç Hesaplama Motoru</t>
         </is>
       </c>
-      <c r="B1" s="196" t="n"/>
-      <c r="C1" s="196" t="n"/>
-      <c r="D1" s="196" t="n"/>
-      <c r="E1" s="196" t="n"/>
-      <c r="F1" s="196" t="n"/>
-      <c r="G1" s="196" t="n"/>
-      <c r="H1" s="196" t="n"/>
-      <c r="I1" s="196" t="n"/>
-      <c r="J1" s="196" t="n"/>
-      <c r="K1" s="196" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -15204,7 +15112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC27"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -15335,7 +15243,7 @@
       <c r="I7" s="89" t="n"/>
       <c r="J7" s="89" t="n"/>
       <c r="K7" s="100">
-        <f>EĞER(E7&gt;0; YUVARLA(B7/E7; 2); 0)</f>
+        <f>IF(E7&gt;0, ROUND(B7/E7, 2), 0)</f>
         <v/>
       </c>
       <c r="L7" s="89" t="n"/>
@@ -15640,11 +15548,11 @@
         </is>
       </c>
       <c r="I19" s="189">
-        <f>TOPLA(I15:I18)</f>
+        <f>SUM(I15:I18)</f>
         <v/>
       </c>
       <c r="J19" s="190">
-        <f>TOPLA(J15:J18)</f>
+        <f>SUM(J15:J18)</f>
         <v/>
       </c>
       <c r="K19" s="114" t="inlineStr"/>
@@ -15791,7 +15699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -15812,14 +15720,6 @@
           <t>LISTELER — Dava Masraf &amp; Harç Hesaplama Motoru</t>
         </is>
       </c>
-      <c r="B1" s="196" t="n"/>
-      <c r="C1" s="196" t="n"/>
-      <c r="D1" s="196" t="n"/>
-      <c r="E1" s="196" t="n"/>
-      <c r="F1" s="196" t="n"/>
-      <c r="G1" s="196" t="n"/>
-      <c r="H1" s="196" t="n"/>
-      <c r="I1" s="196" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -15926,7 +15826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD32"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -15946,13 +15846,6 @@
           <t>AYARLAR — Dava Masraf &amp; Harç Hesaplama Motoru</t>
         </is>
       </c>
-      <c r="B1" s="196" t="n"/>
-      <c r="C1" s="196" t="n"/>
-      <c r="D1" s="196" t="n"/>
-      <c r="E1" s="196" t="n"/>
-      <c r="F1" s="196" t="n"/>
-      <c r="G1" s="196" t="n"/>
-      <c r="H1" s="196" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -17095,7 +16988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90.5" customWidth="1" min="1" max="1"/>
@@ -17116,14 +17009,6 @@
           <t>KILAVUZ — Dava Masraf &amp; Harç Hesaplama Motoru</t>
         </is>
       </c>
-      <c r="B1" s="196" t="n"/>
-      <c r="C1" s="196" t="n"/>
-      <c r="D1" s="196" t="n"/>
-      <c r="E1" s="196" t="n"/>
-      <c r="F1" s="196" t="n"/>
-      <c r="G1" s="196" t="n"/>
-      <c r="H1" s="196" t="n"/>
-      <c r="I1" s="196" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -17207,7 +17092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -17671,7 +17556,7 @@
         </is>
       </c>
       <c r="E17" s="147">
-        <f>TOPLA(E6:E15)</f>
+        <f>SUM(E6:E15)</f>
         <v/>
       </c>
     </row>
@@ -17694,7 +17579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC26"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -17861,7 +17746,7 @@
       <c r="C11" s="89" t="n"/>
       <c r="D11" s="89" t="n"/>
       <c r="E11" s="194">
-        <f>YUVARLA(PANO!B7*0.8/PANO!E7; 2)</f>
+        <f>ROUND(PANO!B7*0.8/PANO!E7, 2)</f>
         <v/>
       </c>
       <c r="F11" s="89" t="n"/>
@@ -18018,7 +17903,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -18039,14 +17924,6 @@
           <t>YÜRÜTME ÇEKİRDEĞİ — ZORUNLU ÜRETİM SIRASI</t>
         </is>
       </c>
-      <c r="B1" s="196" t="n"/>
-      <c r="C1" s="196" t="n"/>
-      <c r="D1" s="196" t="n"/>
-      <c r="E1" s="196" t="n"/>
-      <c r="F1" s="196" t="n"/>
-      <c r="G1" s="196" t="n"/>
-      <c r="H1" s="196" t="n"/>
-      <c r="I1" s="196" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">
@@ -18521,7 +18398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC34"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18542,14 +18419,6 @@
           <t>NİHAİ KONTROL LİSTESİ — KANITSIZ GEÇİŞ YOK</t>
         </is>
       </c>
-      <c r="B1" s="196" t="n"/>
-      <c r="C1" s="196" t="n"/>
-      <c r="D1" s="196" t="n"/>
-      <c r="E1" s="196" t="n"/>
-      <c r="F1" s="196" t="n"/>
-      <c r="G1" s="196" t="n"/>
-      <c r="H1" s="196" t="n"/>
-      <c r="I1" s="196" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">
@@ -19276,7 +19145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC22"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.5" customWidth="1" min="1" max="1"/>
@@ -19297,14 +19166,6 @@
           <t>GÖRSEL TASARIM VE PREMIUM EXCEL STANDARDI</t>
         </is>
       </c>
-      <c r="B1" s="196" t="n"/>
-      <c r="C1" s="196" t="n"/>
-      <c r="D1" s="196" t="n"/>
-      <c r="E1" s="196" t="n"/>
-      <c r="F1" s="196" t="n"/>
-      <c r="G1" s="196" t="n"/>
-      <c r="H1" s="196" t="n"/>
-      <c r="I1" s="196" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">
@@ -19962,7 +19823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC18"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22.5" customWidth="1" min="1" max="1"/>
@@ -19983,14 +19844,6 @@
           <t>TÜRKİYE MUHASEBE VE TEKDÜZEN HESAP PLANI STANDARDI</t>
         </is>
       </c>
-      <c r="B1" s="196" t="n"/>
-      <c r="C1" s="196" t="n"/>
-      <c r="D1" s="196" t="n"/>
-      <c r="E1" s="196" t="n"/>
-      <c r="F1" s="196" t="n"/>
-      <c r="G1" s="196" t="n"/>
-      <c r="H1" s="196" t="n"/>
-      <c r="I1" s="196" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">
@@ -20520,7 +20373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20.5" customWidth="1" min="1" max="1"/>
@@ -20541,14 +20394,6 @@
           <t>KARAR, GÜVEN VE SATIŞA HAZIRLIK STANDARDI</t>
         </is>
       </c>
-      <c r="B1" s="196" t="n"/>
-      <c r="C1" s="196" t="n"/>
-      <c r="D1" s="196" t="n"/>
-      <c r="E1" s="196" t="n"/>
-      <c r="F1" s="196" t="n"/>
-      <c r="G1" s="196" t="n"/>
-      <c r="H1" s="196" t="n"/>
-      <c r="I1" s="196" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">

--- a/EXCELARSIV_PRODUCTS/dava-masraf-harc-hesaplama/DavaMasrafHarcHesaplama.xlsx
+++ b/EXCELARSIV_PRODUCTS/dava-masraf-harc-hesaplama/DavaMasrafHarcHesaplama.xlsx
@@ -108,7 +108,7 @@
     <numFmt numFmtId="169" formatCode="₺#,##0"/>
     <numFmt numFmtId="170" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
-  <fonts count="87">
+  <fonts count="122">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -608,8 +608,214 @@
       <color rgb="00475569"/>
       <sz val="9.5"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00334155"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0064748B"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E40AF"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00B91C1C"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0015803D"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00475569"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0015803D"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00475569"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="000F172A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00475569"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00166534"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E40AF"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0092400E"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00115E59"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0038BDF8"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00F87171"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0034D399"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00059669"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000284C7"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00D97706"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="008B5CF6"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00059669"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00A7F3D0"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00065F46"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00991B1B"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00475569"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00059669"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00B91C1C"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E40AF"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="002563EB"/>
+      <sz val="9.5"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="39">
     <fill>
       <patternFill/>
     </fill>
@@ -801,8 +1007,32 @@
         <bgColor rgb="001B365D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCFCE7"/>
+        <bgColor rgb="00DCFCE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1F5F9"/>
+        <bgColor rgb="00F1F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CCFBF1"/>
+        <bgColor rgb="00CCFBF1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0FDF4"/>
+        <bgColor rgb="00F0FDF4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="35">
+  <borders count="71">
     <border>
       <left/>
       <right/>
@@ -1165,11 +1395,353 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="001E3A8A"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="001E3A8A"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="001E3A8A"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00DC2626"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00DC2626"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00DC2626"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00059669"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00059669"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00059669"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000284C7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000284C7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000284C7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00334155"/>
+      </left>
+      <right style="thin">
+        <color rgb="00334155"/>
+      </right>
+      <top style="thin">
+        <color rgb="000F172A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000F172A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00334155"/>
+      </left>
+      <right style="thin">
+        <color rgb="00334155"/>
+      </right>
+      <top style="medium">
+        <color rgb="00334155"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="000F172A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00065F46"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00065F46"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00065F46"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00065F46"/>
+      </right>
+      <top style="thin">
+        <color rgb="00065F46"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00065F46"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00065F46"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FECACA"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00FECACA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FECACA"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FECACA"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00FECACA"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FCA5A5"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00FCA5A5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FCA5A5"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFDBFE"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFDBFE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFDBFE"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFDBFE"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFDBFE"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="0093C5FD"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="0093C5FD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0093C5FD"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="216">
+  <cellXfs count="313">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1664,6 +2236,235 @@
     </xf>
     <xf numFmtId="0" fontId="86" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="18" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="89" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="18" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="18" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="18" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="51" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="90" fillId="18" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="92" fillId="18" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="90" fillId="18" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="18" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="18" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="18" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="18" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="18" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="96" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="7" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="7" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="40" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="65" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="98" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="40" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="65" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="102" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="37" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="104" fillId="7" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="105" fillId="7" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="54" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="106" fillId="7" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="107" fillId="18" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="113" fillId="17" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="59" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="108" fillId="18" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="18" borderId="56" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="108" fillId="18" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="62" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="109" fillId="18" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="17" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="18" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="111" fillId="18" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="38" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="57" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="115" fillId="12" borderId="63" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="120" fillId="11" borderId="67" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="64" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="65" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="68" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="69" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="116" fillId="18" borderId="64" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="117" fillId="18" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="18" borderId="68" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="121" fillId="18" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="107" fillId="18" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="118" fillId="18" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="118" fillId="18" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="18" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="12" borderId="66" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="11" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="18" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="56" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="107" fillId="18" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="18" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3599,7 +4400,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="162" t="inlineStr">
         <is>
@@ -3864,7 +4664,6 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="165" t="inlineStr">
         <is>
@@ -3998,7 +4797,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="214" t="inlineStr">
         <is>
@@ -4013,7 +4811,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
@@ -4056,7 +4853,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
@@ -4085,7 +4881,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
@@ -4100,7 +4895,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
@@ -4154,7 +4948,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="215" t="inlineStr">
         <is>
@@ -4162,7 +4955,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
         <is>
@@ -4199,7 +4991,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
@@ -4214,7 +5005,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
@@ -4273,7 +5063,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="215" t="inlineStr">
         <is>
@@ -4516,7 +5305,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="21" t="inlineStr">
         <is>
@@ -4528,7 +5316,6 @@
         <v/>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="21" t="inlineStr">
         <is>
@@ -10875,7 +11662,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="215" t="inlineStr">
         <is>
@@ -10890,7 +11676,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="23" t="inlineStr">
         <is>
@@ -11546,7 +12331,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="215" t="inlineStr">
         <is>
@@ -11561,7 +12345,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="23" t="inlineStr">
         <is>
@@ -13403,7 +14186,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="215" t="inlineStr">
         <is>
@@ -13411,7 +14193,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="40" t="inlineStr">
         <is>
@@ -13531,7 +14312,6 @@
         <v/>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="21" t="inlineStr">
         <is>
@@ -13554,7 +14334,6 @@
         <v/>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
@@ -13652,7 +14431,6 @@
         <v/>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="21" t="inlineStr">
         <is>
@@ -13675,7 +14453,6 @@
         <v/>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="A25" s="21" t="inlineStr">
         <is>
@@ -13728,8 +14505,6 @@
         <v>39000</v>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31"/>
     <row r="32">
       <c r="A32" s="21" t="inlineStr">
         <is>
@@ -13862,7 +14637,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="215" t="inlineStr">
         <is>
@@ -13870,7 +14644,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="23" t="inlineStr">
         <is>
@@ -14095,8 +14868,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="21" t="inlineStr">
         <is>
@@ -14178,7 +14949,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="215" t="inlineStr">
         <is>
@@ -14230,7 +15000,6 @@
         <v/>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
@@ -14341,7 +15110,6 @@
         <v/>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
@@ -14357,7 +15125,6 @@
       </c>
     </row>
     <row r="22"/>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="18" t="inlineStr">
         <is>
@@ -14375,7 +15142,6 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
     <row r="26">
       <c r="A26" s="18" t="inlineStr">
         <is>
@@ -14459,7 +15225,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="215" t="inlineStr">
         <is>
@@ -14467,7 +15232,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
         <is>
@@ -14556,7 +15320,6 @@
         <v/>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
         <is>
@@ -14579,7 +15342,6 @@
         <v/>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
         <is>
@@ -14701,7 +15463,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="215" t="inlineStr">
         <is>
@@ -14709,7 +15470,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="23" t="inlineStr">
         <is>
@@ -15115,554 +15875,585 @@
   <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="70.5" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15.5" customWidth="1" min="4" max="4"/>
-    <col width="36.5" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="11.5" customWidth="1" min="7" max="7"/>
-    <col width="75.5" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15.5" customWidth="1" min="10" max="10"/>
-    <col width="81.5" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="68" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="216" t="inlineStr">
         <is>
           <t>☰ PANO</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="B2" s="84" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="217" t="inlineStr">
         <is>
           <t>DAVA MASRAF &amp; HARÇ HESAPLAMA MOTORU</t>
         </is>
       </c>
-      <c r="L2" s="85" t="inlineStr">
+      <c r="L2" s="218" t="inlineStr">
         <is>
           <t>Dönem: 2026 / Tam ▼</t>
         </is>
       </c>
-      <c r="M2" s="86" t="inlineStr">
+      <c r="M2" s="219" t="inlineStr">
         <is>
           <t>★ DOĞRULANMIŞ</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="B3" s="87" t="inlineStr">
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="220" t="inlineStr">
         <is>
           <t>Hedef Kullanıcı: Hukuk bürosu sahibi, serbest avukat, kurum içi hukuk müşaviri · 2026 Q3 Denetim Standardı</t>
         </is>
       </c>
     </row>
-    <row r="4"/>
-    <row r="5">
-      <c r="B5" s="88" t="inlineStr">
+    <row r="4" ht="10" customHeight="1"/>
+    <row r="5" ht="20" customHeight="1">
+      <c r="B5" s="221" t="inlineStr">
         <is>
           <t>TOPLAM YÜK / DAVA DEĞERI</t>
         </is>
       </c>
-      <c r="C5" s="89" t="n"/>
-      <c r="D5" s="90" t="inlineStr">
+      <c r="C5" s="222" t="n"/>
+      <c r="D5" s="223" t="inlineStr">
         <is>
           <t>KONSOLİDE</t>
         </is>
       </c>
-      <c r="E5" s="91" t="inlineStr">
+      <c r="E5" s="224" t="inlineStr">
         <is>
           <t>HARÇ PAYI</t>
         </is>
       </c>
-      <c r="F5" s="89" t="n"/>
-      <c r="G5" s="92" t="inlineStr">
+      <c r="F5" s="222" t="n"/>
+      <c r="G5" s="225" t="inlineStr">
         <is>
           <t>KONTROL</t>
         </is>
       </c>
-      <c r="H5" s="88" t="inlineStr">
+      <c r="H5" s="226" t="inlineStr">
         <is>
           <t>NET OPERASYONEL MARJ</t>
         </is>
       </c>
-      <c r="I5" s="89" t="n"/>
-      <c r="J5" s="93" t="inlineStr">
+      <c r="I5" s="222" t="n"/>
+      <c r="J5" s="227" t="inlineStr">
         <is>
           <t>GÜVENLİ</t>
         </is>
       </c>
-      <c r="K5" s="94" t="inlineStr">
+      <c r="K5" s="228" t="inlineStr">
         <is>
           <t>SİSTEM GÜVEN SKORU</t>
         </is>
       </c>
-      <c r="L5" s="89" t="n"/>
-      <c r="M5" s="90" t="inlineStr">
+      <c r="L5" s="222" t="n"/>
+      <c r="M5" s="229" t="inlineStr">
         <is>
           <t>DENETLENDİ</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" s="95" t="n"/>
-      <c r="C6" s="89" t="n"/>
-      <c r="D6" s="89" t="n"/>
-      <c r="E6" s="96" t="n"/>
-      <c r="F6" s="89" t="n"/>
-      <c r="G6" s="89" t="n"/>
-      <c r="H6" s="95" t="n"/>
-      <c r="I6" s="89" t="n"/>
-      <c r="J6" s="89" t="n"/>
-      <c r="K6" s="97" t="n"/>
-      <c r="L6" s="89" t="n"/>
-      <c r="M6" s="89" t="n"/>
-    </row>
-    <row r="7">
-      <c r="B7" s="185">
+    <row r="6" ht="6" customHeight="1">
+      <c r="B6" s="230" t="n"/>
+      <c r="C6" s="231" t="n"/>
+      <c r="D6" s="232" t="n"/>
+      <c r="E6" s="233" t="n"/>
+      <c r="F6" s="231" t="n"/>
+      <c r="G6" s="232" t="n"/>
+      <c r="H6" s="234" t="n"/>
+      <c r="I6" s="231" t="n"/>
+      <c r="J6" s="232" t="n"/>
+      <c r="K6" s="235" t="n"/>
+      <c r="L6" s="231" t="n"/>
+      <c r="M6" s="232" t="n"/>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="B7" s="236">
         <f>GİRDİLER!E17</f>
         <v/>
       </c>
-      <c r="C7" s="89" t="n"/>
-      <c r="D7" s="89" t="n"/>
-      <c r="E7" s="186">
+      <c r="C7" s="231" t="n"/>
+      <c r="D7" s="232" t="n"/>
+      <c r="E7" s="237">
         <f>B7*0.22</f>
         <v/>
       </c>
-      <c r="F7" s="89" t="n"/>
-      <c r="G7" s="89" t="n"/>
-      <c r="H7" s="185">
+      <c r="F7" s="231" t="n"/>
+      <c r="G7" s="232" t="n"/>
+      <c r="H7" s="238">
         <f>B7-E7</f>
         <v/>
       </c>
-      <c r="I7" s="89" t="n"/>
-      <c r="J7" s="89" t="n"/>
-      <c r="K7" s="100">
+      <c r="I7" s="231" t="n"/>
+      <c r="J7" s="232" t="n"/>
+      <c r="K7" s="239">
         <f>IF(E7&gt;0, ROUND(B7/E7, 2), 0)</f>
         <v/>
       </c>
-      <c r="L7" s="89" t="n"/>
-      <c r="M7" s="89" t="n"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="95" t="n"/>
-      <c r="C8" s="89" t="n"/>
-      <c r="D8" s="89" t="n"/>
-      <c r="E8" s="96" t="n"/>
-      <c r="F8" s="89" t="n"/>
-      <c r="G8" s="89" t="n"/>
-      <c r="H8" s="95" t="n"/>
-      <c r="I8" s="89" t="n"/>
-      <c r="J8" s="89" t="n"/>
-      <c r="K8" s="97" t="n"/>
-      <c r="L8" s="89" t="n"/>
-      <c r="M8" s="89" t="n"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="101" t="inlineStr">
+      <c r="L7" s="231" t="n"/>
+      <c r="M7" s="232" t="n"/>
+    </row>
+    <row r="8" ht="6" customHeight="1">
+      <c r="B8" s="230" t="n"/>
+      <c r="C8" s="231" t="n"/>
+      <c r="D8" s="232" t="n"/>
+      <c r="E8" s="233" t="n"/>
+      <c r="F8" s="231" t="n"/>
+      <c r="G8" s="232" t="n"/>
+      <c r="H8" s="234" t="n"/>
+      <c r="I8" s="231" t="n"/>
+      <c r="J8" s="232" t="n"/>
+      <c r="K8" s="235" t="n"/>
+      <c r="L8" s="231" t="n"/>
+      <c r="M8" s="232" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="B9" s="240" t="inlineStr">
         <is>
           <t>↑ %14.2 konsolide canlı veri bağlantısı</t>
         </is>
       </c>
-      <c r="C9" s="89" t="n"/>
-      <c r="D9" s="89" t="n"/>
-      <c r="E9" s="102" t="inlineStr">
+      <c r="C9" s="241" t="n"/>
+      <c r="D9" s="242" t="n"/>
+      <c r="E9" s="243" t="inlineStr">
         <is>
           <t>● 8 Kalem nakit karşılığı: bloke</t>
         </is>
       </c>
-      <c r="F9" s="89" t="n"/>
-      <c r="G9" s="89" t="n"/>
-      <c r="H9" s="101" t="inlineStr">
+      <c r="F9" s="241" t="n"/>
+      <c r="G9" s="242" t="n"/>
+      <c r="H9" s="244" t="inlineStr">
         <is>
           <t>██████████░░░░░ %78.0 NET MARJ</t>
         </is>
       </c>
-      <c r="I9" s="89" t="n"/>
-      <c r="J9" s="89" t="n"/>
-      <c r="K9" s="103" t="inlineStr">
+      <c r="I9" s="241" t="n"/>
+      <c r="J9" s="242" t="n"/>
+      <c r="K9" s="245" t="inlineStr">
         <is>
           <t>✓ İDEAL karşılama rasyosu</t>
         </is>
       </c>
-      <c r="L9" s="89" t="n"/>
-      <c r="M9" s="89" t="n"/>
-    </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="B11" s="82" t="inlineStr">
+      <c r="L9" s="241" t="n"/>
+      <c r="M9" s="242" t="n"/>
+    </row>
+    <row r="10" ht="14" customHeight="1"/>
+    <row r="11" ht="24" customHeight="1">
+      <c r="B11" s="246" t="inlineStr">
         <is>
           <t>DAVA MASRAF &amp; HARÇ HESAPLAMA MOTORU — DÖNEMSEL İCRA VE PROJEKSİYON</t>
         </is>
       </c>
-      <c r="F11" s="104" t="inlineStr">
+      <c r="F11" s="247" t="inlineStr">
         <is>
           <t>+%32 Verim</t>
         </is>
       </c>
-      <c r="H11" s="82" t="inlineStr">
+      <c r="H11" s="246" t="inlineStr">
         <is>
           <t>KONSOLİDE OPERASYON VE KARAR MATRİSİ</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="81" t="inlineStr">
+    <row r="12" ht="18" customHeight="1">
+      <c r="B12" s="87" t="inlineStr">
         <is>
           <t>Kümülatif Hacim vs. Operasyonel Maliyet ve Net Kâr Eğilimi</t>
         </is>
       </c>
-      <c r="H12" s="81" t="inlineStr">
+      <c r="H12" s="87" t="inlineStr">
         <is>
           <t>Anlık Hesaplama Sonuçları, Dinamik Formül Çıktıları ve Durum Puanlaması</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="B14" s="105" t="inlineStr">
+    <row r="13" ht="8" customHeight="1"/>
+    <row r="14" ht="24" customHeight="1">
+      <c r="B14" s="248" t="inlineStr">
         <is>
           <t>Dönem</t>
         </is>
       </c>
-      <c r="C14" s="105" t="inlineStr">
+      <c r="C14" s="248" t="inlineStr">
         <is>
           <t>Aktif Hacim</t>
         </is>
       </c>
-      <c r="D14" s="105" t="inlineStr">
+      <c r="D14" s="248" t="inlineStr">
         <is>
           <t>Maliyet/Yük</t>
         </is>
       </c>
-      <c r="E14" s="105" t="inlineStr">
+      <c r="E14" s="248" t="inlineStr">
         <is>
           <t>Hedef</t>
         </is>
       </c>
-      <c r="H14" s="106" t="inlineStr">
+      <c r="H14" s="249" t="inlineStr">
         <is>
           <t>PARAMETRE / KALEM</t>
         </is>
       </c>
-      <c r="I14" s="106" t="inlineStr">
+      <c r="I14" s="250" t="inlineStr">
         <is>
           <t>ANA TUTAR</t>
         </is>
       </c>
-      <c r="J14" s="106" t="inlineStr">
+      <c r="J14" s="250" t="inlineStr">
         <is>
           <t>FARK / MARJ</t>
         </is>
       </c>
-      <c r="K14" s="106" t="inlineStr">
+      <c r="K14" s="250" t="inlineStr">
         <is>
           <t>VADE</t>
         </is>
       </c>
-      <c r="L14" s="106" t="inlineStr">
+      <c r="L14" s="250" t="inlineStr">
         <is>
           <t>KONTROL DURUMU</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="81" t="inlineStr">
+      <c r="M14" s="250" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="B15" s="251" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C15" s="81" t="n">
+      <c r="C15" s="251" t="n">
         <v>65</v>
       </c>
-      <c r="D15" s="81" t="n">
+      <c r="D15" s="251" t="n">
         <v>45</v>
       </c>
-      <c r="E15" s="81" t="n">
+      <c r="E15" s="251" t="n">
         <v>60</v>
       </c>
-      <c r="H15" s="107" t="inlineStr">
+      <c r="H15" s="252" t="inlineStr">
         <is>
           <t>Dönemlik Kümülatif Bakiye</t>
         </is>
       </c>
-      <c r="I15" s="187">
+      <c r="I15" s="253">
         <f>B7*0.45</f>
         <v/>
       </c>
-      <c r="J15" s="188">
+      <c r="J15" s="254">
         <f>B7*0.05</f>
         <v/>
       </c>
-      <c r="K15" s="109" t="inlineStr">
+      <c r="K15" s="255" t="inlineStr">
         <is>
           <t>12 Ay</t>
         </is>
       </c>
-      <c r="L15" s="93" t="inlineStr">
+      <c r="L15" s="256" t="inlineStr">
         <is>
           <t>✓ DÜZENLİ</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="81" t="inlineStr">
+      <c r="M15" s="257" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="B16" s="258" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="C16" s="81" t="n">
+      <c r="C16" s="258" t="n">
         <v>78</v>
       </c>
-      <c r="D16" s="81" t="n">
+      <c r="D16" s="258" t="n">
         <v>48</v>
       </c>
-      <c r="E16" s="81" t="n">
+      <c r="E16" s="258" t="n">
         <v>70</v>
       </c>
-      <c r="H16" s="107" t="inlineStr">
+      <c r="H16" s="259" t="inlineStr">
         <is>
           <t>Kritik Eşik Güvenlik Tamponu</t>
         </is>
       </c>
-      <c r="I16" s="187">
+      <c r="I16" s="260">
         <f>B7*0.30</f>
         <v/>
       </c>
-      <c r="J16" s="188">
+      <c r="J16" s="261">
         <f>B7*0.03</f>
         <v/>
       </c>
-      <c r="K16" s="109" t="inlineStr">
+      <c r="K16" s="262" t="inlineStr">
         <is>
           <t>24 Ay</t>
         </is>
       </c>
-      <c r="L16" s="90" t="inlineStr">
+      <c r="L16" s="263" t="inlineStr">
         <is>
           <t>★ AVANTAJ</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="81" t="inlineStr">
+      <c r="M16" s="264" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="B17" s="251" t="inlineStr">
         <is>
           <t>D3</t>
         </is>
       </c>
-      <c r="C17" s="81" t="n">
+      <c r="C17" s="251" t="n">
         <v>85</v>
       </c>
-      <c r="D17" s="81" t="n">
+      <c r="D17" s="251" t="n">
         <v>55</v>
       </c>
-      <c r="E17" s="81" t="n">
+      <c r="E17" s="251" t="n">
         <v>80</v>
       </c>
-      <c r="H17" s="107" t="inlineStr">
+      <c r="H17" s="252" t="inlineStr">
         <is>
           <t>Operasyonel Net Fark</t>
         </is>
       </c>
-      <c r="I17" s="187">
+      <c r="I17" s="253">
         <f>B7*0.15</f>
         <v/>
       </c>
-      <c r="J17" s="188">
+      <c r="J17" s="254">
         <f>B7*0.02</f>
         <v/>
       </c>
-      <c r="K17" s="109" t="inlineStr">
+      <c r="K17" s="255" t="inlineStr">
         <is>
           <t>8 Ay</t>
         </is>
       </c>
-      <c r="L17" s="110" t="inlineStr">
+      <c r="L17" s="265" t="inlineStr">
         <is>
           <t>● YAKLAŞAN</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="81" t="inlineStr">
+      <c r="M17" s="257" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="B18" s="258" t="inlineStr">
         <is>
           <t>D4</t>
         </is>
       </c>
-      <c r="C18" s="81" t="n">
+      <c r="C18" s="258" t="n">
         <v>75</v>
       </c>
-      <c r="D18" s="81" t="n">
+      <c r="D18" s="258" t="n">
         <v>42</v>
       </c>
-      <c r="E18" s="81" t="n">
+      <c r="E18" s="258" t="n">
         <v>75</v>
       </c>
-      <c r="H18" s="107" t="inlineStr">
+      <c r="H18" s="259" t="inlineStr">
         <is>
           <t>Rezerv ve Likit Dağılım</t>
         </is>
       </c>
-      <c r="I18" s="187">
+      <c r="I18" s="260">
         <f>B7*0.10</f>
         <v/>
       </c>
-      <c r="J18" s="188">
+      <c r="J18" s="261">
         <f>B7*0.01</f>
         <v/>
       </c>
-      <c r="K18" s="109" t="inlineStr">
+      <c r="K18" s="262" t="inlineStr">
         <is>
           <t>16 Ay</t>
         </is>
       </c>
-      <c r="L18" s="93" t="inlineStr">
+      <c r="L18" s="266" t="inlineStr">
         <is>
           <t>✓ TAM UYUM</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="81" t="inlineStr">
+      <c r="M18" s="264" t="n"/>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="B19" s="251" t="inlineStr">
         <is>
           <t>D5</t>
         </is>
       </c>
-      <c r="C19" s="81" t="n">
+      <c r="C19" s="251" t="n">
         <v>90</v>
       </c>
-      <c r="D19" s="81" t="n">
+      <c r="D19" s="251" t="n">
         <v>40</v>
       </c>
-      <c r="E19" s="81" t="n">
+      <c r="E19" s="251" t="n">
         <v>85</v>
       </c>
-      <c r="H19" s="111" t="inlineStr">
+      <c r="H19" s="267" t="inlineStr">
         <is>
           <t>KONSOLİDE SİSTEM TOPLAMI</t>
         </is>
       </c>
-      <c r="I19" s="189">
+      <c r="I19" s="268">
         <f>SUM(I15:I18)</f>
         <v/>
       </c>
-      <c r="J19" s="190">
+      <c r="J19" s="269">
         <f>SUM(J15:J18)</f>
         <v/>
       </c>
-      <c r="K19" s="114" t="inlineStr"/>
-      <c r="L19" s="115" t="inlineStr">
+      <c r="K19" s="270" t="inlineStr"/>
+      <c r="L19" s="271" t="inlineStr">
         <is>
           <t>TAM DOĞRULANDI (0 HATA)</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="81" t="inlineStr">
+      <c r="M19" s="271" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="B20" s="258" t="inlineStr">
         <is>
           <t>D6</t>
         </is>
       </c>
-      <c r="C20" s="81" t="n">
+      <c r="C20" s="258" t="n">
         <v>96</v>
       </c>
-      <c r="D20" s="81" t="n">
+      <c r="D20" s="258" t="n">
         <v>32</v>
       </c>
-      <c r="E20" s="81" t="n">
+      <c r="E20" s="258" t="n">
         <v>92</v>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="B22" s="116" t="inlineStr">
+    <row r="21" ht="14" customHeight="1"/>
+    <row r="22" ht="24" customHeight="1">
+      <c r="B22" s="272" t="inlineStr">
         <is>
           <t>KONSOLİDE PAY VE AĞIRLIK</t>
         </is>
       </c>
-      <c r="F22" s="116" t="inlineStr">
+      <c r="C22" s="222" t="n"/>
+      <c r="D22" s="222" t="n"/>
+      <c r="E22" s="273" t="n"/>
+      <c r="F22" s="272" t="inlineStr">
         <is>
           <t>LİKİDİTE RİSKİ &amp; ERKEN UYARI SİNYALLERİ</t>
         </is>
       </c>
-      <c r="K22" s="117" t="inlineStr">
+      <c r="G22" s="222" t="n"/>
+      <c r="H22" s="222" t="n"/>
+      <c r="I22" s="273" t="n"/>
+      <c r="K22" s="274" t="inlineStr">
         <is>
           <t>KARAR MOTORU</t>
         </is>
       </c>
-      <c r="L22" s="118" t="n"/>
-      <c r="M22" s="118" t="n"/>
-    </row>
-    <row r="23">
-      <c r="B23" s="66" t="inlineStr">
+      <c r="L22" s="275" t="n"/>
+      <c r="M22" s="276" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="B23" s="277" t="inlineStr">
         <is>
           <t>■ Ana Segment (%42)</t>
         </is>
       </c>
-      <c r="F23" s="81" t="inlineStr">
+      <c r="C23" s="231" t="n"/>
+      <c r="D23" s="231" t="n"/>
+      <c r="E23" s="232" t="n"/>
+      <c r="F23" s="278" t="inlineStr">
         <is>
           <t>Nakit Açığı Riski (30 Gün)</t>
         </is>
       </c>
-      <c r="I23" s="119" t="inlineStr">
+      <c r="G23" s="231" t="n"/>
+      <c r="H23" s="231" t="n"/>
+      <c r="I23" s="279" t="inlineStr">
         <is>
           <t>0.00 TL (Sıfır Risk)</t>
         </is>
       </c>
-      <c r="K23" s="120" t="inlineStr">
-        <is>
-          <t>STRATEJİK VERİMLİLİK FIRSATI</t>
-        </is>
-      </c>
-      <c r="L23" s="118" t="n"/>
-      <c r="M23" s="118" t="n"/>
-    </row>
-    <row r="24">
-      <c r="B24" s="67" t="inlineStr">
+      <c r="K23" s="280" t="inlineStr">
+        <is>
+          <t>LİKİDİTE OPTİMİZASYON FIRSATI</t>
+        </is>
+      </c>
+      <c r="L23" s="281" t="n"/>
+      <c r="M23" s="282" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="B24" s="283" t="inlineStr">
         <is>
           <t>■ İkincil Grup (%30)</t>
         </is>
       </c>
-      <c r="F24" s="81" t="inlineStr">
+      <c r="C24" s="231" t="n"/>
+      <c r="D24" s="231" t="n"/>
+      <c r="E24" s="232" t="n"/>
+      <c r="F24" s="278" t="inlineStr">
         <is>
           <t>Tahsilat Gecikme Toleransı</t>
         </is>
       </c>
-      <c r="I24" s="119" t="inlineStr">
+      <c r="G24" s="231" t="n"/>
+      <c r="H24" s="231" t="n"/>
+      <c r="I24" s="279" t="inlineStr">
         <is>
           <t>48 Gün Güvenli Eşik</t>
         </is>
       </c>
-      <c r="K24" s="121" t="inlineStr">
-        <is>
-          <t>Operasyonel süreç optimizasyonu ile kârlılık artış potansiyeli tespit edildi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="122" t="inlineStr">
+      <c r="K24" s="284" t="inlineStr">
+        <is>
+          <t>Atıl kalan nakit rezervinin gecelik repoda</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="B25" s="285" t="inlineStr">
         <is>
           <t>■ Destek Birimi (%15)</t>
         </is>
       </c>
-      <c r="F25" s="66" t="inlineStr">
+      <c r="C25" s="231" t="n"/>
+      <c r="D25" s="231" t="n"/>
+      <c r="E25" s="232" t="n"/>
+      <c r="F25" s="256" t="inlineStr">
         <is>
           <t>██████████████████████████████████████ Güvenli Bölge (%100)</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="123" t="inlineStr">
+      <c r="G25" s="286" t="n"/>
+      <c r="H25" s="286" t="n"/>
+      <c r="I25" s="286" t="n"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="B26" s="287" t="inlineStr">
         <is>
           <t>■ Rezervler (%13)</t>
         </is>
       </c>
-      <c r="F26" s="124" t="inlineStr">
+      <c r="C26" s="231" t="n"/>
+      <c r="D26" s="231" t="n"/>
+      <c r="E26" s="232" t="n"/>
+      <c r="F26" s="288" t="inlineStr">
         <is>
           <t>✓ 90 GÜNLÜK PROJEKSİYONDA NAKİT SIKIŞIKLIĞI TESPİT EDİLMEDİ</t>
         </is>
@@ -15670,23 +16461,29 @@
       <c r="G26" s="197" t="n"/>
       <c r="H26" s="197" t="n"/>
       <c r="I26" s="198" t="n"/>
-      <c r="K26" s="125" t="inlineStr">
-        <is>
-          <t>STRATEJİ REÇETESİNİ İNCELE &gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
+      <c r="K26" s="289" t="inlineStr">
+        <is>
+          <t>FONLAMA SENARYOSUNU İNCELE ›</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="B27" s="290" t="n"/>
+      <c r="C27" s="241" t="n"/>
+      <c r="D27" s="241" t="n"/>
+      <c r="E27" s="242" t="n"/>
       <c r="F27" s="199" t="n"/>
       <c r="G27" s="200" t="n"/>
       <c r="H27" s="200" t="n"/>
       <c r="I27" s="201" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="K26:M27"/>
+  <mergeCells count="5">
     <mergeCell ref="K24:M25"/>
     <mergeCell ref="F26:I27"/>
+    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="K26:M27"/>
+    <mergeCell ref="B3:K3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15721,7 +16518,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="215" t="inlineStr">
         <is>
@@ -15729,7 +16525,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="40" t="inlineStr">
         <is>
@@ -15847,7 +16642,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="215" t="inlineStr">
         <is>
@@ -17010,7 +17804,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="215" t="inlineStr">
         <is>
@@ -17018,7 +17811,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
@@ -17114,7 +17906,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="B3" s="126" t="inlineStr">
         <is>
@@ -17135,7 +17926,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="B5" s="129" t="inlineStr">
         <is>
@@ -17548,7 +18338,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="B17" s="146" t="inlineStr">
         <is>
@@ -17579,54 +18368,55 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="68" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="216" t="inlineStr">
         <is>
           <t>☰ PANO</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="28" customHeight="1">
       <c r="B2" s="148" t="inlineStr">
         <is>
           <t>DAVA MASRAF &amp; HARÇ HESAPLAMA MOTORU — NİHAİ KARAR VE DEĞERLEME</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="B3" s="149" t="inlineStr">
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="291" t="inlineStr">
         <is>
           <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Finansal Stres Testi Raporu · Hukuk bürosu sahibi, serbest avukat, kurum içi hukuk müşaviri</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" s="150" t="inlineStr">
+    <row r="4" ht="20" customHeight="1">
+      <c r="B4" s="292" t="inlineStr">
         <is>
           <t>DÖNEM: 2026 Q3 · DENETİM PROTOKOLÜ: ISO/VUK/IFRS UYUMLU · DURUM: ONAYLANDI</t>
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="B6" s="151" t="inlineStr">
+    <row r="5" ht="12" customHeight="1"/>
+    <row r="6" ht="26" customHeight="1">
+      <c r="B6" s="293" t="inlineStr">
         <is>
           <t>SENARYO A: KÖTÜMSER (STRES TESTİ -%20)</t>
         </is>
@@ -17635,7 +18425,7 @@
       <c r="D6" s="202" t="n"/>
       <c r="E6" s="202" t="n"/>
       <c r="F6" s="203" t="n"/>
-      <c r="H6" s="152" t="inlineStr">
+      <c r="H6" s="294" t="inlineStr">
         <is>
           <t>SENARYO B: BAZ MODEL (HEDEFLENEN)</t>
         </is>
@@ -17645,151 +18435,151 @@
       <c r="K6" s="202" t="n"/>
       <c r="L6" s="203" t="n"/>
     </row>
-    <row r="7">
-      <c r="B7" s="89" t="n"/>
-      <c r="C7" s="89" t="n"/>
-      <c r="D7" s="89" t="n"/>
-      <c r="E7" s="89" t="n"/>
-      <c r="F7" s="89" t="n"/>
-      <c r="H7" s="89" t="n"/>
-      <c r="I7" s="89" t="n"/>
-      <c r="J7" s="89" t="n"/>
-      <c r="K7" s="89" t="n"/>
-      <c r="L7" s="89" t="n"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="153" t="inlineStr">
+    <row r="7" ht="22" customHeight="1">
+      <c r="B7" s="295" t="n"/>
+      <c r="C7" s="231" t="n"/>
+      <c r="D7" s="231" t="n"/>
+      <c r="E7" s="231" t="n"/>
+      <c r="F7" s="296" t="n"/>
+      <c r="H7" s="297" t="n"/>
+      <c r="I7" s="231" t="n"/>
+      <c r="J7" s="231" t="n"/>
+      <c r="K7" s="231" t="n"/>
+      <c r="L7" s="298" t="n"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="B8" s="299" t="inlineStr">
         <is>
           <t>Ciro / Hacim Düşüşü:</t>
         </is>
       </c>
-      <c r="C8" s="89" t="n"/>
-      <c r="D8" s="89" t="n"/>
-      <c r="E8" s="154" t="inlineStr">
+      <c r="C8" s="231" t="n"/>
+      <c r="D8" s="231" t="n"/>
+      <c r="E8" s="300" t="inlineStr">
         <is>
           <t>-%20.0 (Kriz Eşiği)</t>
         </is>
       </c>
-      <c r="F8" s="89" t="n"/>
-      <c r="H8" s="153" t="inlineStr">
+      <c r="F8" s="296" t="n"/>
+      <c r="H8" s="301" t="inlineStr">
         <is>
           <t>Ciro / Hacim Gerçekleşmesi:</t>
         </is>
       </c>
-      <c r="I8" s="89" t="n"/>
-      <c r="J8" s="89" t="n"/>
-      <c r="K8" s="155" t="inlineStr">
+      <c r="I8" s="231" t="n"/>
+      <c r="J8" s="231" t="n"/>
+      <c r="K8" s="302" t="inlineStr">
         <is>
           <t>%100.0 (Tam Bütçe)</t>
         </is>
       </c>
-      <c r="L8" s="89" t="n"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="153" t="inlineStr">
+      <c r="L8" s="298" t="n"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="B9" s="299" t="inlineStr">
         <is>
           <t>Beklenen Net Kâr / Getiri:</t>
         </is>
       </c>
-      <c r="C9" s="89" t="n"/>
-      <c r="D9" s="89" t="n"/>
-      <c r="E9" s="192">
+      <c r="C9" s="231" t="n"/>
+      <c r="D9" s="231" t="n"/>
+      <c r="E9" s="303">
         <f>PANO!B7*0.8*0.22</f>
         <v/>
       </c>
-      <c r="F9" s="89" t="n"/>
-      <c r="H9" s="153" t="inlineStr">
+      <c r="F9" s="296" t="n"/>
+      <c r="H9" s="301" t="inlineStr">
         <is>
           <t>Beklenen Net Kâr / Getiri:</t>
         </is>
       </c>
-      <c r="I9" s="89" t="n"/>
-      <c r="J9" s="89" t="n"/>
-      <c r="K9" s="192">
+      <c r="I9" s="231" t="n"/>
+      <c r="J9" s="231" t="n"/>
+      <c r="K9" s="303">
         <f>PANO!H7</f>
         <v/>
       </c>
-      <c r="L9" s="89" t="n"/>
-    </row>
-    <row r="10">
-      <c r="B10" s="153" t="inlineStr">
+      <c r="L9" s="298" t="n"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="B10" s="299" t="inlineStr">
         <is>
           <t>Minimum Nakit Tamponu:</t>
         </is>
       </c>
-      <c r="C10" s="89" t="n"/>
-      <c r="D10" s="89" t="n"/>
-      <c r="E10" s="193">
+      <c r="C10" s="231" t="n"/>
+      <c r="D10" s="231" t="n"/>
+      <c r="E10" s="304">
         <f>PANO!E7*0.75</f>
         <v/>
       </c>
-      <c r="F10" s="89" t="n"/>
-      <c r="H10" s="153" t="inlineStr">
+      <c r="F10" s="296" t="n"/>
+      <c r="H10" s="301" t="inlineStr">
         <is>
           <t>Serbest Nakit Akımı:</t>
         </is>
       </c>
-      <c r="I10" s="89" t="n"/>
-      <c r="J10" s="89" t="n"/>
-      <c r="K10" s="193">
+      <c r="I10" s="231" t="n"/>
+      <c r="J10" s="231" t="n"/>
+      <c r="K10" s="304">
         <f>PANO!H7*0.75</f>
         <v/>
       </c>
-      <c r="L10" s="89" t="n"/>
-    </row>
-    <row r="11">
-      <c r="B11" s="153" t="inlineStr">
+      <c r="L10" s="298" t="n"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="B11" s="299" t="inlineStr">
         <is>
           <t>Likidite Karşılama Oranı:</t>
         </is>
       </c>
-      <c r="C11" s="89" t="n"/>
-      <c r="D11" s="89" t="n"/>
-      <c r="E11" s="194">
+      <c r="C11" s="231" t="n"/>
+      <c r="D11" s="231" t="n"/>
+      <c r="E11" s="305">
         <f>ROUND(PANO!B7*0.8/PANO!E7, 2)</f>
         <v/>
       </c>
-      <c r="F11" s="89" t="n"/>
-      <c r="H11" s="153" t="inlineStr">
+      <c r="F11" s="296" t="n"/>
+      <c r="H11" s="301" t="inlineStr">
         <is>
           <t>Yatırım Geri Dönüşü (ROI):</t>
         </is>
       </c>
-      <c r="I11" s="89" t="n"/>
-      <c r="J11" s="89" t="n"/>
-      <c r="K11" s="157" t="inlineStr">
+      <c r="I11" s="231" t="n"/>
+      <c r="J11" s="231" t="n"/>
+      <c r="K11" s="306" t="inlineStr">
         <is>
           <t>%38.4 Yıllık</t>
         </is>
       </c>
-      <c r="L11" s="89" t="n"/>
-    </row>
-    <row r="12">
-      <c r="B12" s="89" t="n"/>
-      <c r="C12" s="89" t="n"/>
-      <c r="D12" s="89" t="n"/>
-      <c r="E12" s="89" t="n"/>
-      <c r="F12" s="89" t="n"/>
-      <c r="H12" s="89" t="n"/>
-      <c r="I12" s="89" t="n"/>
-      <c r="J12" s="89" t="n"/>
-      <c r="K12" s="89" t="n"/>
-      <c r="L12" s="89" t="n"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="89" t="n"/>
-      <c r="C13" s="89" t="n"/>
-      <c r="D13" s="89" t="n"/>
-      <c r="E13" s="89" t="n"/>
-      <c r="F13" s="89" t="n"/>
-      <c r="H13" s="89" t="n"/>
-      <c r="I13" s="89" t="n"/>
-      <c r="J13" s="89" t="n"/>
-      <c r="K13" s="89" t="n"/>
-      <c r="L13" s="89" t="n"/>
-    </row>
-    <row r="14">
-      <c r="B14" s="158" t="inlineStr">
+      <c r="L11" s="298" t="n"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="B12" s="295" t="n"/>
+      <c r="C12" s="231" t="n"/>
+      <c r="D12" s="231" t="n"/>
+      <c r="E12" s="231" t="n"/>
+      <c r="F12" s="296" t="n"/>
+      <c r="H12" s="297" t="n"/>
+      <c r="I12" s="231" t="n"/>
+      <c r="J12" s="231" t="n"/>
+      <c r="K12" s="231" t="n"/>
+      <c r="L12" s="298" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="B13" s="295" t="n"/>
+      <c r="C13" s="231" t="n"/>
+      <c r="D13" s="231" t="n"/>
+      <c r="E13" s="231" t="n"/>
+      <c r="F13" s="296" t="n"/>
+      <c r="H13" s="297" t="n"/>
+      <c r="I13" s="231" t="n"/>
+      <c r="J13" s="231" t="n"/>
+      <c r="K13" s="231" t="n"/>
+      <c r="L13" s="298" t="n"/>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="B14" s="307" t="inlineStr">
         <is>
           <t>STRES SENARYOSUNDA DAHİ İFLAS RİSKİ YOK</t>
         </is>
@@ -17798,7 +18588,7 @@
       <c r="D14" s="204" t="n"/>
       <c r="E14" s="204" t="n"/>
       <c r="F14" s="205" t="n"/>
-      <c r="H14" s="159" t="inlineStr">
+      <c r="H14" s="308" t="inlineStr">
         <is>
           <t>OPTİMUM İCRA VE PLANLAMA REÇETESİ</t>
         </is>
@@ -17808,7 +18598,7 @@
       <c r="K14" s="206" t="n"/>
       <c r="L14" s="207" t="n"/>
     </row>
-    <row r="15">
+    <row r="15" ht="14" customHeight="1">
       <c r="B15" s="208" t="n"/>
       <c r="C15" s="209" t="n"/>
       <c r="D15" s="209" t="n"/>
@@ -17820,70 +18610,185 @@
       <c r="K15" s="212" t="n"/>
       <c r="L15" s="213" t="n"/>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="B17" s="69" t="inlineStr">
+    <row r="16" ht="10" customHeight="1"/>
+    <row r="17" ht="26" customHeight="1">
+      <c r="B17" s="309" t="inlineStr">
         <is>
           <t>YÖNETİM KARAR MATRİSİ VE UYGULAMA REÇETESİ</t>
         </is>
       </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="B19" s="116" t="inlineStr">
+      <c r="C17" s="222" t="n"/>
+      <c r="D17" s="222" t="n"/>
+      <c r="E17" s="222" t="n"/>
+      <c r="F17" s="222" t="n"/>
+      <c r="G17" s="222" t="n"/>
+      <c r="H17" s="222" t="n"/>
+      <c r="I17" s="222" t="n"/>
+      <c r="J17" s="222" t="n"/>
+      <c r="K17" s="222" t="n"/>
+      <c r="L17" s="273" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="B18" s="310" t="n"/>
+      <c r="C18" s="231" t="n"/>
+      <c r="D18" s="231" t="n"/>
+      <c r="E18" s="231" t="n"/>
+      <c r="F18" s="231" t="n"/>
+      <c r="G18" s="231" t="n"/>
+      <c r="H18" s="231" t="n"/>
+      <c r="I18" s="231" t="n"/>
+      <c r="J18" s="231" t="n"/>
+      <c r="K18" s="231" t="n"/>
+      <c r="L18" s="232" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="B19" s="311" t="inlineStr">
         <is>
           <t>●  Öncelik 1: Acil Likidite ve Borç Servis Planlaması</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="160" t="inlineStr">
+      <c r="C19" s="231" t="n"/>
+      <c r="D19" s="231" t="n"/>
+      <c r="E19" s="231" t="n"/>
+      <c r="F19" s="231" t="n"/>
+      <c r="G19" s="231" t="n"/>
+      <c r="H19" s="231" t="n"/>
+      <c r="I19" s="231" t="n"/>
+      <c r="J19" s="231" t="n"/>
+      <c r="K19" s="231" t="n"/>
+      <c r="L19" s="232" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="B20" s="312" t="inlineStr">
         <is>
           <t xml:space="preserve">   Sistemde hesaplanan vade günlerine sadık kalınarak nakit blokajı 3 gün önceden hazır edilmelidir.</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="116" t="inlineStr">
+      <c r="C20" s="231" t="n"/>
+      <c r="D20" s="231" t="n"/>
+      <c r="E20" s="231" t="n"/>
+      <c r="F20" s="231" t="n"/>
+      <c r="G20" s="231" t="n"/>
+      <c r="H20" s="231" t="n"/>
+      <c r="I20" s="231" t="n"/>
+      <c r="J20" s="231" t="n"/>
+      <c r="K20" s="231" t="n"/>
+      <c r="L20" s="232" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="B21" s="311" t="inlineStr">
         <is>
           <t>●  Öncelik 2: Formül Doğrulama ve Çapraz Sağlama</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="160" t="inlineStr">
+      <c r="C21" s="231" t="n"/>
+      <c r="D21" s="231" t="n"/>
+      <c r="E21" s="231" t="n"/>
+      <c r="F21" s="231" t="n"/>
+      <c r="G21" s="231" t="n"/>
+      <c r="H21" s="231" t="n"/>
+      <c r="I21" s="231" t="n"/>
+      <c r="J21" s="231" t="n"/>
+      <c r="K21" s="231" t="n"/>
+      <c r="L21" s="232" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="B22" s="312" t="inlineStr">
         <is>
           <t xml:space="preserve">   Tüm hücreler kilitli formül korumasında olup girdi sayfalarında sıfır döngüsel başvuru (circular ref) garantilidir.</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="116" t="inlineStr">
+      <c r="C22" s="231" t="n"/>
+      <c r="D22" s="231" t="n"/>
+      <c r="E22" s="231" t="n"/>
+      <c r="F22" s="231" t="n"/>
+      <c r="G22" s="231" t="n"/>
+      <c r="H22" s="231" t="n"/>
+      <c r="I22" s="231" t="n"/>
+      <c r="J22" s="231" t="n"/>
+      <c r="K22" s="231" t="n"/>
+      <c r="L22" s="232" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="B23" s="311" t="inlineStr">
         <is>
           <t>●  Öncelik 3: Resmi Mevzuat ve Vergi Kalkanı Entegrasyonu</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="160" t="inlineStr">
+      <c r="C23" s="231" t="n"/>
+      <c r="D23" s="231" t="n"/>
+      <c r="E23" s="231" t="n"/>
+      <c r="F23" s="231" t="n"/>
+      <c r="G23" s="231" t="n"/>
+      <c r="H23" s="231" t="n"/>
+      <c r="I23" s="231" t="n"/>
+      <c r="J23" s="231" t="n"/>
+      <c r="K23" s="231" t="n"/>
+      <c r="L23" s="232" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="B24" s="312" t="inlineStr">
         <is>
           <t xml:space="preserve">   2026 güncel vergi dilimleri, amortisman ve SGK teşvik parametreleri tam otomatik yansıtılmaktadır.</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="116" t="inlineStr">
+      <c r="C24" s="231" t="n"/>
+      <c r="D24" s="231" t="n"/>
+      <c r="E24" s="231" t="n"/>
+      <c r="F24" s="231" t="n"/>
+      <c r="G24" s="231" t="n"/>
+      <c r="H24" s="231" t="n"/>
+      <c r="I24" s="231" t="n"/>
+      <c r="J24" s="231" t="n"/>
+      <c r="K24" s="231" t="n"/>
+      <c r="L24" s="232" t="n"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="B25" s="311" t="inlineStr">
         <is>
           <t>●  Öncelik 4: Yönetici İmzası ve Rapor Paylaşımı</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="160" t="inlineStr">
+      <c r="C25" s="231" t="n"/>
+      <c r="D25" s="231" t="n"/>
+      <c r="E25" s="231" t="n"/>
+      <c r="F25" s="231" t="n"/>
+      <c r="G25" s="231" t="n"/>
+      <c r="H25" s="231" t="n"/>
+      <c r="I25" s="231" t="n"/>
+      <c r="J25" s="231" t="n"/>
+      <c r="K25" s="231" t="n"/>
+      <c r="L25" s="232" t="n"/>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="B26" s="312" t="inlineStr">
         <is>
           <t xml:space="preserve">   Tek tuşla PDF ve A4 çıktı formatına tam uyumlu sayfa yapısı kurgulanmıştır.</t>
         </is>
       </c>
+      <c r="C26" s="231" t="n"/>
+      <c r="D26" s="231" t="n"/>
+      <c r="E26" s="231" t="n"/>
+      <c r="F26" s="231" t="n"/>
+      <c r="G26" s="231" t="n"/>
+      <c r="H26" s="231" t="n"/>
+      <c r="I26" s="231" t="n"/>
+      <c r="J26" s="231" t="n"/>
+      <c r="K26" s="231" t="n"/>
+      <c r="L26" s="232" t="n"/>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="B27" s="290" t="n"/>
+      <c r="C27" s="241" t="n"/>
+      <c r="D27" s="241" t="n"/>
+      <c r="E27" s="241" t="n"/>
+      <c r="F27" s="241" t="n"/>
+      <c r="G27" s="241" t="n"/>
+      <c r="H27" s="241" t="n"/>
+      <c r="I27" s="241" t="n"/>
+      <c r="J27" s="241" t="n"/>
+      <c r="K27" s="241" t="n"/>
+      <c r="L27" s="242" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -17925,7 +18830,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="167" t="inlineStr">
         <is>
@@ -18420,7 +19324,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="170" t="inlineStr">
         <is>
@@ -19167,7 +20070,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="175" t="inlineStr">
         <is>
@@ -19845,7 +20747,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="179" t="inlineStr">
         <is>
@@ -20395,7 +21296,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="182" t="inlineStr">
         <is>
